--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45012</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>45798.58304398148</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>44299</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>44264</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>45579</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>45645.27462962963</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45012</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45139</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45441</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>45568</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>45133</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44067</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>45604</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>45783.4903125</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44076</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>44578</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>45421</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>45723.61545138889</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>45742.41269675926</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>45832.36966435185</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>44412</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45042</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>45723.59275462963</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>45568</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>45723.57098379629</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45731.65016203704</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>45421</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>45764.47825231482</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45441.33914351852</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>45012</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>45013.77040509259</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>45086</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>44977</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45604</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>44931</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>45832.31648148148</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>45833.56057870371</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>45583</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>45772.6571412037</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>45758.54390046297</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44789</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>45583</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45258.56491898148</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44067</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>45568.44137731481</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>45733.45780092593</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45694</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45832.3365625</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>44454</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>45086</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>44308</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>44480</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>44426</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>44524</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>44452</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>44490</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>45742.43848379629</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>45723.66964120371</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>45744</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>45744.41443287037</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>45411.57177083333</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>45583.3479050926</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44132</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45369</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>45747.58131944444</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45348.68336805556</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>44886.54420138889</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>45770.63996527778</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>45408</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>44089</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45763.60795138889</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>45783.61222222223</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>45376</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>45362</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45201</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>45796</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>45201</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>45421</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>45251</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>45096</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45716.5672337963</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>45580</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         <v>45117</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>45723.55663194445</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>45583</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>44354</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>44777.49493055556</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>45702.76395833334</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>45174</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>45056</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>45042</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>45583</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>44151</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>44219</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>44064</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>44211</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>44211</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>44158</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>44063</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44146</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>44456</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>44456</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>44301</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>44307</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>44530</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>44582.4696875</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>44211</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>44217</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>44214</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>44176</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>44504</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>44107</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44502</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>44622</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>44537</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>44218</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>44825.47923611111</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>44728.82296296296</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>44340.80107638889</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>44279</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>44739</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>44368</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>44719.43086805556</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>44216</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>44169</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>44169</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>44370</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>44258</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>44503</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>44440</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44448</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>44306</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44368</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44441</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>44301</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>44865</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>44055</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>44294</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>44286</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44524.67836805555</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44385</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>44696.775</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44390</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>44432</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>44433</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44494</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>44447</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44368.88704861111</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>44340</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>44333</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>44671</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>44713</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>44813</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44530</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>44515</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>44571</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44169</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44442.66228009259</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44208</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>44272</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>44475</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>44475</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>44393</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>44630.3978587963</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>44371</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44371</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44124.63679398148</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44362</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44211</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44211</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44524</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>44271.81282407408</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>44447</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>44530</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>44313</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44300</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44503</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>44300</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>44459</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>44446</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>44321</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>44879.39153935185</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>44459</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44475</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>44475</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>44063</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44249</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44686</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44602</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44574</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44326</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44326</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44326</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>44363</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>44098</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15224,7 +15224,7 @@
         <v>44348</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>44726</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44886.47697916667</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>44889.55255787037</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44328</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44452</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>44152</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>44874</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>44219</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>44449</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>44162</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44825</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>44487</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>44596</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>44358</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>44468</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>44756</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>44208</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>44252</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>44441</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>44137</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>44137</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>44452</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>44432</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>44272</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>44582</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>44630</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>44825</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>44740</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>44344.49251157408</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17004,7 +17004,7 @@
         <v>44363</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>44741.57063657408</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>44313</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>44279</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>44445</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>44557</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>44302</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>44270</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>44730</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>44354.45140046296</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>44053</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>44869.4575</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>45729</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>45110</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>45274.43547453704</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45678.44092592593</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>44652</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>44362</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45733.44431712963</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45076</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>45709.4119212963</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>44067</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44096</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>45706.49520833333</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45706.54385416667</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45405</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>45772.6652662037</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>44578</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>45254</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>45077</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45048</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
         <v>45509.57052083333</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45121</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>45043</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>45268</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>45043.53597222222</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45215.63818287037</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>45183</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>44825</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>44865</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>45771.76943287037</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>45072</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44862</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>45043</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45614.52813657407</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19689,7 +19689,7 @@
         <v>45771.69168981481</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45202</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>45532</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45049.34974537037</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>45049.35048611111</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45527.41597222222</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>44939</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>45012.79270833333</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>44803.59099537037</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45678.57045138889</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45363.58979166667</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45678.58166666667</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45716.55766203703</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>44061</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>45237</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20554,7 +20554,7 @@
         <v>45769.45751157407</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>45771.66951388889</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45769.41631944444</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>45628.56513888889</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45769</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45769</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>44159.36447916667</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45736.31508101852</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45436.41305555555</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45758.60465277778</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45758.61055555556</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>44454</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>45736.72646990741</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45733.43347222222</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>45699.65944444444</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>45699.75690972222</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>44805</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44096</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45118</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>45369.62108796297</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45336</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>45741.63417824074</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>45092</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>45037</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>44860</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>44137</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45741.51940972222</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>44439.97621527778</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>44147</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45706.42958333333</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>45414.3944212963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45092.36790509259</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45090</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>45535.91413194445</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>44896</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>45373.48878472222</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>44900</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45520.52375</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>44083</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>45373.73894675926</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22909,7 +22909,7 @@
         <v>44862</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45769</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45219.32268518519</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45330</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>44860</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>45562.57070601852</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>44897</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>44928.45552083333</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>45386.32806712963</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>44923.67971064815</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44414</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>45731.59962962963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>44151.53271990741</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>45442.67793981481</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45386</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>44462</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>45723.67724537037</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>45279.66864583334</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>44907.66710648148</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>45747.59501157407</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>45027</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45373.72511574074</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24208,7 +24208,7 @@
         <v>44433</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>44935</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>45558</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>44935.60138888889</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>44588</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>45317</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>45359.68173611111</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45334</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>45478.47236111111</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>45128</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44237</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44861</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>45432.6291550926</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>45425.89037037037</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>45436.41847222222</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45118</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>44980</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>44880.44351851852</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>45317</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>44783</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>44057.35462962963</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>44977.63902777778</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>44939</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>45278</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>44858</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45678.6377199074</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>45117</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>44236</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>45153</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>44163</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>45603.49528935185</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>44936</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>45742.31784722222</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>45153</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45093</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44067</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44907.65043981482</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>45731.60166666667</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>45716.39159722222</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>45211.52895833334</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>44936</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45369.61550925926</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>45016.64986111111</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>45129</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>45457.59425925926</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26873,7 +26873,7 @@
         <v>45250.5799537037</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>44361</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>45764.43782407408</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>44488</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>45106</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>45096</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45379</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45405</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45497</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>45240</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45684.4203125</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45706.54204861111</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>45706.54572916667</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>45310</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>45644</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>45742.32277777778</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>45266</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>45490.72372685185</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>44930</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45758.56056712963</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>45709.42859953704</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>44936</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>45339.5277199074</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>45527.42443287037</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>45408.49326388889</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>45254</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>45741.53599537037</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>45629.7202662037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>45763.64096064815</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>44607</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>44322</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>44890</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>44950</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>45092.35266203704</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>45006</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>45414.5519212963</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45726.91224537037</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>45030.62740740741</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>45030</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>45777.61991898148</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>45782.66719907407</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>45782.659375</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29332,7 +29332,7 @@
         <v>44994.41405092592</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29389,7 +29389,7 @@
         <v>45783</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29446,7 +29446,7 @@
         <v>45110.56027777777</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29503,7 +29503,7 @@
         <v>45110</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>45784</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>45784.62866898148</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>44582</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>45783.68689814815</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>45783.48681712963</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>45132</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>45202.56994212963</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>45365</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>44176</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45370</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>44957</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>45670</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>44494</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>44974.564375</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>45771.44005787037</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>45442.6052199074</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30584,7 +30584,7 @@
         <v>45442.60829861111</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>45092.36126157407</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>44936</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45184</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>45178.43909722222</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>45786.36358796297</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>44084</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45671.62931712963</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>45595</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45030</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45637</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>45593.59819444444</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>44889</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45673.49019675926</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>45126</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31469,7 +31469,7 @@
         <v>45126</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>45028</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>45587.58498842592</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>44910</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>45141</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31769,7 +31769,7 @@
         <v>44181</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>45453.54733796296</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45453.55123842593</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45145</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>45400</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>45671.59245370371</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>44131</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>45403.86942129629</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         <v>45106</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>45106</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>44935.64165509259</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>44181</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>45114</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>45114</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45706.47790509259</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>45786</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>45789.42597222222</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>44565</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>45201.63637731481</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45310.41982638889</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>45527.43385416667</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>45758.36203703703</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>44427.49322916667</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>45790</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>45546</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>45356.64872685185</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45106</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>45369.61841435185</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>45566.46769675926</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>45215</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>45678.57731481481</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>44936.46326388889</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>45092.35369212963</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45336</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>45266.69091435185</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>44974.65918981482</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45792.42109953704</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>45792.42542824074</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45191</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>44168</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>45033</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>44536</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>45678.57503472222</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44596</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>45794.82583333334</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44943.56112268518</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>44573</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45794.81975694445</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>45794.82150462963</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>45579.56570601852</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>45527.40489583334</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>45794.81730324074</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>45796.49842592593</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>45796</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>45794.81583333333</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45723.65960648148</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>45174</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>45174</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35125,7 +35125,7 @@
         <v>45550.68804398148</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>45742.33188657407</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>44448</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>45794.82371527778</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35353,7 +35353,7 @@
         <v>45796</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35410,7 +35410,7 @@
         <v>45796.36326388889</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>45394</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>45259</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>45453.52299768518</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>45727.6683449074</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35710,7 +35710,7 @@
         <v>45159</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>45238.33091435185</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>45432.54622685185</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>44455</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>45838.683125</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>45043</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>45798.59671296296</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>45049</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36176,7 +36176,7 @@
         <v>44943</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>45798.66228009259</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36300,7 +36300,7 @@
         <v>45764.43002314815</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36357,7 +36357,7 @@
         <v>45091</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>45797.39876157408</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>44641.78332175926</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         <v>45183.65135416666</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>45183.65233796297</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>45558.54422453704</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>45112</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>45673</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>45729.36478009259</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>45053.36554398148</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>45217.51479166667</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>44677</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>45636.4737962963</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>45798.45043981481</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>45313</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>45840.65777777778</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>45840.66978009259</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37336,7 +37336,7 @@
         <v>45840.65592592592</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37393,7 +37393,7 @@
         <v>45840.6602199074</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>45840.66780092593</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37507,7 +37507,7 @@
         <v>45716.40918981482</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>45121</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37631,7 +37631,7 @@
         <v>44834</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>45565.5381712963</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>45317</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>45408</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>44741</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>45554.28857638889</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37988,7 +37988,7 @@
         <v>45008.66204861111</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>45722.46946759259</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>45562.56372685185</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>45205.3119212963</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>45205.35753472222</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>44965</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>45684.41622685185</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>45014</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>44956.54967592593</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45583.55850694444</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45356.64724537037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>44679</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45803.4409837963</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>45803.43815972222</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38816,7 +38816,7 @@
         <v>45758.35732638889</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45804.59579861111</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>45636.45989583333</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>45758.60146990741</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>45845.45563657407</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>45845.65797453704</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45614.46292824074</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39235,7 +39235,7 @@
         <v>44279</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39292,7 +39292,7 @@
         <v>45761.59716435185</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39354,7 +39354,7 @@
         <v>44630</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>45211.52641203703</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39468,7 +39468,7 @@
         <v>45762.76337962963</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39525,7 +39525,7 @@
         <v>44719.43200231482</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>44651.42819444444</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45581.62796296296</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>44573.38521990741</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>45736.32038194445</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45414.39614583334</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>45446.57724537037</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>45446.5790625</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45645.27707175926</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45261.50924768519</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>44998</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>44512</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>44970.65930555556</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>44993</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>44980</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>45030</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>44312</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>45254.54892361111</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40571,7 +40571,7 @@
         <v>45215</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>45386.35986111111</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>45188</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>45680</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45715.5837962963</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>45807</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>45769.57802083333</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45723.66629629629</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44721</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45369</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45114</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41218,7 +41218,7 @@
         <v>44221</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45764.47553240741</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>45699.75583333334</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45178.4275</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45629.67508101852</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45629.67931712963</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>45098.37322916667</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>44805</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>45096</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45117</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45582.98494212963</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41870,7 +41870,7 @@
         <v>45204</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>45468.82832175926</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>45727.64337962963</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45769.62891203703</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>45401.46640046296</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>45597.40140046296</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>45469.43265046296</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>45726.90959490741</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44713.58678240741</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>45274</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45121</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42522,7 +42522,7 @@
         <v>45252</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>45813.56320601852</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42641,7 +42641,7 @@
         <v>45191.39708333334</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45758.56946759259</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>45254</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>45736.31737268518</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
         <v>45747.44502314815</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>45201.56556712963</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45030.61489583334</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>45030.61744212963</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43107,7 +43107,7 @@
         <v>45246.41627314815</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45246</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>44455.68550925926</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>45860</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>44956</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>45719.4522337963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43459,7 +43459,7 @@
         <v>44956</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45716.45121527778</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>45252.91344907408</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         <v>45272</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>45769.40231481481</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43764,7 +43764,7 @@
         <v>44974</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43826,7 +43826,7 @@
         <v>45817</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43883,7 +43883,7 @@
         <v>45657.94784722223</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>45817</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>44853.64244212963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         <v>45817.42607638889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44116,7 +44116,7 @@
         <v>45399.62587962963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>45817.64487268519</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>44742</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44297,7 +44297,7 @@
         <v>45317</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44359,7 +44359,7 @@
         <v>44999</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>45836</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>45817.47909722223</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44540,7 +44540,7 @@
         <v>45817.41037037037</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>45820.37113425926</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>44249</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>45110</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44773,7 +44773,7 @@
         <v>45820.39863425926</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44830,7 +44830,7 @@
         <v>44826</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44887,7 +44887,7 @@
         <v>44862</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44944,7 +44944,7 @@
         <v>45442.38490740741</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>45716.37259259259</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45063,7 +45063,7 @@
         <v>45266.66998842593</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45120,7 +45120,7 @@
         <v>44859</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45182,7 +45182,7 @@
         <v>44469</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>45824.32293981482</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45330</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45797</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45266</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45442.61221064815</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>45824.45221064815</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45596,7 +45596,7 @@
         <v>45796.44922453703</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45658,7 +45658,7 @@
         <v>44851</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45715,7 +45715,7 @@
         <v>44243</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45772,7 +45772,7 @@
         <v>45798.60880787037</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45834,7 +45834,7 @@
         <v>45106</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45891,7 +45891,7 @@
         <v>45763.41083333334</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>45008.62458333333</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>45824.31493055556</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>44980</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45702.76590277778</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45043</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46258,7 +46258,7 @@
         <v>45867.7115625</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>45013.63658564815</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46372,7 +46372,7 @@
         <v>45229</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46429,7 +46429,7 @@
         <v>45764.44263888889</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45716.57158564815</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46543,7 +46543,7 @@
         <v>44364.78170138889</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46600,7 +46600,7 @@
         <v>45715.56964120371</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46662,7 +46662,7 @@
         <v>44746</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46719,7 +46719,7 @@
         <v>44384</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>44767</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
         <v>45016.67141203704</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>44880</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>44992</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>44575</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47071,7 +47071,7 @@
         <v>44957</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47133,7 +47133,7 @@
         <v>44945.58030092593</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47190,7 +47190,7 @@
         <v>45268</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>45736.32394675926</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45093.54811342592</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>44599</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47418,7 +47418,7 @@
         <v>45832</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47475,7 +47475,7 @@
         <v>44597</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>44225</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45678.59783564815</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>44754.57658564814</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>44739.52209490741</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47765,7 +47765,7 @@
         <v>44970.44197916667</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45873</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>45832</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47941,7 +47941,7 @@
         <v>45832</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47998,7 +47998,7 @@
         <v>45833.4374537037</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>45215.63990740741</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         <v>45833.40451388889</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45106</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48231,7 +48231,7 @@
         <v>45638</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>45833.65659722222</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45053.82055555555</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48407,7 +48407,7 @@
         <v>45874</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48464,7 +48464,7 @@
         <v>44181</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>45043.49425925926</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>45671.5678125</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>44908</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>44897</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>45642</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45733.62203703704</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48888,7 +48888,7 @@
         <v>45686.61590277778</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48950,7 +48950,7 @@
         <v>44867</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>44105</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49074,7 +49074,7 @@
         <v>45442.68033564815</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49136,7 +49136,7 @@
         <v>44957</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49198,7 +49198,7 @@
         <v>45043</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49255,7 +49255,7 @@
         <v>44333</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>44861</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49374,7 +49374,7 @@
         <v>44166</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49431,7 +49431,7 @@
         <v>45008</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>44936</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49550,7 +49550,7 @@
         <v>44936</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45030</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>44177</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49726,7 +49726,7 @@
         <v>44177</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>44358</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>45174</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49902,7 +49902,7 @@
         <v>45174.87439814815</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49959,7 +49959,7 @@
         <v>44992</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50016,7 +50016,7 @@
         <v>44155</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50073,7 +50073,7 @@
         <v>45014</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50130,7 +50130,7 @@
         <v>45246.41783564815</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         <v>44218</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50249,7 +50249,7 @@
         <v>45453.55534722222</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>45022.34695601852</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50363,7 +50363,7 @@
         <v>44987.5428587963</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50420,7 +50420,7 @@
         <v>45770.84420138889</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>45090.90752314815</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50539,7 +50539,7 @@
         <v>44783</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50596,7 +50596,7 @@
         <v>45048</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50658,7 +50658,7 @@
         <v>45356.66037037037</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50715,7 +50715,7 @@
         <v>44286.88952546296</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>45043</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50829,7 +50829,7 @@
         <v>45071</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50886,7 +50886,7 @@
         <v>45699</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50943,7 +50943,7 @@
         <v>45435</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51000,7 +51000,7 @@
         <v>45547.64484953704</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51062,7 +51062,7 @@
         <v>45657.95927083334</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51124,7 +51124,7 @@
         <v>45678.47236111111</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51181,7 +51181,7 @@
         <v>45086.71662037037</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>45636.45025462963</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51300,7 +51300,7 @@
         <v>45583.34371527778</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51362,7 +51362,7 @@
         <v>45071</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51419,7 +51419,7 @@
         <v>45096</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51481,7 +51481,7 @@
         <v>45153.36402777778</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51543,7 +51543,7 @@
         <v>45117</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51605,7 +51605,7 @@
         <v>45757.66474537037</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>44980</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>45093</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>44974</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51843,7 +51843,7 @@
         <v>44980.48200231481</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>44981</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51967,7 +51967,7 @@
         <v>44966.57550925926</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52029,7 +52029,7 @@
         <v>45030.62916666667</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52086,7 +52086,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52148,7 +52148,7 @@
         <v>44977.57584490741</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>44433</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52267,7 +52267,7 @@
         <v>45721.51255787037</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52324,7 +52324,7 @@
         <v>45721.51346064815</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52381,7 +52381,7 @@
         <v>44644</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52443,7 +52443,7 @@
         <v>45012</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45012</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>45798.58304398148</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>44299</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>44264</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>45579</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>45645.27462962963</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45012</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45139</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45441</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>45568</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>45133</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44067</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>45604</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>45783.4903125</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44076</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>44578</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>45421</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>45723.61545138889</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>45742.41269675926</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>45832.36966435185</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>44412</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45042</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>45723.59275462963</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>45568</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>45723.57098379629</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45731.65016203704</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>45421</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>45764.47825231482</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45441.33914351852</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>45012</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>45013.77040509259</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>45086</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>44977</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45604</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>44931</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>45832.31648148148</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>45833.56057870371</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>45583</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>45772.6571412037</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>45758.54390046297</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44789</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>45583</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45258.56491898148</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44067</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>45568.44137731481</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>45733.45780092593</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45694</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45832.3365625</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>44454</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>45086</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>44308</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>44480</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>44426</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>44524</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>44452</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>44490</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>45742.43848379629</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>45723.66964120371</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>45744</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>45744.41443287037</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>45411.57177083333</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>45583.3479050926</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44132</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45369</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>45747.58131944444</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45348.68336805556</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>44886.54420138889</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>45770.63996527778</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>45408</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>44089</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45763.60795138889</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>45783.61222222223</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>45376</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>45362</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45201</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>45796</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>45201</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>45421</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>45251</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>45096</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45716.5672337963</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>45580</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         <v>45117</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>45723.55663194445</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>45583</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>44354</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>44777.49493055556</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>45702.76395833334</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>45174</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>45056</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>45042</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>45583</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>44151</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>44219</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>44064</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>44211</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>44211</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>44158</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>44063</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44146</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>44456</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>44456</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>44301</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>44307</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>44530</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>44582.4696875</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>44211</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>44217</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>44214</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>44176</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>44504</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>44107</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44502</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>44622</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>44537</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>44218</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>44825.47923611111</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>44728.82296296296</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>44340.80107638889</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>44279</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>44739</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>44368</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>44719.43086805556</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>44216</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>44169</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>44169</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>44370</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>44258</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>44503</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>44440</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44448</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>44306</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44368</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44441</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>44301</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>44865</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>44055</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>44294</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>44286</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44524.67836805555</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44385</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>44696.775</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44390</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>44432</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>44433</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44494</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>44447</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44368.88704861111</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>44340</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>44333</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>44671</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>44713</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>44813</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44530</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>44515</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>44571</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44169</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44442.66228009259</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44208</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>44272</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>44475</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>44475</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>44393</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>44630.3978587963</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>44371</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44371</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44124.63679398148</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44362</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44211</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44211</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44524</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>44271.81282407408</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>44447</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>44530</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>44313</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44300</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44503</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>44300</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>44459</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>44446</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>44321</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>44879.39153935185</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>44459</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44475</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>44475</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>44063</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44249</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44686</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44602</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44574</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44326</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44326</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44326</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>44363</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>44098</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15224,7 +15224,7 @@
         <v>44348</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>44726</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44886.47697916667</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>44889.55255787037</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44328</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44452</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>44152</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>44874</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>44219</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>44449</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>44162</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44825</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>44487</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>44596</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>44358</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>44468</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>44756</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>44208</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>44252</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>44441</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>44137</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>44137</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>44452</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>44432</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>44272</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>44582</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>44630</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>44825</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>44740</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>44344.49251157408</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17004,7 +17004,7 @@
         <v>44363</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>44741.57063657408</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>44313</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>44279</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>44445</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>44557</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>44302</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>44270</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>44730</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>44354.45140046296</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>44053</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>44869.4575</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>45729</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>45110</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>45274.43547453704</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45678.44092592593</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>44652</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>44362</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45733.44431712963</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45076</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>45709.4119212963</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>44067</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44096</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>45706.49520833333</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45706.54385416667</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45405</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>45772.6652662037</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>44578</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>45254</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>45077</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45048</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
         <v>45509.57052083333</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45121</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>45043</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>45268</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>45043.53597222222</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45215.63818287037</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>45183</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>44825</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>44865</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>45771.76943287037</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>45072</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44862</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>45043</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45614.52813657407</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19689,7 +19689,7 @@
         <v>45771.69168981481</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45202</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>45532</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45049.34974537037</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>45049.35048611111</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45527.41597222222</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>44939</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>45012.79270833333</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>44803.59099537037</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45678.57045138889</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45363.58979166667</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45678.58166666667</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45716.55766203703</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>44061</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>45237</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20554,7 +20554,7 @@
         <v>45769.45751157407</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>45771.66951388889</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45769.41631944444</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>45628.56513888889</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45769</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45769</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>44159.36447916667</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45736.31508101852</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45436.41305555555</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45758.60465277778</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45758.61055555556</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>44454</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>45736.72646990741</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45733.43347222222</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>45699.65944444444</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>45699.75690972222</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>44805</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44096</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45118</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>45369.62108796297</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45336</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>45741.63417824074</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>45092</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>45037</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>44860</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>44137</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45741.51940972222</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>44439.97621527778</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>44147</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45706.42958333333</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>45414.3944212963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45092.36790509259</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45090</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>45535.91413194445</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>44896</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>45373.48878472222</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>44900</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45520.52375</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>44083</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>45373.73894675926</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22909,7 +22909,7 @@
         <v>44862</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45769</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45219.32268518519</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45330</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>44860</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>45562.57070601852</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>44897</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>44928.45552083333</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>45386.32806712963</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>44923.67971064815</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44414</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>45731.59962962963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>44151.53271990741</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>45442.67793981481</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45386</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>44462</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>45723.67724537037</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>45279.66864583334</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>44907.66710648148</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>45747.59501157407</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>45027</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45373.72511574074</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24208,7 +24208,7 @@
         <v>44433</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>44935</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>45558</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>44935.60138888889</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>44588</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>45317</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>45359.68173611111</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45334</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>45478.47236111111</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>45128</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44237</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44861</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>45432.6291550926</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>45425.89037037037</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>45436.41847222222</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45118</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>44980</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>44880.44351851852</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>45317</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>44783</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>44057.35462962963</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>44977.63902777778</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>44939</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>45278</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>44858</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45678.6377199074</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>45117</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>44236</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>45153</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>44163</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>45603.49528935185</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>44936</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>45742.31784722222</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>45153</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45093</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44067</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44907.65043981482</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>45731.60166666667</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>45716.39159722222</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>45211.52895833334</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>44936</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45369.61550925926</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>45016.64986111111</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>45129</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>45457.59425925926</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26873,7 +26873,7 @@
         <v>45250.5799537037</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>44361</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>45764.43782407408</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>44488</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>45106</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>45096</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45379</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45405</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45497</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>45240</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45684.4203125</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45706.54204861111</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>45706.54572916667</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>45310</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>45644</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>45742.32277777778</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>45266</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>45490.72372685185</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>44930</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45758.56056712963</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>45709.42859953704</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>44936</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>45339.5277199074</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>45527.42443287037</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>45408.49326388889</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>45254</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>45741.53599537037</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>45629.7202662037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>45763.64096064815</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>44607</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>44322</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>44890</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>44950</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>45092.35266203704</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>45006</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>45414.5519212963</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45726.91224537037</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>45030.62740740741</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>45030</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>45777.61991898148</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>45782.66719907407</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>45782.659375</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29332,7 +29332,7 @@
         <v>44994.41405092592</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29389,7 +29389,7 @@
         <v>45783</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29446,7 +29446,7 @@
         <v>45110.56027777777</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29503,7 +29503,7 @@
         <v>45110</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>45784</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>45784.62866898148</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>44582</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>45783.68689814815</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>45783.48681712963</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>45132</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>45202.56994212963</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>45365</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>44176</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45370</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>44957</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>45670</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>44494</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>44974.564375</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>45771.44005787037</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>45442.6052199074</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30584,7 +30584,7 @@
         <v>45442.60829861111</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>45092.36126157407</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>44936</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45184</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>45178.43909722222</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>45786.36358796297</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>44084</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45671.62931712963</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>45595</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45030</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45637</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>45593.59819444444</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>44889</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45673.49019675926</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>45126</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31469,7 +31469,7 @@
         <v>45126</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>45028</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>45587.58498842592</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>44910</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>45141</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31769,7 +31769,7 @@
         <v>44181</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>45453.54733796296</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45453.55123842593</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45145</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>45400</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>45671.59245370371</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>44131</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>45403.86942129629</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         <v>45106</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>45106</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>44935.64165509259</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>44181</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>45114</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>45114</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45706.47790509259</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>45786</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>45789.42597222222</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>44565</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>45201.63637731481</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45310.41982638889</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>45527.43385416667</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>45758.36203703703</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>44427.49322916667</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>45790</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>45546</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>45356.64872685185</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45106</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>45369.61841435185</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>45566.46769675926</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>45215</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>45678.57731481481</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>44936.46326388889</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>45092.35369212963</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45336</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>45266.69091435185</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>44974.65918981482</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45792.42109953704</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>45792.42542824074</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45191</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>44168</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>45033</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>44536</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>45678.57503472222</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44596</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>45794.82583333334</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44943.56112268518</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>44573</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45794.81975694445</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>45794.82150462963</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>45579.56570601852</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>45527.40489583334</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>45794.81730324074</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>45796.49842592593</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>45796</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>45794.81583333333</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45723.65960648148</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>45174</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>45174</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35125,7 +35125,7 @@
         <v>45550.68804398148</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>45742.33188657407</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>44448</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>45794.82371527778</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35353,7 +35353,7 @@
         <v>45796</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35410,7 +35410,7 @@
         <v>45796.36326388889</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>45394</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>45259</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>45453.52299768518</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>45727.6683449074</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35710,7 +35710,7 @@
         <v>45159</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>45238.33091435185</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>45432.54622685185</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>44455</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>45838.683125</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>45043</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>45798.59671296296</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>45049</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36176,7 +36176,7 @@
         <v>44943</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>45798.66228009259</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36300,7 +36300,7 @@
         <v>45764.43002314815</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36357,7 +36357,7 @@
         <v>45091</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>45797.39876157408</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>44641.78332175926</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         <v>45183.65135416666</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>45183.65233796297</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>45558.54422453704</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>45112</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>45673</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>45729.36478009259</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>45053.36554398148</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>45217.51479166667</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>44677</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>45636.4737962963</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>45798.45043981481</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>45313</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>45840.65777777778</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>45840.66978009259</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37336,7 +37336,7 @@
         <v>45840.65592592592</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37393,7 +37393,7 @@
         <v>45840.6602199074</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>45840.66780092593</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37507,7 +37507,7 @@
         <v>45716.40918981482</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>45121</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37631,7 +37631,7 @@
         <v>44834</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>45565.5381712963</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>45317</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>45408</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>44741</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>45554.28857638889</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37988,7 +37988,7 @@
         <v>45008.66204861111</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>45722.46946759259</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>45562.56372685185</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>45205.3119212963</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>45205.35753472222</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>44965</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>45684.41622685185</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>45014</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>44956.54967592593</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45583.55850694444</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45356.64724537037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>44679</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45803.4409837963</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>45803.43815972222</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38816,7 +38816,7 @@
         <v>45758.35732638889</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45804.59579861111</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>45636.45989583333</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>45758.60146990741</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>45845.45563657407</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>45845.65797453704</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45614.46292824074</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39235,7 +39235,7 @@
         <v>44279</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39292,7 +39292,7 @@
         <v>45761.59716435185</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39354,7 +39354,7 @@
         <v>44630</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>45211.52641203703</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39468,7 +39468,7 @@
         <v>45762.76337962963</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39525,7 +39525,7 @@
         <v>44719.43200231482</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>44651.42819444444</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45581.62796296296</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>44573.38521990741</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>45736.32038194445</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45414.39614583334</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>45446.57724537037</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>45446.5790625</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45645.27707175926</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45261.50924768519</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>44998</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>44512</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>44970.65930555556</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>44993</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>44980</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>45030</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>44312</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>45254.54892361111</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40571,7 +40571,7 @@
         <v>45215</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>45386.35986111111</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>45188</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>45680</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45715.5837962963</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>45807</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>45769.57802083333</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45723.66629629629</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44721</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45369</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45114</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41218,7 +41218,7 @@
         <v>44221</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45764.47553240741</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>45699.75583333334</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45178.4275</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45629.67508101852</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45629.67931712963</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>45098.37322916667</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>44805</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>45096</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45117</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45582.98494212963</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41870,7 +41870,7 @@
         <v>45204</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>45468.82832175926</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>45727.64337962963</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45769.62891203703</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>45401.46640046296</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>45597.40140046296</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>45469.43265046296</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>45726.90959490741</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44713.58678240741</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>45274</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45121</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42522,7 +42522,7 @@
         <v>45252</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>45813.56320601852</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42641,7 +42641,7 @@
         <v>45191.39708333334</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45758.56946759259</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>45254</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>45736.31737268518</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
         <v>45747.44502314815</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>45201.56556712963</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45030.61489583334</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>45030.61744212963</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43107,7 +43107,7 @@
         <v>45246.41627314815</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45246</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>44455.68550925926</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>45860</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>44956</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>45719.4522337963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43459,7 +43459,7 @@
         <v>44956</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45716.45121527778</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>45252.91344907408</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         <v>45272</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>45769.40231481481</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43764,7 +43764,7 @@
         <v>44974</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43826,7 +43826,7 @@
         <v>45817</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43883,7 +43883,7 @@
         <v>45657.94784722223</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>45817</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>44853.64244212963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         <v>45817.42607638889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44116,7 +44116,7 @@
         <v>45399.62587962963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>45817.64487268519</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>44742</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44297,7 +44297,7 @@
         <v>45317</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44359,7 +44359,7 @@
         <v>44999</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>45836</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>45817.47909722223</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44540,7 +44540,7 @@
         <v>45817.41037037037</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>45820.37113425926</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>44249</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>45110</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44773,7 +44773,7 @@
         <v>45820.39863425926</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44830,7 +44830,7 @@
         <v>44826</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44887,7 +44887,7 @@
         <v>44862</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44944,7 +44944,7 @@
         <v>45442.38490740741</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>45716.37259259259</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45063,7 +45063,7 @@
         <v>45266.66998842593</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45120,7 +45120,7 @@
         <v>44859</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45182,7 +45182,7 @@
         <v>44469</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>45824.32293981482</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45330</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45797</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45266</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45442.61221064815</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>45824.45221064815</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45596,7 +45596,7 @@
         <v>45796.44922453703</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45658,7 +45658,7 @@
         <v>44851</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45715,7 +45715,7 @@
         <v>44243</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45772,7 +45772,7 @@
         <v>45798.60880787037</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45834,7 +45834,7 @@
         <v>45106</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45891,7 +45891,7 @@
         <v>45763.41083333334</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>45008.62458333333</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>45824.31493055556</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>44980</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45702.76590277778</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45043</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46258,7 +46258,7 @@
         <v>45867.7115625</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>45013.63658564815</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46372,7 +46372,7 @@
         <v>45229</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46429,7 +46429,7 @@
         <v>45764.44263888889</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45716.57158564815</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46543,7 +46543,7 @@
         <v>44364.78170138889</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46600,7 +46600,7 @@
         <v>45715.56964120371</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46662,7 +46662,7 @@
         <v>44746</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46719,7 +46719,7 @@
         <v>44384</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>44767</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
         <v>45016.67141203704</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>44880</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>44992</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>44575</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47071,7 +47071,7 @@
         <v>44957</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47133,7 +47133,7 @@
         <v>44945.58030092593</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47190,7 +47190,7 @@
         <v>45268</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>45736.32394675926</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45093.54811342592</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>44599</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47418,7 +47418,7 @@
         <v>45832</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47475,7 +47475,7 @@
         <v>44597</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>44225</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45678.59783564815</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>44754.57658564814</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>44739.52209490741</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47765,7 +47765,7 @@
         <v>44970.44197916667</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45873</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>45832</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47941,7 +47941,7 @@
         <v>45832</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47998,7 +47998,7 @@
         <v>45833.4374537037</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>45215.63990740741</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         <v>45833.40451388889</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45106</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48231,7 +48231,7 @@
         <v>45638</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>45833.65659722222</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45053.82055555555</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48407,7 +48407,7 @@
         <v>45874</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48464,7 +48464,7 @@
         <v>44181</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>45043.49425925926</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>45671.5678125</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>44908</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>44897</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>45642</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45733.62203703704</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48888,7 +48888,7 @@
         <v>45686.61590277778</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48950,7 +48950,7 @@
         <v>44867</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>44105</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49074,7 +49074,7 @@
         <v>45442.68033564815</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49136,7 +49136,7 @@
         <v>44957</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49198,7 +49198,7 @@
         <v>45043</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49255,7 +49255,7 @@
         <v>44333</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>44861</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49374,7 +49374,7 @@
         <v>44166</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49431,7 +49431,7 @@
         <v>45008</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>44936</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49550,7 +49550,7 @@
         <v>44936</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45030</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>44177</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49726,7 +49726,7 @@
         <v>44177</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>44358</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>45174</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49902,7 +49902,7 @@
         <v>45174.87439814815</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49959,7 +49959,7 @@
         <v>44992</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50016,7 +50016,7 @@
         <v>44155</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50073,7 +50073,7 @@
         <v>45014</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50130,7 +50130,7 @@
         <v>45246.41783564815</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         <v>44218</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50249,7 +50249,7 @@
         <v>45453.55534722222</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>45022.34695601852</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50363,7 +50363,7 @@
         <v>44987.5428587963</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50420,7 +50420,7 @@
         <v>45770.84420138889</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>45090.90752314815</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50539,7 +50539,7 @@
         <v>44783</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50596,7 +50596,7 @@
         <v>45048</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50658,7 +50658,7 @@
         <v>45356.66037037037</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50715,7 +50715,7 @@
         <v>44286.88952546296</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>45043</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50829,7 +50829,7 @@
         <v>45071</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50886,7 +50886,7 @@
         <v>45699</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50943,7 +50943,7 @@
         <v>45435</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51000,7 +51000,7 @@
         <v>45547.64484953704</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51062,7 +51062,7 @@
         <v>45657.95927083334</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51124,7 +51124,7 @@
         <v>45678.47236111111</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51181,7 +51181,7 @@
         <v>45086.71662037037</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>45636.45025462963</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51300,7 +51300,7 @@
         <v>45583.34371527778</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51362,7 +51362,7 @@
         <v>45071</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51419,7 +51419,7 @@
         <v>45096</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51481,7 +51481,7 @@
         <v>45153.36402777778</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51543,7 +51543,7 @@
         <v>45117</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51605,7 +51605,7 @@
         <v>45757.66474537037</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>44980</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>45093</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>44974</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51843,7 +51843,7 @@
         <v>44980.48200231481</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>44981</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51967,7 +51967,7 @@
         <v>44966.57550925926</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52029,7 +52029,7 @@
         <v>45030.62916666667</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52086,7 +52086,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52148,7 +52148,7 @@
         <v>44977.57584490741</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>44433</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52267,7 +52267,7 @@
         <v>45721.51255787037</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52324,7 +52324,7 @@
         <v>45721.51346064815</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52381,7 +52381,7 @@
         <v>44644</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52443,7 +52443,7 @@
         <v>45012</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45012</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45798.58304398148</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44896</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>44299</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>44264</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>45579</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>45645.27462962963</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45139</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>45012</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45441</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>45568</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>45880.62738425926</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>44067</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>45133</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>45783.4903125</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45604</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44076</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>45421</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45723.61545138889</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>45742.41269675926</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>45832.36966435185</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44578</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>44412</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>45723.59275462963</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>45723.57098379629</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>45568</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45731.65016203704</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>45421</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>45881.41636574074</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>45042</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44977</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>45604</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>45832.31648148148</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45833.56057870371</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>45884.4946875</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>44931</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45583</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>45441.33914351852</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>45012</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45764.47825231482</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>45013.77040509259</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45086</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>44789</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>44067</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>45258.56491898148</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45832.3365625</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>45568.44137731481</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>44454</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45086</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>45733.45780092593</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45694</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>45772.6571412037</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>45758.54390046297</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>45583</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>44308</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>44480</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>44426</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>44452</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>44524</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>44490</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>45723.66964120371</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>45583.3479050926</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>45369</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>45770.63996527778</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>45408</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>45763.60795138889</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>45783.61222222223</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>45376</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45362</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>45796</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45201</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>45421</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>45096</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>45716.5672337963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>44886.54420138889</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44089</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>45723.55663194445</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>45583</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>44777.49493055556</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45201</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>45251</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>45174</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>45056</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>45580</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>45042</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45117</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>45583</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>44354</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>45702.76395833334</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>45744</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>45744.41443287037</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>45742.43848379629</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>45411.57177083333</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44132</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>45348.68336805556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>45747.58131944444</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44151</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>44219</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>44064</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>44211</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>44211</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>44146</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>44158</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>44063</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>44456</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44456</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44301</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44307</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>44530</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>44582.4696875</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>44211</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>44217</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>44214</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>44176</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44107</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>44502</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>44622</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>44537</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>44218</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>44825.47923611111</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44728.82296296296</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44340.80107638889</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>44279</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44739</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>44368</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>44719.43086805556</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>44169</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44169</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         <v>44216</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44370</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>44258</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>44503</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>44440</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>44448</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>44306</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>44368</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>44441</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44301</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>44865</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>44294</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44286</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>44524.67836805555</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44385</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>44696.775</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>44390</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>44432</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44433</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>44494</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>44447</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>44368.88704861111</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>44340</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>44333</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>44671</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12769,7 +12769,7 @@
         <v>44713</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>44813</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>44530</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>44515</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>44571</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>44169</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44442.66228009259</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>44208</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>44475</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44475</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>44272</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>44393</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44630.3978587963</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>44371</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>44371</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>44124.63679398148</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>44362</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>44211</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44211</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44524</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>44271.81282407408</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>44447</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>44530</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44313</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>44300</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>44300</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44503</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>44459</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44446</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>44321</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>44459</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>44879.39153935185</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>44475</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>44475</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>44063</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>44249</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>44574</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44686</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>44602</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>44889.55255787037</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>44328</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>44452</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>44874</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>44825</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>44219</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>44162</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>44487</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>44358</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>44596</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>44468</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>44756</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>44208</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>44252</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>44441</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>44137</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>44137</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>44432</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>44452</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>44272</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>44582</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44630</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>44740</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>44825</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>44344.49251157408</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>44363</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>44741.57063657408</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>44313</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44279</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44302</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44270</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44730</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>44354.45140046296</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44445</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>44557</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44362</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>44869.4575</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>44363</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>44098</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>44348</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>44578</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
         <v>44726</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>44326</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>44326</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>44326</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>44152</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>45709.4119212963</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>45363.58979166667</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45369.61550925926</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>44067</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         <v>45405</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>44886.47697916667</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>45736.72646990741</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>45106</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>44449</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>44805</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>45742.32277777778</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45379</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45118</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>45369.62108796297</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>45336</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>45741.63417824074</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45092</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>45037</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>45240</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>45268</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>45758.56056712963</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>45043.53597222222</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>45414.3944212963</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>45215.63818287037</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>45644</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>45709.42859953704</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19341,7 +19341,7 @@
         <v>44825</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>44865</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45072</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>44862</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>45373.73894675926</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>45043</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>44862</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>45771.69168981481</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>44860</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>45629.7202662037</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>45202</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>45339.5277199074</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45532</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45763.64096064815</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45408.49326388889</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>45562.57070601852</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>45254</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45678.57045138889</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>44414</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>45741.53599537037</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>45386</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>44607</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>44322</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>45726.91224537037</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45777.61991898148</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>44950</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45092.35266203704</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45006</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>45782.66719907407</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>45030.62740740741</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>45030</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>45782.659375</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>44994.41405092592</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>45783</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45784</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>45784.62866898148</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>45110.56027777777</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>45110</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>45783.68689814815</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>45783.48681712963</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>44462</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21738,7 +21738,7 @@
         <v>45132</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>45370</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>44957</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45670</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>45092.36126157407</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>44494</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>44974.564375</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>45771.44005787037</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>45786.36358796297</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>45671.62931712963</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>44084</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22457,7 +22457,7 @@
         <v>45587.58498842592</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>45595</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>45637</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>45593.59819444444</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45673.49019675926</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45126</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45126</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>45453.54733796296</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>45453.55123842593</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>45141</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>45786</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>45789.42597222222</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>44565</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>45310.41982638889</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>45145</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>45400</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>45671.59245370371</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45790</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>45403.86942129629</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>44935.64165509259</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45114</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45114</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>45706.47790509259</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45792.42109953704</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>45792.42542824074</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45527.43385416667</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45758.36203703703</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45678.57503472222</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45546</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>45794.82583333334</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45356.64872685185</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45106</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45794.81975694445</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45794.82150462963</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>44433</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>45794.81730324074</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>45796.49842592593</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>45317</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>45092.35369212963</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>45796</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45794.81583333333</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>45336</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>45266.69091435185</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45794.82371527778</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45796</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45796.36326388889</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>45191</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45259</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44168</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>45033</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>44536</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>44596</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44573</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45798.59671296296</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45798.66228009259</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>45359.68173611111</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45797.39876157408</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45798.45043981481</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45723.65960648148</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>45565.5381712963</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45550.68804398148</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>45742.33188657407</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>45408</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>45554.28857638889</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45722.46946759259</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>45727.6683449074</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45803.4409837963</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>45803.43815972222</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45804.59579861111</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45159</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>45432.54622685185</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>45334</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45128</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>45845.45563657407</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45845.65797453704</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>45043</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>45762.76337962963</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>44861</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>45432.6291550926</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         <v>45425.89037037037</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>44641.78332175926</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>45183.65135416666</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45183.65233796297</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>44880.44351851852</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45673</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>45729.36478009259</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>45053.36554398148</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>45217.51479166667</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>45317</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>45636.4737962963</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45313</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>44939</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>45278</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>44858</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>45716.40918981482</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>45121</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45117</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>44236</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>44163</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>45093</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44067</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>45807</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>45205.3119212963</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45205.35753472222</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45684.41622685185</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>45369</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28679,7 +28679,7 @@
         <v>44679</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>44361</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>44488</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28855,7 +28855,7 @@
         <v>45096</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45758.60146990741</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>45761.59716435185</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>44630</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>45211.52641203703</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>45266</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         <v>45490.72372685185</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44930</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>44651.42819444444</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>44936</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>45736.32038194445</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>45527.42443287037</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45446.57724537037</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>45446.5790625</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>45261.50924768519</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44890</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>45813.56320601852</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>45254.54892361111</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>45215</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45414.5519212963</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>45188</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>45680</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>45715.5837962963</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45860</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>45817</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>45657.94784722223</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>45723.66629629629</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>45817</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>44582</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>45764.47553240741</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30610,7 +30610,7 @@
         <v>45699.75583333334</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         <v>45817.42607638889</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>45817.64487268519</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>45817.47909722223</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>45817.41037037037</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>45820.37113425926</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45202.56994212963</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45204</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>45468.82832175926</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>45365</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>45820.39863425926</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>45769.62891203703</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31319,7 +31319,7 @@
         <v>45401.46640046296</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>44176</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>45274</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>45824.32293981482</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31562,7 +31562,7 @@
         <v>45797</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>45824.45221064815</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>45796.44922453703</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>45798.60880787037</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>45252</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>45824.31493055556</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45191.39708333334</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>45867.7115625</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>45442.6052199074</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>45442.60829861111</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32162,7 +32162,7 @@
         <v>44936</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45178.43909722222</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>45758.56946759259</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>45254</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>45030</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>44889</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>45246.41627314815</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45246</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32633,7 +32633,7 @@
         <v>44455.68550925926</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32690,7 +32690,7 @@
         <v>45028</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>44956</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45719.4522337963</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
         <v>44956</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45716.45121527778</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44910</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>45252.91344907408</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>45272</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>45769.40231481481</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>44974</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         <v>44181</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33352,7 +33352,7 @@
         <v>45399.62587962963</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>45317</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>44131</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45106</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45106</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>44181</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45832</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>44249</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>44862</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45201.63637731481</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45716.37259259259</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>45266.66998842593</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>45873</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>44859</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34170,7 +34170,7 @@
         <v>44469</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>45832</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34284,7 +34284,7 @@
         <v>45832</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>45330</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>45833.4374537037</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>45833.40451388889</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34517,7 +34517,7 @@
         <v>45266</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>44427.49322916667</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>44851</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>44243</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>45106</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34802,7 +34802,7 @@
         <v>45763.41083333334</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>45833.65659722222</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>45043</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>45838.683125</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>45369.61841435185</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35097,7 +35097,7 @@
         <v>44384</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>44767</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45016.67141203704</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>45566.46769675926</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>45836</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>45215</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>45268</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>45736.32394675926</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>45678.57731481481</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>44599</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>44936.46326388889</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>44597</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>44225</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>44504</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>45678.59783564815</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>44754.57658564814</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>44739.52209490741</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>44974.65918981482</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>44970.44197916667</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>45840.65777777778</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36267,7 +36267,7 @@
         <v>45840.65592592592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>45840.6602199074</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>44943.56112268518</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45840.66780092593</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45215.63990740741</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>45106</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45840.66978009259</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>45638</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45579.56570601852</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>45883.58974537037</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>45883.63648148148</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>45883.69113425926</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45883.74664351852</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45527.40489583334</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45053.82055555555</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>45883.5738425926</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37199,7 +37199,7 @@
         <v>44181</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>45174</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45174</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45043.49425925926</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45874</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>44448</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>45884.45916666667</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>45881</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>45883.58756944445</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>45671.5678125</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37784,7 +37784,7 @@
         <v>44908</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         <v>45884.57759259259</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>45884.60458333333</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>45884.68263888889</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>45394</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>44897</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>45642</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>45453.52299768518</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>45733.62203703704</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>45881</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>45883.59934027777</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
         <v>45686.61590277778</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45238.33091435185</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>44455</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38622,7 +38622,7 @@
         <v>44867</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>44105</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>45049</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45442.68033564815</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>44943</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>44957</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45043</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>44333</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39103,7 +39103,7 @@
         <v>45764.43002314815</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39160,7 +39160,7 @@
         <v>45091</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>44861</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>44166</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>45008</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39398,7 +39398,7 @@
         <v>45558.54422453704</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39455,7 +39455,7 @@
         <v>45112</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44936</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>44936</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>45030</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>44177</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>44177</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39807,7 +39807,7 @@
         <v>44677</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39864,7 +39864,7 @@
         <v>44358</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>44834</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39988,7 +39988,7 @@
         <v>45317</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40050,7 +40050,7 @@
         <v>45174</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40107,7 +40107,7 @@
         <v>45174.87439814815</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40164,7 +40164,7 @@
         <v>44741</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>44992</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45008.66204861111</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>44155</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45014</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>44965</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>45014</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40568,7 +40568,7 @@
         <v>44956.54967592593</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>45583.55850694444</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>45246.41783564815</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40749,7 +40749,7 @@
         <v>45356.64724537037</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45758.35732638889</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>44218</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40925,7 +40925,7 @@
         <v>45636.45989583333</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45453.55534722222</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45022.34695601852</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41096,7 +41096,7 @@
         <v>45614.46292824074</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>44987.5428587963</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>44279</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>44719.43200231482</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45581.62796296296</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41386,7 +41386,7 @@
         <v>44573.38521990741</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>45770.84420138889</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>45090.90752314815</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45414.39614583334</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>44783</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45645.27707175926</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45048</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>44998</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>44512</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>44970.65930555556</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>44993</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42033,7 +42033,7 @@
         <v>44980</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>45030</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>45356.66037037037</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         <v>44312</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42271,7 +42271,7 @@
         <v>44286.88952546296</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42328,7 +42328,7 @@
         <v>45043</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42385,7 +42385,7 @@
         <v>45386.35986111111</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>45071</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>45769.57802083333</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>44721</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>45114</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>44221</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>45699</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>45178.4275</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
         <v>45435</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42908,7 +42908,7 @@
         <v>45547.64484953704</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>45657.95927083334</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45678.47236111111</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>45086.71662037037</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45636.45025462963</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45629.67508101852</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>45629.67931712963</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43322,7 +43322,7 @@
         <v>45583.34371527778</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>45098.37322916667</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>44805</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>45096</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45117</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45582.98494212963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45727.64337962963</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>45071</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43808,7 +43808,7 @@
         <v>45597.40140046296</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43865,7 +43865,7 @@
         <v>45469.43265046296</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45096</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>45726.90959490741</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>44713.58678240741</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45121</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>45736.31737268518</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>45747.44502314815</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>45201.56556712963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45030.61489583334</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45030.61744212963</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45153.36402777778</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45117</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>45757.66474537037</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>44980</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44688,7 +44688,7 @@
         <v>44853.64244212963</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45093</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44802,7 +44802,7 @@
         <v>44974</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>44980.48200231481</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>44981</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44988,7 +44988,7 @@
         <v>44966.57550925926</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>45030.62916666667</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>44742</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>44999</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45110</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>44977.57584490741</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>44826</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45469,7 +45469,7 @@
         <v>45442.38490740741</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45526,7 +45526,7 @@
         <v>44433</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45583,7 +45583,7 @@
         <v>45721.51255787037</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         <v>45721.51346064815</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45697,7 +45697,7 @@
         <v>45442.61221064815</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>44644</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>45012</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45878,7 +45878,7 @@
         <v>45008.62458333333</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45940,7 +45940,7 @@
         <v>44980</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46002,7 +46002,7 @@
         <v>45702.76590277778</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>44652</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>45013.63658564815</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>45076</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45229</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45706.49520833333</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45706.54385416667</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45764.44263888889</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45716.57158564815</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45048</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45121</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>44364.78170138889</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>45715.56964120371</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>44746</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46815,7 +46815,7 @@
         <v>44880</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46872,7 +46872,7 @@
         <v>44992</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46929,7 +46929,7 @@
         <v>44575</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46986,7 +46986,7 @@
         <v>44957</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>44945.58030092593</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45093.54811342592</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>45729</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
         <v>45110</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>45274.43547453704</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45678.44092592593</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>44803.59099537037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47457,7 +47457,7 @@
         <v>45733.44431712963</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>45678.58166666667</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45716.55766203703</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>44061</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47710,7 +47710,7 @@
         <v>45771.66951388889</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>45769.41631944444</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>44096</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47891,7 +47891,7 @@
         <v>45628.56513888889</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>45772.6652662037</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>44159.36447916667</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48072,7 +48072,7 @@
         <v>45436.41305555555</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45254</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48196,7 +48196,7 @@
         <v>45758.60465277778</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48253,7 +48253,7 @@
         <v>45758.61055555556</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>45077</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>45509.57052083333</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45699.65944444444</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45699.75690972222</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45043</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>45183</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>45771.76943287037</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>45614.52813657407</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45092.36790509259</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45535.91413194445</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45049.34974537037</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45049.35048611111</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45527.41597222222</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>44939</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45012.79270833333</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45373.48878472222</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45237</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45769.45751157407</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>45769</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45769</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>45736.31508101852</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>44454</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49589,7 +49589,7 @@
         <v>45219.32268518519</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49646,7 +49646,7 @@
         <v>45330</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45733.43347222222</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45386.32806712963</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>44096</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49884,7 +49884,7 @@
         <v>45442.67793981481</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49946,7 +49946,7 @@
         <v>44860</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50003,7 +50003,7 @@
         <v>44137</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50060,7 +50060,7 @@
         <v>45741.51940972222</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50122,7 +50122,7 @@
         <v>45723.67724537037</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         <v>44439.97621527778</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>44147</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>45706.42958333333</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50355,7 +50355,7 @@
         <v>45090</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>44896</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>45747.59501157407</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>45027</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45373.72511574074</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>44935</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>45558</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>44935.60138888889</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50831,7 +50831,7 @@
         <v>44900</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50893,7 +50893,7 @@
         <v>45520.52375</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50950,7 +50950,7 @@
         <v>44083</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51007,7 +51007,7 @@
         <v>45478.47236111111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45769</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45118</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>44980</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51245,7 +51245,7 @@
         <v>44897</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51307,7 +51307,7 @@
         <v>44928.45552083333</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51369,7 +51369,7 @@
         <v>44923.67971064815</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45731.59962962963</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51488,7 +51488,7 @@
         <v>44151.53271990741</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>44977.63902777778</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45678.6377199074</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45153</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51726,7 +51726,7 @@
         <v>45603.49528935185</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51783,7 +51783,7 @@
         <v>44936</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51840,7 +51840,7 @@
         <v>45742.31784722222</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51897,7 +51897,7 @@
         <v>45153</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51959,7 +51959,7 @@
         <v>45279.66864583334</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52021,7 +52021,7 @@
         <v>44907.66710648148</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52078,7 +52078,7 @@
         <v>44588</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52135,7 +52135,7 @@
         <v>44237</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>44907.65043981482</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52254,7 +52254,7 @@
         <v>45211.52895833334</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52311,7 +52311,7 @@
         <v>44936</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52368,7 +52368,7 @@
         <v>45436.41847222222</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52430,7 +52430,7 @@
         <v>45016.64986111111</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52492,7 +52492,7 @@
         <v>45129</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52549,7 +52549,7 @@
         <v>44783</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52606,7 +52606,7 @@
         <v>45457.59425925926</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52663,7 +52663,7 @@
         <v>45250.5799537037</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52720,7 +52720,7 @@
         <v>45764.43782407408</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52777,7 +52777,7 @@
         <v>45405</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52834,7 +52834,7 @@
         <v>45731.60166666667</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52891,7 +52891,7 @@
         <v>45716.39159722222</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52948,7 +52948,7 @@
         <v>45497</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53005,7 +53005,7 @@
         <v>45684.4203125</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53067,7 +53067,7 @@
         <v>45706.54204861111</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53124,7 +53124,7 @@
         <v>45706.54572916667</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>45310</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45012</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45798.58304398148</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44896</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>44299</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>44264</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>45579</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>45645.27462962963</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45139</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>45012</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45441</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>45568</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>45880.62738425926</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>44067</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>45133</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>45783.4903125</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45604</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44076</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>45421</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45723.61545138889</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>45742.41269675926</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>45832.36966435185</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44578</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>44412</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>45723.59275462963</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>45723.57098379629</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>45568</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45731.65016203704</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>45421</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>45881.41636574074</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>45042</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44977</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>45604</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>45832.31648148148</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45833.56057870371</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>45884.4946875</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>44931</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45583</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>45441.33914351852</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>45012</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45764.47825231482</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>45013.77040509259</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45086</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>44789</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>44067</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>45258.56491898148</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45832.3365625</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>45568.44137731481</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>44454</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45086</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>45733.45780092593</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45694</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>45772.6571412037</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>45758.54390046297</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>45583</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>44308</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>44480</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>44426</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>44452</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>44524</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>44490</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>45723.66964120371</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>45583.3479050926</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>45369</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>45770.63996527778</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>45408</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>45763.60795138889</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>45783.61222222223</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>45376</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45362</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>45796</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45201</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>45421</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>45096</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>45716.5672337963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>44886.54420138889</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44089</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>45723.55663194445</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>45583</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>44777.49493055556</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45201</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>45251</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>45174</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>45056</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>45580</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>45042</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45117</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>45583</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>44354</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>45702.76395833334</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>45744</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>45744.41443287037</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>45742.43848379629</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>45411.57177083333</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44132</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>45348.68336805556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>45747.58131944444</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44151</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>44219</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>44064</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>44211</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>44211</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>44146</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>44158</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>44063</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>44456</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44456</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44301</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44307</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>44530</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>44582.4696875</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>44211</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>44217</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>44214</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>44176</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44107</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>44502</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>44622</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>44537</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>44218</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>44825.47923611111</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44728.82296296296</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44340.80107638889</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>44279</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44739</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>44368</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>44719.43086805556</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>44169</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44169</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         <v>44216</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44370</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>44258</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>44503</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>44440</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>44448</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>44306</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>44368</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>44441</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44301</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>44865</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>44294</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44286</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>44524.67836805555</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44385</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>44696.775</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>44390</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>44432</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44433</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>44494</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>44447</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>44368.88704861111</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>44340</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>44333</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>44671</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12769,7 +12769,7 @@
         <v>44713</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>44813</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>44530</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>44515</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>44571</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>44169</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44442.66228009259</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>44208</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>44475</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44475</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>44272</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>44393</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44630.3978587963</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>44371</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>44371</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>44124.63679398148</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>44362</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>44211</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44211</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44524</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>44271.81282407408</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>44447</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>44530</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44313</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>44300</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>44300</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44503</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>44459</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44446</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>44321</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>44459</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>44879.39153935185</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>44475</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>44475</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>44063</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>44249</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>44574</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44686</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>44602</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>44889.55255787037</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>44328</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>44452</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>44874</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>44825</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>44219</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>44162</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>44487</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>44358</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>44596</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>44468</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>44756</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>44208</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>44252</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>44441</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>44137</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>44137</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>44432</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>44452</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>44272</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>44582</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44630</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>44740</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>44825</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>44344.49251157408</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>44363</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>44741.57063657408</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>44313</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44279</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44302</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44270</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44730</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>44354.45140046296</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44445</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>44557</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44362</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>44869.4575</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>44363</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>44098</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>44348</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>44578</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
         <v>44726</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>44326</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>44326</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>44326</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>44152</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>45709.4119212963</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>45363.58979166667</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45369.61550925926</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>44067</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         <v>45405</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>44886.47697916667</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>45736.72646990741</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>45106</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>44449</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>44805</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>45742.32277777778</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45379</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45118</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>45369.62108796297</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>45336</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>45741.63417824074</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45092</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>45037</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>45240</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>45268</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>45758.56056712963</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>45043.53597222222</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>45414.3944212963</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>45215.63818287037</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>45644</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>45709.42859953704</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19341,7 +19341,7 @@
         <v>44825</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>44865</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45072</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>44862</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>45373.73894675926</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>45043</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>44862</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>45771.69168981481</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>44860</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>45629.7202662037</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>45202</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>45339.5277199074</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45532</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45763.64096064815</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45408.49326388889</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>45562.57070601852</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>45254</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45678.57045138889</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>44414</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>45741.53599537037</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>45386</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>44607</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>44322</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>45726.91224537037</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45777.61991898148</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>44950</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45092.35266203704</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45006</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>45782.66719907407</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>45030.62740740741</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>45030</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>45782.659375</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>44994.41405092592</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>45783</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45784</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>45784.62866898148</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>45110.56027777777</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>45110</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>45783.68689814815</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>45783.48681712963</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>44462</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21738,7 +21738,7 @@
         <v>45132</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>45370</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>44957</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45670</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>45092.36126157407</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>44494</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>44974.564375</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>45771.44005787037</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>45786.36358796297</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>45671.62931712963</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>44084</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22457,7 +22457,7 @@
         <v>45587.58498842592</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>45595</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>45637</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>45593.59819444444</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45673.49019675926</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45126</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45126</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>45453.54733796296</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>45453.55123842593</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>45141</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>45786</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>45789.42597222222</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>44565</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>45310.41982638889</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>45145</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>45400</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>45671.59245370371</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45790</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>45403.86942129629</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>44935.64165509259</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45114</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45114</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>45706.47790509259</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45792.42109953704</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>45792.42542824074</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45527.43385416667</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45758.36203703703</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45678.57503472222</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45546</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>45794.82583333334</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45356.64872685185</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45106</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45794.81975694445</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45794.82150462963</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>44433</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>45794.81730324074</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>45796.49842592593</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>45317</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>45092.35369212963</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>45796</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45794.81583333333</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>45336</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>45266.69091435185</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45794.82371527778</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45796</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45796.36326388889</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>45191</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45259</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44168</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>45033</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>44536</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>44596</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44573</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45798.59671296296</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45798.66228009259</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>45359.68173611111</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45797.39876157408</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45798.45043981481</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45723.65960648148</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>45565.5381712963</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45550.68804398148</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>45742.33188657407</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>45408</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>45554.28857638889</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45722.46946759259</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>45727.6683449074</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45803.4409837963</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>45803.43815972222</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45804.59579861111</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45159</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>45432.54622685185</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>45334</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45128</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>45845.45563657407</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45845.65797453704</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>45043</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>45762.76337962963</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>44861</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>45432.6291550926</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         <v>45425.89037037037</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>44641.78332175926</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>45183.65135416666</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45183.65233796297</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>44880.44351851852</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45673</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>45729.36478009259</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>45053.36554398148</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>45217.51479166667</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>45317</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>45636.4737962963</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45313</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>44939</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>45278</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>44858</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>45716.40918981482</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>45121</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45117</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>44236</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>44163</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>45093</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44067</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>45807</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>45205.3119212963</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45205.35753472222</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45684.41622685185</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>45369</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28679,7 +28679,7 @@
         <v>44679</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>44361</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>44488</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28855,7 +28855,7 @@
         <v>45096</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45758.60146990741</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>45761.59716435185</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>44630</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>45211.52641203703</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>45266</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         <v>45490.72372685185</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44930</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>44651.42819444444</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>44936</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>45736.32038194445</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>45527.42443287037</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45446.57724537037</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>45446.5790625</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>45261.50924768519</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44890</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>45813.56320601852</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>45254.54892361111</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>45215</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45414.5519212963</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>45188</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>45680</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>45715.5837962963</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45860</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>45817</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>45657.94784722223</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>45723.66629629629</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>45817</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>44582</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>45764.47553240741</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30610,7 +30610,7 @@
         <v>45699.75583333334</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         <v>45817.42607638889</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>45817.64487268519</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>45817.47909722223</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>45817.41037037037</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>45820.37113425926</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45202.56994212963</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45204</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>45468.82832175926</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>45365</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>45820.39863425926</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>45769.62891203703</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31319,7 +31319,7 @@
         <v>45401.46640046296</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>44176</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>45274</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>45824.32293981482</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31562,7 +31562,7 @@
         <v>45797</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>45824.45221064815</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>45796.44922453703</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>45798.60880787037</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>45252</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>45824.31493055556</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45191.39708333334</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>45867.7115625</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>45442.6052199074</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>45442.60829861111</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32162,7 +32162,7 @@
         <v>44936</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45178.43909722222</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>45758.56946759259</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>45254</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>45030</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>44889</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>45246.41627314815</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45246</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32633,7 +32633,7 @@
         <v>44455.68550925926</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32690,7 +32690,7 @@
         <v>45028</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>44956</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45719.4522337963</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
         <v>44956</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45716.45121527778</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44910</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>45252.91344907408</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>45272</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>45769.40231481481</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>44974</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         <v>44181</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33352,7 +33352,7 @@
         <v>45399.62587962963</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>45317</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>44131</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45106</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45106</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>44181</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45832</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>44249</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>44862</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45201.63637731481</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45716.37259259259</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>45266.66998842593</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>45873</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>44859</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34170,7 +34170,7 @@
         <v>44469</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>45832</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34284,7 +34284,7 @@
         <v>45832</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>45330</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>45833.4374537037</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>45833.40451388889</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34517,7 +34517,7 @@
         <v>45266</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>44427.49322916667</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>44851</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>44243</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>45106</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34802,7 +34802,7 @@
         <v>45763.41083333334</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>45833.65659722222</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>45043</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>45838.683125</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>45369.61841435185</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35097,7 +35097,7 @@
         <v>44384</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>44767</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45016.67141203704</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>45566.46769675926</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>45836</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>45215</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>45268</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>45736.32394675926</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>45678.57731481481</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>44599</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>44936.46326388889</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>44597</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>44225</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>44504</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>45678.59783564815</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>44754.57658564814</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>44739.52209490741</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>44974.65918981482</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>44970.44197916667</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>45840.65777777778</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36267,7 +36267,7 @@
         <v>45840.65592592592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>45840.6602199074</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>44943.56112268518</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45840.66780092593</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45215.63990740741</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>45106</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45840.66978009259</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>45638</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45579.56570601852</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>45883.58974537037</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>45883.63648148148</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>45883.69113425926</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45883.74664351852</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45527.40489583334</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45053.82055555555</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>45883.5738425926</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37199,7 +37199,7 @@
         <v>44181</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>45174</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45174</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45043.49425925926</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45874</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>44448</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>45884.45916666667</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>45881</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>45883.58756944445</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>45671.5678125</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37784,7 +37784,7 @@
         <v>44908</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         <v>45884.57759259259</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>45884.60458333333</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>45884.68263888889</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>45394</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>44897</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>45642</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>45453.52299768518</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>45733.62203703704</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>45881</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>45883.59934027777</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
         <v>45686.61590277778</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45238.33091435185</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>44455</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38622,7 +38622,7 @@
         <v>44867</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>44105</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>45049</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45442.68033564815</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>44943</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>44957</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45043</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>44333</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39103,7 +39103,7 @@
         <v>45764.43002314815</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39160,7 +39160,7 @@
         <v>45091</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>44861</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>44166</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>45008</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39398,7 +39398,7 @@
         <v>45558.54422453704</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39455,7 +39455,7 @@
         <v>45112</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44936</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>44936</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>45030</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>44177</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>44177</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39807,7 +39807,7 @@
         <v>44677</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39864,7 +39864,7 @@
         <v>44358</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>44834</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39988,7 +39988,7 @@
         <v>45317</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40050,7 +40050,7 @@
         <v>45174</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40107,7 +40107,7 @@
         <v>45174.87439814815</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40164,7 +40164,7 @@
         <v>44741</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>44992</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45008.66204861111</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>44155</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45014</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>44965</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>45014</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40568,7 +40568,7 @@
         <v>44956.54967592593</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>45583.55850694444</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>45246.41783564815</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40749,7 +40749,7 @@
         <v>45356.64724537037</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45758.35732638889</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>44218</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40925,7 +40925,7 @@
         <v>45636.45989583333</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45453.55534722222</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45022.34695601852</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41096,7 +41096,7 @@
         <v>45614.46292824074</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>44987.5428587963</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>44279</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>44719.43200231482</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45581.62796296296</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41386,7 +41386,7 @@
         <v>44573.38521990741</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>45770.84420138889</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>45090.90752314815</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45414.39614583334</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>44783</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45645.27707175926</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45048</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>44998</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>44512</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>44970.65930555556</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>44993</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42033,7 +42033,7 @@
         <v>44980</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>45030</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>45356.66037037037</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         <v>44312</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42271,7 +42271,7 @@
         <v>44286.88952546296</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42328,7 +42328,7 @@
         <v>45043</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42385,7 +42385,7 @@
         <v>45386.35986111111</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>45071</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>45769.57802083333</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>44721</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>45114</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>44221</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>45699</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>45178.4275</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
         <v>45435</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42908,7 +42908,7 @@
         <v>45547.64484953704</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>45657.95927083334</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45678.47236111111</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>45086.71662037037</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45636.45025462963</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45629.67508101852</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>45629.67931712963</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43322,7 +43322,7 @@
         <v>45583.34371527778</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>45098.37322916667</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>44805</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>45096</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45117</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45582.98494212963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45727.64337962963</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>45071</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43808,7 +43808,7 @@
         <v>45597.40140046296</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43865,7 +43865,7 @@
         <v>45469.43265046296</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45096</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>45726.90959490741</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>44713.58678240741</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45121</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>45736.31737268518</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>45747.44502314815</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>45201.56556712963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45030.61489583334</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45030.61744212963</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45153.36402777778</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45117</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>45757.66474537037</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>44980</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44688,7 +44688,7 @@
         <v>44853.64244212963</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45093</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44802,7 +44802,7 @@
         <v>44974</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>44980.48200231481</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>44981</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44988,7 +44988,7 @@
         <v>44966.57550925926</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>45030.62916666667</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>44742</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>44999</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45110</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>44977.57584490741</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>44826</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45469,7 +45469,7 @@
         <v>45442.38490740741</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45526,7 +45526,7 @@
         <v>44433</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45583,7 +45583,7 @@
         <v>45721.51255787037</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         <v>45721.51346064815</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45697,7 +45697,7 @@
         <v>45442.61221064815</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>44644</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>45012</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45878,7 +45878,7 @@
         <v>45008.62458333333</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45940,7 +45940,7 @@
         <v>44980</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46002,7 +46002,7 @@
         <v>45702.76590277778</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>44652</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>45013.63658564815</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>45076</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45229</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45706.49520833333</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45706.54385416667</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45764.44263888889</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45716.57158564815</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45048</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45121</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>44364.78170138889</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>45715.56964120371</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>44746</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46815,7 +46815,7 @@
         <v>44880</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46872,7 +46872,7 @@
         <v>44992</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46929,7 +46929,7 @@
         <v>44575</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46986,7 +46986,7 @@
         <v>44957</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>44945.58030092593</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45093.54811342592</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>45729</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
         <v>45110</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>45274.43547453704</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45678.44092592593</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>44803.59099537037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47457,7 +47457,7 @@
         <v>45733.44431712963</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>45678.58166666667</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45716.55766203703</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>44061</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47710,7 +47710,7 @@
         <v>45771.66951388889</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>45769.41631944444</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>44096</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47891,7 +47891,7 @@
         <v>45628.56513888889</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>45772.6652662037</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>44159.36447916667</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48072,7 +48072,7 @@
         <v>45436.41305555555</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45254</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48196,7 +48196,7 @@
         <v>45758.60465277778</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48253,7 +48253,7 @@
         <v>45758.61055555556</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>45077</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>45509.57052083333</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45699.65944444444</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45699.75690972222</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45043</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>45183</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>45771.76943287037</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>45614.52813657407</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45092.36790509259</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45535.91413194445</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45049.34974537037</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45049.35048611111</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45527.41597222222</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>44939</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45012.79270833333</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45373.48878472222</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45237</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45769.45751157407</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>45769</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45769</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>45736.31508101852</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>44454</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49589,7 +49589,7 @@
         <v>45219.32268518519</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49646,7 +49646,7 @@
         <v>45330</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45733.43347222222</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45386.32806712963</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>44096</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49884,7 +49884,7 @@
         <v>45442.67793981481</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49946,7 +49946,7 @@
         <v>44860</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50003,7 +50003,7 @@
         <v>44137</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50060,7 +50060,7 @@
         <v>45741.51940972222</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50122,7 +50122,7 @@
         <v>45723.67724537037</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         <v>44439.97621527778</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>44147</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>45706.42958333333</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50355,7 +50355,7 @@
         <v>45090</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>44896</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>45747.59501157407</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>45027</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45373.72511574074</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>44935</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>45558</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>44935.60138888889</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50831,7 +50831,7 @@
         <v>44900</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50893,7 +50893,7 @@
         <v>45520.52375</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50950,7 +50950,7 @@
         <v>44083</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51007,7 +51007,7 @@
         <v>45478.47236111111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45769</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45118</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>44980</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51245,7 +51245,7 @@
         <v>44897</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51307,7 +51307,7 @@
         <v>44928.45552083333</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51369,7 +51369,7 @@
         <v>44923.67971064815</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45731.59962962963</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51488,7 +51488,7 @@
         <v>44151.53271990741</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>44977.63902777778</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45678.6377199074</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45153</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51726,7 +51726,7 @@
         <v>45603.49528935185</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51783,7 +51783,7 @@
         <v>44936</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51840,7 +51840,7 @@
         <v>45742.31784722222</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51897,7 +51897,7 @@
         <v>45153</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51959,7 +51959,7 @@
         <v>45279.66864583334</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52021,7 +52021,7 @@
         <v>44907.66710648148</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52078,7 +52078,7 @@
         <v>44588</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52135,7 +52135,7 @@
         <v>44237</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>44907.65043981482</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52254,7 +52254,7 @@
         <v>45211.52895833334</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52311,7 +52311,7 @@
         <v>44936</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52368,7 +52368,7 @@
         <v>45436.41847222222</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52430,7 +52430,7 @@
         <v>45016.64986111111</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52492,7 +52492,7 @@
         <v>45129</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52549,7 +52549,7 @@
         <v>44783</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52606,7 +52606,7 @@
         <v>45457.59425925926</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52663,7 +52663,7 @@
         <v>45250.5799537037</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52720,7 +52720,7 @@
         <v>45764.43782407408</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52777,7 +52777,7 @@
         <v>45405</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52834,7 +52834,7 @@
         <v>45731.60166666667</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52891,7 +52891,7 @@
         <v>45716.39159722222</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52948,7 +52948,7 @@
         <v>45497</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53005,7 +53005,7 @@
         <v>45684.4203125</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53067,7 +53067,7 @@
         <v>45706.54204861111</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53124,7 +53124,7 @@
         <v>45706.54572916667</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>45310</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45012</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>45798.58304398148</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>44299</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>44264</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>45579</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>45645.27462962963</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45012</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45139</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45441</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>45880.62738425926</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>45568</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>45886.64045138889</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>44067</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45133</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>45604</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>45783.4903125</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>44076</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>45421</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>44578</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>45723.61545138889</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>45742.41269675926</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>45832.36966435185</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44412</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>45568</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>45042</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>45723.59275462963</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>45421</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>45731.65016203704</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45723.57098379629</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45881.41636574074</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>45441.33914351852</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>45604</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>45583</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>45086</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>45012</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45764.47825231482</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>45013.77040509259</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>44977</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45832.31648148148</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45833.56057870371</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>45884.4946875</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>44931</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>45758.54390046297</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>45733.45780092593</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>45694</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>44454</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>45772.6571412037</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>45568.44137731481</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>45583</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>45258.56491898148</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>45832.3365625</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>44789</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>44067</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>45086</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>44308</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>44480</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>44426</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>44524</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>44452</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>44490</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>45042</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>45421</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45251</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44354</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44089</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45580</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>45362</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>45723.66964120371</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>45747.58131944444</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>44777.49493055556</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>45348.68336805556</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>45117</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>45763.60795138889</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>45783.61222222223</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>45583</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>45702.76395833334</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>45583.3479050926</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>45770.63996527778</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45201</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>45174</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44886.54420138889</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>45796</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>45742.43848379629</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>45744</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>45096</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>45744.41443287037</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>45056</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>45723.55663194445</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>45583</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>45201</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>44132</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>45408</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>45716.5672337963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>45369</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>45376</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>45411.57177083333</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>44151</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>44219</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>44211</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>44211</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>44146</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>44158</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>44456</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>44456</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>44301</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>44307</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>44530</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>44582.4696875</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>44211</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>44217</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>44214</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>44176</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>44502</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>44107</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>44622</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>44537</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>44218</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>44825.47923611111</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>44340.80107638889</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>44728.82296296296</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>44739</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44279</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>44368</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>44719.43086805556</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>44169</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>44169</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>44216</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>44258</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>44503</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44448</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>44306</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>44440</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>44368</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>44441</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         <v>44301</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>44865</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>44294</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>44286</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44524.67836805555</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>44385</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         <v>44696.775</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12166,7 +12166,7 @@
         <v>44390</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>44432</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>44433</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>44494</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>44447</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>44368.88704861111</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>44340</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         <v>44333</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>44370</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>44671</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>44713</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>44813</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>44530</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>44515</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         <v>44571</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>44169</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>44442.66228009259</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>44208</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>44475</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>44475</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>44393</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>44272</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>44630.3978587963</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>44371</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>44371</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>44124.63679398148</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>44362</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>44211</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>44211</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13884,7 +13884,7 @@
         <v>44524</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>44271.81282407408</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>44447</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>44530</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>44313</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>44300</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>44300</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>44503</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>44459</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>44446</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>44321</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>44879.39153935185</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>44459</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>44475</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>44475</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>44249</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>44574</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>44326</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14945,7 +14945,7 @@
         <v>44686</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>44326</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>44326</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>44602</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>44363</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>44098</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>44348</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>44726</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>44152</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>44889.55255787037</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>44328</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>44886.47697916667</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>44452</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>44874</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>44219</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>44162</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>44825</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>44449</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>44487</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>44596</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>44358</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>44468</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>44756</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>44208</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>44252</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>44441</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>44452</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>44272</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>44432</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>44137</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>44137</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>44630</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>44740</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>44344.49251157408</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>44582</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>44363</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
         <v>44279</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>44313</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>44825</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>44445</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>44270</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>44557</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44741.57063657408</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>44869.4575</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>44302</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45736.31508101852</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45769</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45266.69091435185</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>44730</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45435</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>44354.45140046296</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>44977.57584490741</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>44279</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>44862</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>45595</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>45090</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>45706.42958333333</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>44322</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45678.47236111111</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18433,7 +18433,7 @@
         <v>45709.42859953704</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>45614.52813657407</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>45401.46640046296</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>44651.42819444444</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>44362</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>45719.4522337963</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>44147</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>45114</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45106</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>44630</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>45008.62458333333</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>45250.5799537037</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>44286.88952546296</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>44957</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>44573.38521990741</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>44578</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>44249</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>45405</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44783</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>45110</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>45261.50924768519</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>44826</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>45721.51255787037</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>45721.51346064815</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>44713.58678240741</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19898,7 +19898,7 @@
         <v>45758.36203703703</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19955,7 +19955,7 @@
         <v>44083</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>44977.63902777778</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>45336</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44880</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45644</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>45469.43265046296</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>44719.43200231482</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>44900</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>45012.79270833333</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44181</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45016.67141203704</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>45112</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>45043</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>45118</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>45670</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>45671.5678125</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>45310</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45706.47790509259</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>44739.52209490741</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45761.59716435185</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>44364.78170138889</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>45086.71662037037</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>45153</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45490.72372685185</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>45769.40231481481</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>44512</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>44433</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>45716.45121527778</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45370</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>44805</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>44783</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>44746</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>44907.65043981482</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45657.95927083334</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>45191</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>45117</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45076</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>45386.32806712963</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45121</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45579.56570601852</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45733.43347222222</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45733.44431712963</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>45706.49520833333</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>45706.54385416667</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>45716.39159722222</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>45699.75690972222</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44155</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45317</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22836,7 +22836,7 @@
         <v>44168</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>45432.54622685185</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>45520.52375</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>44935.64165509259</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>45093</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>45715.5837962963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>44957</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23250,7 +23250,7 @@
         <v>45053.36554398148</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>45394</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>44767</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45726.90959490741</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45723.67724537037</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>45030.61489583334</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>45030.61744212963</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45769.41631944444</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>45072</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23778,7 +23778,7 @@
         <v>45254</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>44974</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44455</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45642</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>45106</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>44861</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44853.64244212963</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>45110</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>44897</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>45629.67508101852</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45629.67931712963</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>44151.53271990741</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>45356.66037037037</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>44181</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>45205.3119212963</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45727.6683449074</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>44067</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>44851</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>45090.90752314815</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>45729.36478009259</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45129</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45758.56056712963</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>44936.46326388889</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>44998</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>45266</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>45741.53599537037</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>45478.47236111111</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44462</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>45092.35266203704</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45764.47553240741</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44974.65918981482</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45636.45989583333</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>45313</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>44957</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45205.35753472222</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45238.33091435185</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>45403.86942129629</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>44741</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>45446.57724537037</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>45446.5790625</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45077</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>45092</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>44159.36447916667</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26361,7 +26361,7 @@
         <v>45278</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>45566.46769675926</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>45742.31784722222</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>45030</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>45399.62587962963</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>45716.55766203703</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>44105</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>45547.64484953704</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>45159</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>45121</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>45699</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45699.75583333334</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>44910</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45442.67793981481</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>45008.66204861111</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>44928.45552083333</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45033</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45637</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>45593.59819444444</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>45037</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>45117</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>45583.55850694444</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>45373.73894675926</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45030</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45048</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>45583.34371527778</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45777.61991898148</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>45726.91224537037</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>45527.40489583334</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45386.35986111111</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>45678.57731481481</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>45022.34695601852</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>45043.53597222222</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>45014</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>45527.41597222222</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>45783</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>44970.44197916667</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>44181</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45783.68689814815</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>44862</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>45783.48681712963</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>44096</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>45782.659375</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45782.66719907407</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>45254.54892361111</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>45266</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>45049.34974537037</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45049.35048611111</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>45266.66998842593</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>45432.6291550926</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45671.62931712963</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45237</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29410,7 +29410,7 @@
         <v>45784</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>45535.91413194445</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>44974.564375</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>44137</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>44965</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>45784.62866898148</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45702.76590277778</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>44067</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>45747.59501157407</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29943,7 +29943,7 @@
         <v>45786</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>45786.36358796297</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>45356.64724537037</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>44834</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>44980</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>44956</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>45764.43002314815</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>45789.42597222222</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>44966.57550925926</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>44652</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>45587.58498842592</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>44565</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         <v>45092.36126157407</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>44596</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>44936</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30843,7 +30843,7 @@
         <v>45246.41783564815</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30900,7 +30900,7 @@
         <v>45772.6652662037</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>44575</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45414.5519212963</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>45453.54733796296</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>45453.55123842593</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>45310.41982638889</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>45771.44005787037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>45546</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>45229</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>45272</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45030.62740740741</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>45030</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>45188</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>45790</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31718,7 +31718,7 @@
         <v>45603.49528935185</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>45400</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>45274</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>45268</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31951,7 +31951,7 @@
         <v>44754.57658564814</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32008,7 +32008,7 @@
         <v>45550.68804398148</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32065,7 +32065,7 @@
         <v>45792.42109953704</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32122,7 +32122,7 @@
         <v>45771.69168981481</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32179,7 +32179,7 @@
         <v>45792.42542824074</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>45259</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>44439.97621527778</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>45794.82150462963</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>45174</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>45174.87439814815</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>45053.82055555555</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45796</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>45796.36326388889</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>44860</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45678.57503472222</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45796</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>44597</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>45014</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>44936</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>45731.60166666667</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>45794.81583333333</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>45797.39876157408</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>45796.49842592593</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>45363.58979166667</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>45794.81730324074</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>45794.82583333334</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>45628.56513888889</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>45723.65960648148</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>44455.68550925926</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33619,7 +33619,7 @@
         <v>45794.82371527778</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>44588</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33733,7 +33733,7 @@
         <v>44897</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45794.81975694445</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>45769.62891203703</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>45798.45043981481</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>44935</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>44935.60138888889</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44950</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34147,7 +34147,7 @@
         <v>44494</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>44896</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44858</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>45436.41305555555</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>45758.56946759259</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44644</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>44084</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>44454</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>45110.56027777777</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>45110</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>45798.59671296296</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45274.43547453704</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>45671.59245370371</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>45408</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>45558.54422453704</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>45558</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35104,7 +35104,7 @@
         <v>45096</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>45565.5381712963</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>45798.66228009259</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45532</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>45202</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>44859</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45554.28857638889</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>45121</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>45336</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>44582</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>45442.6052199074</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>45442.60829861111</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45442.68033564815</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45722.46946759259</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>45183.65135416666</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45183.65233796297</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45803.43815972222</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>45762.76337962963</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>45597.40140046296</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>45279.66864583334</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36289,7 +36289,7 @@
         <v>45043</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>45736.72646990741</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36403,7 +36403,7 @@
         <v>45071</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36460,7 +36460,7 @@
         <v>45684.4203125</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45678.6377199074</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36579,7 +36579,7 @@
         <v>45509.57052083333</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36636,7 +36636,7 @@
         <v>44889</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>44166</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36750,7 +36750,7 @@
         <v>45678.59783564815</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36807,7 +36807,7 @@
         <v>45317</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>45804.59579861111</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>45369.61550925926</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45202.56994212963</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>45145</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>45807</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>45043</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>45215.63990740741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>45453.55534722222</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>44936</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>45098.37322916667</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
         <v>44890</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>44176</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>45769</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37687,7 +37687,7 @@
         <v>45013.63658564815</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37744,7 +37744,7 @@
         <v>45414.39614583334</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37801,7 +37801,7 @@
         <v>44956.54967592593</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45183</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45764.43782407408</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45764.44263888889</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>44721</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>45117</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>44980</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38215,7 +38215,7 @@
         <v>45043</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38277,7 +38277,7 @@
         <v>44096</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38334,7 +38334,7 @@
         <v>45757.66474537037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38391,7 +38391,7 @@
         <v>45763.41083333334</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38453,7 +38453,7 @@
         <v>45758.35732638889</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>45217.51479166667</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>45240</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>45191.39708333334</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>45369</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>45118</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>45813.56320601852</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>45715.56964120371</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38924,7 +38924,7 @@
         <v>45733.62203703704</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>44536</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44448</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44993</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39162,7 +39162,7 @@
         <v>44803.59099537037</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39219,7 +39219,7 @@
         <v>45178.43909722222</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39281,7 +39281,7 @@
         <v>45817.42607638889</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>45153</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>44860</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>45215</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>45096</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45817.64487268519</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39638,7 +39638,7 @@
         <v>45817.41037037037</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39695,7 +39695,7 @@
         <v>44939</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>44987.5428587963</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>45817.47909722223</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>44599</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>44999</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
         <v>44956</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         <v>45379</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>45049</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>45817</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45817</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>45330</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>45860</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>44677</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>45219.32268518519</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>45468.82832175926</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40575,7 +40575,7 @@
         <v>45126</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40632,7 +40632,7 @@
         <v>45126</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40689,7 +40689,7 @@
         <v>45657.94784722223</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>44384</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>45201.63637731481</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>44980.48200231481</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>45820.39863425926</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>45820.37113425926</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>45741.63417824074</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
         <v>45268</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>44907.66710648148</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>45114</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>45114</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41341,7 +41341,7 @@
         <v>44742</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>44163</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>45824.31493055556</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41517,7 +41517,7 @@
         <v>44469</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>45729</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>45723.66629629629</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>45867.7115625</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>45824.45221064815</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>45824.32293981482</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>45614.46292824074</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>44679</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>45317</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45365</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>45359.68173611111</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42174,7 +42174,7 @@
         <v>45405</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42231,7 +42231,7 @@
         <v>45769.45751157407</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42293,7 +42293,7 @@
         <v>44923.67971064815</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42355,7 +42355,7 @@
         <v>44880.44351851852</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>44930</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>44974</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42536,7 +42536,7 @@
         <v>44221</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>45832</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42650,7 +42650,7 @@
         <v>44414</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42707,7 +42707,7 @@
         <v>45873</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>45048</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>44936</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42888,7 +42888,7 @@
         <v>44936</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42950,7 +42950,7 @@
         <v>45833.65659722222</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43007,7 +43007,7 @@
         <v>45043</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
         <v>45716.57158564815</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45833.40451388889</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>45092.35369212963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43240,7 +43240,7 @@
         <v>45106</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43297,7 +43297,7 @@
         <v>45833.4374537037</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43354,7 +43354,7 @@
         <v>45832</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
         <v>45832</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>44970.65930555556</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>45747.44502314815</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43582,7 +43582,7 @@
         <v>45769.57802083333</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43639,7 +43639,7 @@
         <v>45769</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43696,7 +43696,7 @@
         <v>45178.4275</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43758,7 +43758,7 @@
         <v>44865</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>45770.84420138889</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>44488</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>44994.41405092592</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43986,7 +43986,7 @@
         <v>45028</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44043,7 +44043,7 @@
         <v>45442.38490740741</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>45727.64337962963</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>44908</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>44943.56112268518</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44281,7 +44281,7 @@
         <v>44943</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45408.49326388889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44400,7 +44400,7 @@
         <v>45106</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>45211.52641203703</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45211.52895833334</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>45678.57045138889</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>45678.58166666667</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45716.40918981482</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44747,7 +44747,7 @@
         <v>44862</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44809,7 +44809,7 @@
         <v>45684.41622685185</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44871,7 +44871,7 @@
         <v>45317</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45215.63818287037</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45043.49425925926</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>44236</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45109,7 +45109,7 @@
         <v>44427.49322916667</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45436.41847222222</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>44805</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>45204</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>45201.56556712963</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45409,7 +45409,7 @@
         <v>45132</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>45356.64872685185</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45528,7 +45528,7 @@
         <v>44504</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45590,7 +45590,7 @@
         <v>44361</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>45836</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45704,7 +45704,7 @@
         <v>45373.48878472222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>45527.43385416667</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>45215</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>44992</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45838.683125</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45334</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>44641.78332175926</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45252</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45369.61841435185</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>45141</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46284,7 +46284,7 @@
         <v>44945.58030092593</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46341,7 +46341,7 @@
         <v>45673</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46398,7 +46398,7 @@
         <v>45128</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>45758.60146990741</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46512,7 +46512,7 @@
         <v>45686.61590277778</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46574,7 +46574,7 @@
         <v>45741.51940972222</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45874</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45883.5738425926</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45883.59934027777</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45881</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46869,7 +46869,7 @@
         <v>45096</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45881</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>44218</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>44936</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
         <v>44312</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>45883.63648148148</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>45883.69113425926</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>45736.32394675926</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>45840.65592592592</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47397,7 +47397,7 @@
         <v>45883.58756944445</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47454,7 +47454,7 @@
         <v>45840.65777777778</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47511,7 +47511,7 @@
         <v>45840.66978009259</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47568,7 +47568,7 @@
         <v>45840.66780092593</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>45638</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>45883.58974537037</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45883.74664351852</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47806,7 +47806,7 @@
         <v>45006</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>45840.6602199074</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>45246.41627314815</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45246</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48039,7 +48039,7 @@
         <v>45673.49019675926</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>45582.98494212963</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45174</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45174</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45886</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>45886.65516203704</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45457.59425925926</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45884.57759259259</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48510,7 +48510,7 @@
         <v>45884.60458333333</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48572,7 +48572,7 @@
         <v>45845.65797453704</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48634,7 +48634,7 @@
         <v>45680</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48696,7 +48696,7 @@
         <v>45678.44092592593</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48753,7 +48753,7 @@
         <v>45386</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48810,7 +48810,7 @@
         <v>45092.36790509259</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48867,7 +48867,7 @@
         <v>44981</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48929,7 +48929,7 @@
         <v>45414.3944212963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48986,7 +48986,7 @@
         <v>45254</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>45027</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45425.89037037037</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>45581.62796296296</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>45091</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>45369.62108796297</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>44131</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49395,7 +49395,7 @@
         <v>45071</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49452,7 +49452,7 @@
         <v>45887</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>45884.68263888889</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>45887</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>45845.45563657407</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49685,7 +49685,7 @@
         <v>45043</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45884.45916666667</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49804,7 +49804,7 @@
         <v>45771.76943287037</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49861,7 +49861,7 @@
         <v>44825</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49918,7 +49918,7 @@
         <v>45888.61847222222</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45442.61221064815</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50042,7 +50042,7 @@
         <v>44358</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45008</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45888.46922453704</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45888.4712037037</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>45645.27707175926</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50332,7 +50332,7 @@
         <v>45888.4658449074</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45763.64096064815</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50456,7 +50456,7 @@
         <v>45699.65944444444</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50518,7 +50518,7 @@
         <v>45339.5277199074</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50575,7 +50575,7 @@
         <v>45758.60465277778</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50632,7 +50632,7 @@
         <v>45758.61055555556</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50689,7 +50689,7 @@
         <v>44237</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45797</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50813,7 +50813,7 @@
         <v>45891.60103009259</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50870,7 +50870,7 @@
         <v>45889</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50927,7 +50927,7 @@
         <v>45877</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50984,7 +50984,7 @@
         <v>45877</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>45891.59726851852</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51098,7 +51098,7 @@
         <v>45891.59938657407</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51155,7 +51155,7 @@
         <v>45796.44922453703</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51217,7 +51217,7 @@
         <v>45030</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51274,7 +51274,7 @@
         <v>44433</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51336,7 +51336,7 @@
         <v>45030.62916666667</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>44939</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51450,7 +51450,7 @@
         <v>45093.54811342592</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>45891.60346064815</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51564,7 +51564,7 @@
         <v>45798.60880787037</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51626,7 +51626,7 @@
         <v>44177</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
         <v>44177</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51740,7 +51740,7 @@
         <v>45889</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51797,7 +51797,7 @@
         <v>45093</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51859,7 +51859,7 @@
         <v>44992</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51916,7 +51916,7 @@
         <v>45012</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>44980</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52035,7 +52035,7 @@
         <v>45771.66951388889</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>45153.36402777778</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52159,7 +52159,7 @@
         <v>45709.4119212963</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52221,7 +52221,7 @@
         <v>45453.52299768518</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52278,7 +52278,7 @@
         <v>45252.91344907408</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52335,7 +52335,7 @@
         <v>45636.45025462963</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>45636.4737962963</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52449,7 +52449,7 @@
         <v>44243</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52506,7 +52506,7 @@
         <v>45731.59962962963</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52563,7 +52563,7 @@
         <v>44867</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45373.72511574074</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>44980</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45016.64986111111</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>44573</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52863,7 +52863,7 @@
         <v>45254</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52925,7 +52925,7 @@
         <v>45742.32277777778</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52982,7 +52982,7 @@
         <v>44333</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53039,7 +53039,7 @@
         <v>44225</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53101,7 +53101,7 @@
         <v>45330</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53158,7 +53158,7 @@
         <v>45497</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53215,7 +53215,7 @@
         <v>44861</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53277,7 +53277,7 @@
         <v>44607</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53334,7 +53334,7 @@
         <v>45629.7202662037</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53391,7 +53391,7 @@
         <v>45716.37259259259</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         <v>45106</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53510,7 +53510,7 @@
         <v>45706.54204861111</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -53567,7 +53567,7 @@
         <v>45706.54572916667</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45012</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -673,59 +673,169 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
+          <t>A 24615-2025</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45798.58304398148</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>45894</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NORRKÖPING</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>13</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>17</v>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Tornseglare
+Lakritsmusseron
+Blå taggsvamp
+Gropticka
+Motaggsvamp
+Orange taggsvamp
+Spillkråka
+Svart taggsvamp
+Svartvit taggsvamp
+Talltaggsvamp
+Tallticka
+Talltita
+Ullticka
+Blomkålssvamp
+Dropptaggsvamp
+Grönpyrola
+Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="S3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0581/artfynd/A 24615-2025 artfynd.xlsx", "A 24615-2025")</f>
+        <v/>
+      </c>
+      <c r="T3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0581/kartor/A 24615-2025 karta.png", "A 24615-2025")</f>
+        <v/>
+      </c>
+      <c r="V3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0581/klagomål/A 24615-2025 FSC-klagomål.docx", "A 24615-2025")</f>
+        <v/>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0581/klagomålsmail/A 24615-2025 FSC-klagomål mail.docx", "A 24615-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0581/tillsyn/A 24615-2025 tillsynsbegäran.docx", "A 24615-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0581/tillsynsmail/A 24615-2025 tillsynsbegäran mail.docx", "A 24615-2025")</f>
+        <v/>
+      </c>
+      <c r="Z3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0581/fåglar/A 24615-2025 prioriterade fågelarter.docx", "A 24615-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>A 57525-2022</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B4" s="1" t="n">
         <v>44896</v>
       </c>
-      <c r="C3" s="1" t="n">
-        <v>45893</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>NORRKÖPING</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="C4" s="1" t="n">
+        <v>45894</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NORRKÖPING</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>16.7</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H4" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I4" t="n">
         <v>8</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>7</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>7</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>16</v>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Granticka
 Kandelabersvamp
@@ -745,137 +855,28 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="S3">
+      <c r="S4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0581/artfynd/A 57525-2022 artfynd.xlsx", "A 57525-2022")</f>
         <v/>
       </c>
-      <c r="T3">
+      <c r="T4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0581/kartor/A 57525-2022 karta.png", "A 57525-2022")</f>
         <v/>
       </c>
-      <c r="V3">
+      <c r="V4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0581/klagomål/A 57525-2022 FSC-klagomål.docx", "A 57525-2022")</f>
         <v/>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0581/klagomålsmail/A 57525-2022 FSC-klagomål mail.docx", "A 57525-2022")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0581/tillsyn/A 57525-2022 tillsynsbegäran.docx", "A 57525-2022")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0581/tillsynsmail/A 57525-2022 tillsynsbegäran mail.docx", "A 57525-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 24615-2025</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>45798.58304398148</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>45893</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>NORRKÖPING</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>12</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>16</v>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>Tornseglare
-Blå taggsvamp
-Gropticka
-Motaggsvamp
-Orange taggsvamp
-Spillkråka
-Svart taggsvamp
-Svartvit taggsvamp
-Talltaggsvamp
-Tallticka
-Talltita
-Ullticka
-Blomkålssvamp
-Dropptaggsvamp
-Grönpyrola
-Zontaggsvamp</t>
-        </is>
-      </c>
-      <c r="S4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0581/artfynd/A 24615-2025 artfynd.xlsx", "A 24615-2025")</f>
-        <v/>
-      </c>
-      <c r="T4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0581/kartor/A 24615-2025 karta.png", "A 24615-2025")</f>
-        <v/>
-      </c>
-      <c r="V4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0581/klagomål/A 24615-2025 FSC-klagomål.docx", "A 24615-2025")</f>
-        <v/>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0581/klagomålsmail/A 24615-2025 FSC-klagomål mail.docx", "A 24615-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0581/tillsyn/A 24615-2025 tillsynsbegäran.docx", "A 24615-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0581/tillsynsmail/A 24615-2025 tillsynsbegäran mail.docx", "A 24615-2025")</f>
-        <v/>
-      </c>
-      <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0581/fåglar/A 24615-2025 prioriterade fågelarter.docx", "A 24615-2025")</f>
         <v/>
       </c>
     </row>
@@ -889,7 +890,7 @@
         <v>44299</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,7 +996,7 @@
         <v>44264</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1096,7 +1097,7 @@
         <v>45579</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,7 +1201,7 @@
         <v>45645.27462962963</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1303,7 @@
         <v>45012</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,7 +1400,7 @@
         <v>45139</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1502,7 @@
         <v>45441</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,7 +1599,7 @@
         <v>45880.62738425926</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,7 +1696,7 @@
         <v>45568</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,7 +1793,7 @@
         <v>45886.64045138889</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1888,7 +1889,7 @@
         <v>44067</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1979,7 +1980,7 @@
         <v>45133</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2072,14 +2073,14 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 51531-2024</t>
+          <t>A 21683-2025</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>45604</v>
+        <v>45783.4903125</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2097,39 +2098,139 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>7</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7</v>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp
+Dvärgbägarlav
+Kolflarnlav
+Orange taggsvamp
+Spillkråka
+Svart taggsvamp
+Ullticka</t>
+        </is>
+      </c>
+      <c r="S17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0581/artfynd/A 21683-2025 artfynd.xlsx", "A 21683-2025")</f>
+        <v/>
+      </c>
+      <c r="T17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0581/kartor/A 21683-2025 karta.png", "A 21683-2025")</f>
+        <v/>
+      </c>
+      <c r="V17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0581/klagomål/A 21683-2025 FSC-klagomål.docx", "A 21683-2025")</f>
+        <v/>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0581/klagomålsmail/A 21683-2025 FSC-klagomål mail.docx", "A 21683-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0581/tillsyn/A 21683-2025 tillsynsbegäran.docx", "A 21683-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0581/tillsynsmail/A 21683-2025 tillsynsbegäran mail.docx", "A 21683-2025")</f>
+        <v/>
+      </c>
+      <c r="Z17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0581/fåglar/A 21683-2025 prioriterade fågelarter.docx", "A 21683-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 51531-2024</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>45604</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>45894</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NORRKÖPING</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>3</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>2</v>
       </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>6</v>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>Lunglav
 Scharlakansvaxing
@@ -2139,127 +2240,28 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="S17">
+      <c r="S18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0581/artfynd/A 51531-2024 artfynd.xlsx", "A 51531-2024")</f>
         <v/>
       </c>
-      <c r="T17">
+      <c r="T18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0581/kartor/A 51531-2024 karta.png", "A 51531-2024")</f>
         <v/>
       </c>
-      <c r="V17">
+      <c r="V18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0581/klagomål/A 51531-2024 FSC-klagomål.docx", "A 51531-2024")</f>
         <v/>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0581/klagomålsmail/A 51531-2024 FSC-klagomål mail.docx", "A 51531-2024")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0581/tillsyn/A 51531-2024 tillsynsbegäran.docx", "A 51531-2024")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0581/tillsynsmail/A 51531-2024 tillsynsbegäran mail.docx", "A 51531-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 21683-2025</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>45783.4903125</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>45893</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>NORRKÖPING</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>6</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>6</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6</v>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav
-Kolflarnlav
-Orange taggsvamp
-Spillkråka
-Svart taggsvamp
-Ullticka</t>
-        </is>
-      </c>
-      <c r="S18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0581/artfynd/A 21683-2025 artfynd.xlsx", "A 21683-2025")</f>
-        <v/>
-      </c>
-      <c r="T18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0581/kartor/A 21683-2025 karta.png", "A 21683-2025")</f>
-        <v/>
-      </c>
-      <c r="V18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0581/klagomål/A 21683-2025 FSC-klagomål.docx", "A 21683-2025")</f>
-        <v/>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0581/klagomålsmail/A 21683-2025 FSC-klagomål mail.docx", "A 21683-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0581/tillsyn/A 21683-2025 tillsynsbegäran.docx", "A 21683-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0581/tillsynsmail/A 21683-2025 tillsynsbegäran mail.docx", "A 21683-2025")</f>
-        <v/>
-      </c>
-      <c r="Z18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0581/fåglar/A 21683-2025 prioriterade fågelarter.docx", "A 21683-2025")</f>
         <v/>
       </c>
     </row>
@@ -2273,7 +2275,7 @@
         <v>44076</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2366,7 +2368,7 @@
         <v>45421</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2460,7 +2462,7 @@
         <v>44578</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2554,7 +2556,7 @@
         <v>45723.61545138889</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2652,7 +2654,7 @@
         <v>45742.41269675926</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2750,7 +2752,7 @@
         <v>45832.36966435185</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2844,7 +2846,7 @@
         <v>44412</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2941,7 +2943,7 @@
         <v>45568</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3034,7 +3036,7 @@
         <v>45042</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3131,7 +3133,7 @@
         <v>45723.59275462963</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3224,7 +3226,7 @@
         <v>45421</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,7 +3323,7 @@
         <v>45731.65016203704</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3413,7 +3415,7 @@
         <v>45723.57098379629</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,7 +3516,7 @@
         <v>45881.41636574074</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3607,7 +3609,7 @@
         <v>45441.33914351852</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3699,7 +3701,7 @@
         <v>45604</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3791,7 +3793,7 @@
         <v>45583</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3883,7 +3885,7 @@
         <v>45086</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3975,7 +3977,7 @@
         <v>45012</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4066,7 +4068,7 @@
         <v>45764.47825231482</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4158,7 +4160,7 @@
         <v>45013.77040509259</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4245,7 +4247,7 @@
         <v>44977</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4332,7 +4334,7 @@
         <v>45832.31648148148</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4419,7 +4421,7 @@
         <v>45833.56057870371</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4510,7 +4512,7 @@
         <v>45884.4946875</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4597,7 +4599,7 @@
         <v>44931</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4689,7 +4691,7 @@
         <v>45758.54390046297</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4780,7 +4782,7 @@
         <v>45733.45780092593</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4871,7 +4873,7 @@
         <v>45694</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4957,7 +4959,7 @@
         <v>44454</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5052,7 +5054,7 @@
         <v>45772.6571412037</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5143,7 +5145,7 @@
         <v>45568.44137731481</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5234,7 +5236,7 @@
         <v>45583</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5325,7 +5327,7 @@
         <v>45258.56491898148</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5416,7 +5418,7 @@
         <v>45832.3365625</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5507,7 +5509,7 @@
         <v>44789</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5598,7 +5600,7 @@
         <v>44067</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5684,7 +5686,7 @@
         <v>45086</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5779,7 +5781,7 @@
         <v>44308</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5873,7 +5875,7 @@
         <v>44480</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5963,7 +5965,7 @@
         <v>44426</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6048,7 +6050,7 @@
         <v>44524</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6133,7 +6135,7 @@
         <v>44452</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6223,7 +6225,7 @@
         <v>44490</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6308,7 +6310,7 @@
         <v>45042</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6398,7 +6400,7 @@
         <v>45421</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6488,7 +6490,7 @@
         <v>45251</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6573,7 +6575,7 @@
         <v>44354</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6658,7 +6660,7 @@
         <v>44089</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6748,7 +6750,7 @@
         <v>45580</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6833,7 +6835,7 @@
         <v>45362</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6923,7 +6925,7 @@
         <v>45723.66964120371</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7008,7 +7010,7 @@
         <v>45747.58131944444</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7098,7 +7100,7 @@
         <v>44777.49493055556</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7188,7 +7190,7 @@
         <v>45348.68336805556</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7278,7 +7280,7 @@
         <v>45117</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7372,7 +7374,7 @@
         <v>45763.60795138889</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7457,7 +7459,7 @@
         <v>45783.61222222223</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7547,7 +7549,7 @@
         <v>45583</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7637,7 +7639,7 @@
         <v>45702.76395833334</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7722,7 +7724,7 @@
         <v>45583.3479050926</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7812,7 +7814,7 @@
         <v>45770.63996527778</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7897,7 +7899,7 @@
         <v>45201</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7982,7 +7984,7 @@
         <v>45174</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8067,7 +8069,7 @@
         <v>44886.54420138889</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8152,7 +8154,7 @@
         <v>45796</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8246,7 +8248,7 @@
         <v>45742.43848379629</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8340,7 +8342,7 @@
         <v>45744</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8430,7 +8432,7 @@
         <v>45096</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8524,7 +8526,7 @@
         <v>45744.41443287037</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8614,7 +8616,7 @@
         <v>45056</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8699,7 +8701,7 @@
         <v>45723.55663194445</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8793,7 +8795,7 @@
         <v>45583</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8883,7 +8885,7 @@
         <v>45201</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8968,7 +8970,7 @@
         <v>44132</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9058,7 +9060,7 @@
         <v>45408</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9147,7 +9149,7 @@
         <v>45716.5672337963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9232,7 +9234,7 @@
         <v>45369</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9326,7 +9328,7 @@
         <v>45376</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9416,7 +9418,7 @@
         <v>45411.57177083333</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9506,7 +9508,7 @@
         <v>44151</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9563,7 +9565,7 @@
         <v>44219</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9625,7 +9627,7 @@
         <v>44211</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9687,7 +9689,7 @@
         <v>44211</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9749,7 +9751,7 @@
         <v>44146</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9811,7 +9813,7 @@
         <v>44158</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9868,7 +9870,7 @@
         <v>44456</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9930,7 +9932,7 @@
         <v>44456</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9992,7 +9994,7 @@
         <v>44301</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10049,7 +10051,7 @@
         <v>44307</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10106,7 +10108,7 @@
         <v>44530</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10168,7 +10170,7 @@
         <v>44582.4696875</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10225,7 +10227,7 @@
         <v>44211</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10287,7 +10289,7 @@
         <v>44217</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10344,7 +10346,7 @@
         <v>44214</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10406,7 +10408,7 @@
         <v>44176</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10468,7 +10470,7 @@
         <v>44502</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10525,7 +10527,7 @@
         <v>44107</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10582,7 +10584,7 @@
         <v>44622</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10644,7 +10646,7 @@
         <v>44537</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10701,7 +10703,7 @@
         <v>44218</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10763,7 +10765,7 @@
         <v>44825.47923611111</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10820,7 +10822,7 @@
         <v>44340.80107638889</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10877,7 +10879,7 @@
         <v>44728.82296296296</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10934,7 +10936,7 @@
         <v>44739</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10991,7 +10993,7 @@
         <v>44279</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11048,7 +11050,7 @@
         <v>44368</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11110,7 +11112,7 @@
         <v>44719.43086805556</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11167,7 +11169,7 @@
         <v>44169</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11229,7 +11231,7 @@
         <v>44169</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11291,7 +11293,7 @@
         <v>44216</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11353,7 +11355,7 @@
         <v>44258</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11410,7 +11412,7 @@
         <v>44503</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11472,7 +11474,7 @@
         <v>44448</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11529,7 +11531,7 @@
         <v>44306</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11586,7 +11588,7 @@
         <v>44440</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11643,7 +11645,7 @@
         <v>44368</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11705,7 +11707,7 @@
         <v>44441</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11767,7 +11769,7 @@
         <v>44301</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11824,7 +11826,7 @@
         <v>44865</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11881,7 +11883,7 @@
         <v>44294</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11938,7 +11940,7 @@
         <v>44286</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11995,7 +11997,7 @@
         <v>44524.67836805555</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12052,7 +12054,7 @@
         <v>44385</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12109,7 +12111,7 @@
         <v>44696.775</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12166,7 +12168,7 @@
         <v>44390</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12223,7 +12225,7 @@
         <v>44432</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12285,7 +12287,7 @@
         <v>44433</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12342,7 +12344,7 @@
         <v>44494</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12399,7 +12401,7 @@
         <v>44447</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12456,7 +12458,7 @@
         <v>44368.88704861111</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12513,7 +12515,7 @@
         <v>44340</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12570,7 +12572,7 @@
         <v>44333</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12627,7 +12629,7 @@
         <v>44370</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12689,7 +12691,7 @@
         <v>44671</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12746,7 +12748,7 @@
         <v>44713</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12803,7 +12805,7 @@
         <v>44813</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12865,7 +12867,7 @@
         <v>44530</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12927,7 +12929,7 @@
         <v>44515</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12989,7 +12991,7 @@
         <v>44571</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13051,7 +13053,7 @@
         <v>44169</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13113,7 +13115,7 @@
         <v>44442.66228009259</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13170,7 +13172,7 @@
         <v>44208</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13232,7 +13234,7 @@
         <v>44475</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13289,7 +13291,7 @@
         <v>44475</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13346,7 +13348,7 @@
         <v>44393</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13403,7 +13405,7 @@
         <v>44272</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13465,7 +13467,7 @@
         <v>44630.3978587963</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13522,7 +13524,7 @@
         <v>44371</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13584,7 +13586,7 @@
         <v>44371</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13646,7 +13648,7 @@
         <v>44124.63679398148</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13703,7 +13705,7 @@
         <v>44362</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13760,7 +13762,7 @@
         <v>44211</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13822,7 +13824,7 @@
         <v>44211</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13884,7 +13886,7 @@
         <v>44524</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13941,7 +13943,7 @@
         <v>44271.81282407408</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13998,7 +14000,7 @@
         <v>44447</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14055,7 +14057,7 @@
         <v>44530</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14117,7 +14119,7 @@
         <v>44313</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14179,7 +14181,7 @@
         <v>44300</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14236,7 +14238,7 @@
         <v>44300</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14293,7 +14295,7 @@
         <v>44503</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14355,7 +14357,7 @@
         <v>44459</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14417,7 +14419,7 @@
         <v>44446</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14479,7 +14481,7 @@
         <v>44321</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14541,7 +14543,7 @@
         <v>44879.39153935185</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14603,7 +14605,7 @@
         <v>44459</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14660,7 +14662,7 @@
         <v>44475</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14717,7 +14719,7 @@
         <v>44475</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14774,7 +14776,7 @@
         <v>44249</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14831,7 +14833,7 @@
         <v>44574</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14888,7 +14890,7 @@
         <v>44326</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14945,7 +14947,7 @@
         <v>44686</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15002,7 +15004,7 @@
         <v>44326</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15059,7 +15061,7 @@
         <v>44326</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15116,7 +15118,7 @@
         <v>44602</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15178,7 +15180,7 @@
         <v>44363</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15240,7 +15242,7 @@
         <v>44098</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15297,7 +15299,7 @@
         <v>44348</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15354,7 +15356,7 @@
         <v>44726</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15416,7 +15418,7 @@
         <v>44152</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15473,7 +15475,7 @@
         <v>44889.55255787037</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15530,7 +15532,7 @@
         <v>44328</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15592,7 +15594,7 @@
         <v>44886.47697916667</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15654,7 +15656,7 @@
         <v>44452</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15711,7 +15713,7 @@
         <v>44874</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15768,7 +15770,7 @@
         <v>44219</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15830,7 +15832,7 @@
         <v>44162</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15892,7 +15894,7 @@
         <v>44825</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15949,7 +15951,7 @@
         <v>44449</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16011,7 +16013,7 @@
         <v>44487</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16073,7 +16075,7 @@
         <v>44596</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16130,7 +16132,7 @@
         <v>44358</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16192,7 +16194,7 @@
         <v>44468</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16254,7 +16256,7 @@
         <v>44756</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16311,7 +16313,7 @@
         <v>44208</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16368,7 +16370,7 @@
         <v>44252</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16430,7 +16432,7 @@
         <v>44441</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16492,7 +16494,7 @@
         <v>44452</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16554,7 +16556,7 @@
         <v>44272</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16611,7 +16613,7 @@
         <v>44432</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16668,7 +16670,7 @@
         <v>44137</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16725,7 +16727,7 @@
         <v>44137</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16782,7 +16784,7 @@
         <v>44630</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16839,7 +16841,7 @@
         <v>44740</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16896,7 +16898,7 @@
         <v>44344.49251157408</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16958,7 +16960,7 @@
         <v>44582</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17020,7 +17022,7 @@
         <v>44363</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17082,7 +17084,7 @@
         <v>44279</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17139,7 +17141,7 @@
         <v>44313</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17201,7 +17203,7 @@
         <v>44825</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17258,7 +17260,7 @@
         <v>44445</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17320,7 +17322,7 @@
         <v>44270</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17377,7 +17379,7 @@
         <v>44557</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17439,7 +17441,7 @@
         <v>44741.57063657408</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17496,7 +17498,7 @@
         <v>44869.4575</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17558,7 +17560,7 @@
         <v>44302</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17615,7 +17617,7 @@
         <v>45736.31508101852</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17672,7 +17674,7 @@
         <v>45769</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17729,7 +17731,7 @@
         <v>45266.69091435185</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17786,7 +17788,7 @@
         <v>44730</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17848,7 +17850,7 @@
         <v>45435</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17905,7 +17907,7 @@
         <v>44354.45140046296</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17962,7 +17964,7 @@
         <v>44977.57584490741</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18024,7 +18026,7 @@
         <v>44279</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18081,7 +18083,7 @@
         <v>44862</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18143,7 +18145,7 @@
         <v>45595</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18200,7 +18202,7 @@
         <v>45090</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18262,7 +18264,7 @@
         <v>45706.42958333333</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18319,7 +18321,7 @@
         <v>44322</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18376,7 +18378,7 @@
         <v>45678.47236111111</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18433,7 +18435,7 @@
         <v>45709.42859953704</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18495,7 +18497,7 @@
         <v>45614.52813657407</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18557,7 +18559,7 @@
         <v>45401.46640046296</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18619,7 +18621,7 @@
         <v>44651.42819444444</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18676,7 +18678,7 @@
         <v>44362</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18738,7 +18740,7 @@
         <v>45719.4522337963</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18795,7 +18797,7 @@
         <v>44147</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18852,7 +18854,7 @@
         <v>45114</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18909,7 +18911,7 @@
         <v>45106</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18966,7 +18968,7 @@
         <v>44630</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19023,7 +19025,7 @@
         <v>45008.62458333333</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19085,7 +19087,7 @@
         <v>45250.5799537037</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19142,7 +19144,7 @@
         <v>44286.88952546296</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19199,7 +19201,7 @@
         <v>44957</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19261,7 +19263,7 @@
         <v>44573.38521990741</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19318,7 +19320,7 @@
         <v>44578</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19380,7 +19382,7 @@
         <v>44249</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19437,7 +19439,7 @@
         <v>45405</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19494,7 +19496,7 @@
         <v>44783</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19551,7 +19553,7 @@
         <v>45110</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19613,7 +19615,7 @@
         <v>45261.50924768519</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19670,7 +19672,7 @@
         <v>44826</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19727,7 +19729,7 @@
         <v>45721.51255787037</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19784,7 +19786,7 @@
         <v>45721.51346064815</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19841,7 +19843,7 @@
         <v>44713.58678240741</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19898,7 +19900,7 @@
         <v>45758.36203703703</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19955,7 +19957,7 @@
         <v>44083</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20012,7 +20014,7 @@
         <v>44977.63902777778</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20074,7 +20076,7 @@
         <v>45336</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20131,7 +20133,7 @@
         <v>44880</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20188,7 +20190,7 @@
         <v>45644</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20250,7 +20252,7 @@
         <v>45469.43265046296</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20307,7 +20309,7 @@
         <v>44719.43200231482</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20364,7 +20366,7 @@
         <v>44900</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20426,7 +20428,7 @@
         <v>45012.79270833333</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20483,7 +20485,7 @@
         <v>44181</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20545,7 +20547,7 @@
         <v>45016.67141203704</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20607,7 +20609,7 @@
         <v>45112</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20664,7 +20666,7 @@
         <v>45043</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20726,7 +20728,7 @@
         <v>45118</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20783,7 +20785,7 @@
         <v>45670</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20840,7 +20842,7 @@
         <v>45671.5678125</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20902,7 +20904,7 @@
         <v>45310</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20964,7 +20966,7 @@
         <v>45706.47790509259</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21021,7 +21023,7 @@
         <v>44739.52209490741</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21078,7 +21080,7 @@
         <v>45761.59716435185</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21140,7 +21142,7 @@
         <v>44364.78170138889</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21197,7 +21199,7 @@
         <v>45086.71662037037</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21259,7 +21261,7 @@
         <v>45153</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21321,7 +21323,7 @@
         <v>45490.72372685185</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21378,7 +21380,7 @@
         <v>45769.40231481481</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21440,7 +21442,7 @@
         <v>44512</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21502,7 +21504,7 @@
         <v>44433</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21559,7 +21561,7 @@
         <v>45716.45121527778</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21621,7 +21623,7 @@
         <v>45370</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21683,7 +21685,7 @@
         <v>44805</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21745,7 +21747,7 @@
         <v>44783</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21802,7 +21804,7 @@
         <v>44746</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21859,7 +21861,7 @@
         <v>44907.65043981482</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21916,7 +21918,7 @@
         <v>45657.95927083334</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21978,7 +21980,7 @@
         <v>45191</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22035,7 +22037,7 @@
         <v>45117</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22097,7 +22099,7 @@
         <v>45076</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22159,7 +22161,7 @@
         <v>45386.32806712963</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22221,7 +22223,7 @@
         <v>45121</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22283,7 +22285,7 @@
         <v>45579.56570601852</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22345,7 +22347,7 @@
         <v>45733.43347222222</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22407,7 +22409,7 @@
         <v>45733.44431712963</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22489,7 +22491,7 @@
         <v>45706.49520833333</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22546,7 +22548,7 @@
         <v>45706.54385416667</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22603,7 +22605,7 @@
         <v>45716.39159722222</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22660,7 +22662,7 @@
         <v>45699.75690972222</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22717,7 +22719,7 @@
         <v>44155</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22774,7 +22776,7 @@
         <v>45317</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22836,7 +22838,7 @@
         <v>44168</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22893,7 +22895,7 @@
         <v>45432.54622685185</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22950,7 +22952,7 @@
         <v>45520.52375</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23007,7 +23009,7 @@
         <v>44935.64165509259</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23069,7 +23071,7 @@
         <v>45093</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23126,7 +23128,7 @@
         <v>45715.5837962963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23188,7 +23190,7 @@
         <v>44957</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23250,7 +23252,7 @@
         <v>45053.36554398148</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23307,7 +23309,7 @@
         <v>45394</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23369,7 +23371,7 @@
         <v>44767</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23426,7 +23428,7 @@
         <v>45726.90959490741</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23483,7 +23485,7 @@
         <v>45723.67724537037</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23540,7 +23542,7 @@
         <v>45030.61489583334</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23597,7 +23599,7 @@
         <v>45030.61744212963</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23654,7 +23656,7 @@
         <v>45769.41631944444</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23716,7 +23718,7 @@
         <v>45072</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23778,7 +23780,7 @@
         <v>45254</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23840,7 +23842,7 @@
         <v>44974</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23902,7 +23904,7 @@
         <v>44455</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23959,7 +23961,7 @@
         <v>45642</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24021,7 +24023,7 @@
         <v>45106</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24078,7 +24080,7 @@
         <v>44861</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24135,7 +24137,7 @@
         <v>44853.64244212963</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24192,7 +24194,7 @@
         <v>45110</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24254,7 +24256,7 @@
         <v>44897</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24316,7 +24318,7 @@
         <v>45629.67508101852</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24373,7 +24375,7 @@
         <v>45629.67931712963</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24430,7 +24432,7 @@
         <v>44151.53271990741</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24487,7 +24489,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24549,7 +24551,7 @@
         <v>45356.66037037037</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24606,7 +24608,7 @@
         <v>44181</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24663,7 +24665,7 @@
         <v>45205.3119212963</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24720,7 +24722,7 @@
         <v>45727.6683449074</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24782,7 +24784,7 @@
         <v>44067</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24844,7 +24846,7 @@
         <v>44851</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24901,7 +24903,7 @@
         <v>45090.90752314815</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24963,7 +24965,7 @@
         <v>45729.36478009259</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25020,7 +25022,7 @@
         <v>45129</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25077,7 +25079,7 @@
         <v>45758.56056712963</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25139,7 +25141,7 @@
         <v>44936.46326388889</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25196,7 +25198,7 @@
         <v>44998</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25253,7 +25255,7 @@
         <v>45266</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25310,7 +25312,7 @@
         <v>45741.53599537037</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25372,7 +25374,7 @@
         <v>45478.47236111111</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25434,7 +25436,7 @@
         <v>44462</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25491,7 +25493,7 @@
         <v>45092.35266203704</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25548,7 +25550,7 @@
         <v>45764.47553240741</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25605,7 +25607,7 @@
         <v>44974.65918981482</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25667,7 +25669,7 @@
         <v>45636.45989583333</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25724,7 +25726,7 @@
         <v>45313</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25786,7 +25788,7 @@
         <v>44957</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25848,7 +25850,7 @@
         <v>45205.35753472222</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25905,7 +25907,7 @@
         <v>45238.33091435185</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25962,7 +25964,7 @@
         <v>45403.86942129629</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26019,7 +26021,7 @@
         <v>44741</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26076,7 +26078,7 @@
         <v>45446.57724537037</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26133,7 +26135,7 @@
         <v>45446.5790625</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26190,7 +26192,7 @@
         <v>45077</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26247,7 +26249,7 @@
         <v>45092</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26304,7 +26306,7 @@
         <v>44159.36447916667</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26361,7 +26363,7 @@
         <v>45278</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26418,7 +26420,7 @@
         <v>45566.46769675926</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26475,7 +26477,7 @@
         <v>45742.31784722222</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26532,7 +26534,7 @@
         <v>45030</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26589,7 +26591,7 @@
         <v>45399.62587962963</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26651,7 +26653,7 @@
         <v>45716.55766203703</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26708,7 +26710,7 @@
         <v>44105</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26770,7 +26772,7 @@
         <v>45547.64484953704</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26832,7 +26834,7 @@
         <v>45159</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26889,7 +26891,7 @@
         <v>45121</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26951,7 +26953,7 @@
         <v>45699</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27008,7 +27010,7 @@
         <v>45699.75583333334</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27065,7 +27067,7 @@
         <v>44910</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27127,7 +27129,7 @@
         <v>45442.67793981481</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27189,7 +27191,7 @@
         <v>45008.66204861111</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27251,7 +27253,7 @@
         <v>44928.45552083333</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27313,7 +27315,7 @@
         <v>45033</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27370,7 +27372,7 @@
         <v>45637</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27427,7 +27429,7 @@
         <v>45593.59819444444</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27489,7 +27491,7 @@
         <v>45037</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27546,7 +27548,7 @@
         <v>45117</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27608,7 +27610,7 @@
         <v>45583.55850694444</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27670,7 +27672,7 @@
         <v>45373.73894675926</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27727,7 +27729,7 @@
         <v>45030</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27784,7 +27786,7 @@
         <v>45048</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27841,7 +27843,7 @@
         <v>45583.34371527778</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27903,7 +27905,7 @@
         <v>45777.61991898148</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27965,7 +27967,7 @@
         <v>45726.91224537037</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28022,7 +28024,7 @@
         <v>45527.40489583334</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28079,7 +28081,7 @@
         <v>45386.35986111111</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28141,7 +28143,7 @@
         <v>45678.57731481481</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28198,7 +28200,7 @@
         <v>45022.34695601852</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28255,7 +28257,7 @@
         <v>45043.53597222222</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28312,7 +28314,7 @@
         <v>45014</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28369,7 +28371,7 @@
         <v>45527.41597222222</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28426,7 +28428,7 @@
         <v>45783</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28483,7 +28485,7 @@
         <v>44970.44197916667</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28545,7 +28547,7 @@
         <v>44181</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28602,7 +28604,7 @@
         <v>45783.68689814815</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28659,7 +28661,7 @@
         <v>44862</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28716,7 +28718,7 @@
         <v>45783.48681712963</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28778,7 +28780,7 @@
         <v>44096</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28835,7 +28837,7 @@
         <v>45782.659375</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28892,7 +28894,7 @@
         <v>45782.66719907407</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28949,7 +28951,7 @@
         <v>45254.54892361111</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29006,7 +29008,7 @@
         <v>45266</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29063,7 +29065,7 @@
         <v>45049.34974537037</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29120,7 +29122,7 @@
         <v>45049.35048611111</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29177,7 +29179,7 @@
         <v>45266.66998842593</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29234,7 +29236,7 @@
         <v>45432.6291550926</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29291,7 +29293,7 @@
         <v>45671.62931712963</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29348,7 +29350,7 @@
         <v>45237</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29410,7 +29412,7 @@
         <v>45784</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29467,7 +29469,7 @@
         <v>45535.91413194445</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29524,7 +29526,7 @@
         <v>44974.564375</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29586,7 +29588,7 @@
         <v>44137</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29643,7 +29645,7 @@
         <v>44965</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29700,7 +29702,7 @@
         <v>45784.62866898148</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29762,7 +29764,7 @@
         <v>45702.76590277778</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29819,7 +29821,7 @@
         <v>44067</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29881,7 +29883,7 @@
         <v>45747.59501157407</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29943,7 +29945,7 @@
         <v>45786</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30005,7 +30007,7 @@
         <v>45786.36358796297</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30067,7 +30069,7 @@
         <v>45356.64724537037</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30124,7 +30126,7 @@
         <v>44834</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30186,7 +30188,7 @@
         <v>44980</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30248,7 +30250,7 @@
         <v>44956</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30310,7 +30312,7 @@
         <v>45764.43002314815</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30367,7 +30369,7 @@
         <v>45789.42597222222</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30424,7 +30426,7 @@
         <v>44966.57550925926</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30486,7 +30488,7 @@
         <v>44652</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30543,7 +30545,7 @@
         <v>45587.58498842592</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30605,7 +30607,7 @@
         <v>44565</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30667,7 +30669,7 @@
         <v>45092.36126157407</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30724,7 +30726,7 @@
         <v>44596</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30786,7 +30788,7 @@
         <v>44936</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30843,7 +30845,7 @@
         <v>45246.41783564815</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30900,7 +30902,7 @@
         <v>45772.6652662037</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30962,7 +30964,7 @@
         <v>44575</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31019,7 +31021,7 @@
         <v>45414.5519212963</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31081,7 +31083,7 @@
         <v>45453.54733796296</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31138,7 +31140,7 @@
         <v>45453.55123842593</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31195,7 +31197,7 @@
         <v>45310.41982638889</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31252,7 +31254,7 @@
         <v>45771.44005787037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31314,7 +31316,7 @@
         <v>45546</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31371,7 +31373,7 @@
         <v>45229</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31428,7 +31430,7 @@
         <v>45272</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31490,7 +31492,7 @@
         <v>45030.62740740741</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31547,7 +31549,7 @@
         <v>45030</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31604,7 +31606,7 @@
         <v>45188</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31661,7 +31663,7 @@
         <v>45790</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31718,7 +31720,7 @@
         <v>45603.49528935185</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31775,7 +31777,7 @@
         <v>45400</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31837,7 +31839,7 @@
         <v>45274</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31894,7 +31896,7 @@
         <v>45268</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31951,7 +31953,7 @@
         <v>44754.57658564814</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32008,7 +32010,7 @@
         <v>45550.68804398148</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32065,7 +32067,7 @@
         <v>45792.42109953704</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32122,7 +32124,7 @@
         <v>45771.69168981481</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32179,7 +32181,7 @@
         <v>45792.42542824074</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32236,7 +32238,7 @@
         <v>45259</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32293,7 +32295,7 @@
         <v>44439.97621527778</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32355,7 +32357,7 @@
         <v>45794.82150462963</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32412,7 +32414,7 @@
         <v>45174</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32469,7 +32471,7 @@
         <v>45174.87439814815</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32526,7 +32528,7 @@
         <v>45053.82055555555</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32583,7 +32585,7 @@
         <v>45796</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32640,7 +32642,7 @@
         <v>45796.36326388889</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32702,7 +32704,7 @@
         <v>44860</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32759,7 +32761,7 @@
         <v>45678.57503472222</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32816,7 +32818,7 @@
         <v>45796</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32873,7 +32875,7 @@
         <v>44597</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32930,7 +32932,7 @@
         <v>45014</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32987,7 +32989,7 @@
         <v>44936</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33044,7 +33046,7 @@
         <v>45731.60166666667</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33101,7 +33103,7 @@
         <v>45794.81583333333</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33158,7 +33160,7 @@
         <v>45797.39876157408</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33215,7 +33217,7 @@
         <v>45796.49842592593</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33272,7 +33274,7 @@
         <v>45363.58979166667</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33329,7 +33331,7 @@
         <v>45794.81730324074</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33386,7 +33388,7 @@
         <v>45794.82583333334</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33443,7 +33445,7 @@
         <v>45628.56513888889</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33505,7 +33507,7 @@
         <v>45723.65960648148</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33562,7 +33564,7 @@
         <v>44455.68550925926</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33619,7 +33621,7 @@
         <v>45794.82371527778</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33676,7 +33678,7 @@
         <v>44588</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33733,7 +33735,7 @@
         <v>44897</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33795,7 +33797,7 @@
         <v>45794.81975694445</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33852,7 +33854,7 @@
         <v>45769.62891203703</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33914,7 +33916,7 @@
         <v>45798.45043981481</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33971,7 +33973,7 @@
         <v>44935</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34028,7 +34030,7 @@
         <v>44935.60138888889</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34090,7 +34092,7 @@
         <v>44950</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34147,7 +34149,7 @@
         <v>44494</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34204,7 +34206,7 @@
         <v>44896</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34266,7 +34268,7 @@
         <v>44858</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34328,7 +34330,7 @@
         <v>45436.41305555555</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34390,7 +34392,7 @@
         <v>45758.56946759259</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34452,7 +34454,7 @@
         <v>44644</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34514,7 +34516,7 @@
         <v>44084</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34571,7 +34573,7 @@
         <v>44454</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34633,7 +34635,7 @@
         <v>45110.56027777777</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34690,7 +34692,7 @@
         <v>45110</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34747,7 +34749,7 @@
         <v>45798.59671296296</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34809,7 +34811,7 @@
         <v>45274.43547453704</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34866,7 +34868,7 @@
         <v>45671.59245370371</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34928,7 +34930,7 @@
         <v>45408</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34990,7 +34992,7 @@
         <v>45558.54422453704</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35047,7 +35049,7 @@
         <v>45558</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35104,7 +35106,7 @@
         <v>45096</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35166,7 +35168,7 @@
         <v>45565.5381712963</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35223,7 +35225,7 @@
         <v>45798.66228009259</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35285,7 +35287,7 @@
         <v>45532</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35342,7 +35344,7 @@
         <v>45202</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35404,7 +35406,7 @@
         <v>44859</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35466,7 +35468,7 @@
         <v>45554.28857638889</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35523,7 +35525,7 @@
         <v>45121</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35585,7 +35587,7 @@
         <v>45336</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35642,7 +35644,7 @@
         <v>44582</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35699,7 +35701,7 @@
         <v>45442.6052199074</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35761,7 +35763,7 @@
         <v>45442.60829861111</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35823,7 +35825,7 @@
         <v>45442.68033564815</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35885,7 +35887,7 @@
         <v>45722.46946759259</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35942,7 +35944,7 @@
         <v>45183.65135416666</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35999,7 +36001,7 @@
         <v>45183.65233796297</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36056,7 +36058,7 @@
         <v>45803.43815972222</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36113,7 +36115,7 @@
         <v>45762.76337962963</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36170,7 +36172,7 @@
         <v>45597.40140046296</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36227,7 +36229,7 @@
         <v>45279.66864583334</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36289,7 +36291,7 @@
         <v>45043</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36346,7 +36348,7 @@
         <v>45736.72646990741</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36403,7 +36405,7 @@
         <v>45071</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36460,7 +36462,7 @@
         <v>45684.4203125</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36522,7 +36524,7 @@
         <v>45678.6377199074</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36579,7 +36581,7 @@
         <v>45509.57052083333</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36636,7 +36638,7 @@
         <v>44889</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36693,7 +36695,7 @@
         <v>44166</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36750,7 +36752,7 @@
         <v>45678.59783564815</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36807,7 +36809,7 @@
         <v>45317</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36869,7 +36871,7 @@
         <v>45804.59579861111</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36931,7 +36933,7 @@
         <v>45369.61550925926</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36988,7 +36990,7 @@
         <v>45202.56994212963</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37045,7 +37047,7 @@
         <v>45145</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37102,7 +37104,7 @@
         <v>45807</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37159,7 +37161,7 @@
         <v>45043</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37216,7 +37218,7 @@
         <v>45215.63990740741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37273,7 +37275,7 @@
         <v>45453.55534722222</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37330,7 +37332,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37392,7 +37394,7 @@
         <v>44936</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37449,7 +37451,7 @@
         <v>45098.37322916667</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37506,7 +37508,7 @@
         <v>44890</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37568,7 +37570,7 @@
         <v>44176</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37630,7 +37632,7 @@
         <v>45769</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37687,7 +37689,7 @@
         <v>45013.63658564815</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37744,7 +37746,7 @@
         <v>45414.39614583334</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37801,7 +37803,7 @@
         <v>44956.54967592593</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37863,7 +37865,7 @@
         <v>45183</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37920,7 +37922,7 @@
         <v>45764.43782407408</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37977,7 +37979,7 @@
         <v>45764.44263888889</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38034,7 +38036,7 @@
         <v>44721</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38091,7 +38093,7 @@
         <v>45117</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38153,7 +38155,7 @@
         <v>44980</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38215,7 +38217,7 @@
         <v>45043</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38277,7 +38279,7 @@
         <v>44096</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38334,7 +38336,7 @@
         <v>45757.66474537037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38391,7 +38393,7 @@
         <v>45763.41083333334</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38453,7 +38455,7 @@
         <v>45758.35732638889</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38510,7 +38512,7 @@
         <v>45217.51479166667</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38567,7 +38569,7 @@
         <v>45240</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38624,7 +38626,7 @@
         <v>45191.39708333334</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38681,7 +38683,7 @@
         <v>45369</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38743,7 +38745,7 @@
         <v>45118</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38800,7 +38802,7 @@
         <v>45813.56320601852</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38862,7 +38864,7 @@
         <v>45715.56964120371</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38924,7 +38926,7 @@
         <v>45733.62203703704</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38986,7 +38988,7 @@
         <v>44536</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39043,7 +39045,7 @@
         <v>44448</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39100,7 +39102,7 @@
         <v>44993</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39162,7 +39164,7 @@
         <v>44803.59099537037</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39219,7 +39221,7 @@
         <v>45178.43909722222</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39281,7 +39283,7 @@
         <v>45817.42607638889</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39338,7 +39340,7 @@
         <v>45153</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39400,7 +39402,7 @@
         <v>44860</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39457,7 +39459,7 @@
         <v>45215</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39514,7 +39516,7 @@
         <v>45096</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39576,7 +39578,7 @@
         <v>45817.64487268519</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39638,7 +39640,7 @@
         <v>45817.41037037037</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39695,7 +39697,7 @@
         <v>44939</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39757,7 +39759,7 @@
         <v>44987.5428587963</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39814,7 +39816,7 @@
         <v>45817.47909722223</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39876,7 +39878,7 @@
         <v>44599</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39933,7 +39935,7 @@
         <v>44999</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39995,7 +39997,7 @@
         <v>44956</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40057,7 +40059,7 @@
         <v>45379</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40114,7 +40116,7 @@
         <v>45049</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40171,7 +40173,7 @@
         <v>45817</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40228,7 +40230,7 @@
         <v>45817</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40285,7 +40287,7 @@
         <v>45330</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40342,7 +40344,7 @@
         <v>45860</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40404,7 +40406,7 @@
         <v>44677</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40461,7 +40463,7 @@
         <v>45219.32268518519</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40518,7 +40520,7 @@
         <v>45468.82832175926</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40575,7 +40577,7 @@
         <v>45126</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40632,7 +40634,7 @@
         <v>45126</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40689,7 +40691,7 @@
         <v>45657.94784722223</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40751,7 +40753,7 @@
         <v>44384</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40813,7 +40815,7 @@
         <v>45201.63637731481</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40870,7 +40872,7 @@
         <v>44980.48200231481</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40932,7 +40934,7 @@
         <v>45820.39863425926</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40989,7 +40991,7 @@
         <v>45820.37113425926</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41046,7 +41048,7 @@
         <v>45741.63417824074</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41108,7 +41110,7 @@
         <v>45268</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41165,7 +41167,7 @@
         <v>44907.66710648148</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41222,7 +41224,7 @@
         <v>45114</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41284,7 +41286,7 @@
         <v>45114</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41341,7 +41343,7 @@
         <v>44742</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41398,7 +41400,7 @@
         <v>44163</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41455,7 +41457,7 @@
         <v>45824.31493055556</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41517,7 +41519,7 @@
         <v>44469</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41574,7 +41576,7 @@
         <v>45729</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41636,7 +41638,7 @@
         <v>45723.66629629629</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41693,7 +41695,7 @@
         <v>45867.7115625</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41750,7 +41752,7 @@
         <v>45824.45221064815</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41807,7 +41809,7 @@
         <v>45824.32293981482</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41869,7 +41871,7 @@
         <v>45614.46292824074</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41931,7 +41933,7 @@
         <v>44679</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41993,7 +41995,7 @@
         <v>45317</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42055,7 +42057,7 @@
         <v>45365</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42117,7 +42119,7 @@
         <v>45359.68173611111</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42174,7 +42176,7 @@
         <v>45405</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42231,7 +42233,7 @@
         <v>45769.45751157407</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42293,7 +42295,7 @@
         <v>44923.67971064815</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42355,7 +42357,7 @@
         <v>44880.44351851852</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42417,7 +42419,7 @@
         <v>44930</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42474,7 +42476,7 @@
         <v>44974</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42536,7 +42538,7 @@
         <v>44221</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42593,7 +42595,7 @@
         <v>45832</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42650,7 +42652,7 @@
         <v>44414</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42707,7 +42709,7 @@
         <v>45873</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42764,7 +42766,7 @@
         <v>45048</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42826,7 +42828,7 @@
         <v>44936</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42888,7 +42890,7 @@
         <v>44936</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42950,7 +42952,7 @@
         <v>45833.65659722222</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43007,7 +43009,7 @@
         <v>45043</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43064,7 +43066,7 @@
         <v>45716.57158564815</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43121,7 +43123,7 @@
         <v>45833.40451388889</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43183,7 +43185,7 @@
         <v>45092.35369212963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43240,7 +43242,7 @@
         <v>45106</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43297,7 +43299,7 @@
         <v>45833.4374537037</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43354,7 +43356,7 @@
         <v>45832</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43411,7 +43413,7 @@
         <v>45832</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43468,7 +43470,7 @@
         <v>44970.65930555556</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43525,7 +43527,7 @@
         <v>45747.44502314815</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43582,7 +43584,7 @@
         <v>45769.57802083333</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43639,7 +43641,7 @@
         <v>45769</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43696,7 +43698,7 @@
         <v>45178.4275</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43758,7 +43760,7 @@
         <v>44865</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43815,7 +43817,7 @@
         <v>45770.84420138889</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43872,7 +43874,7 @@
         <v>44488</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43929,7 +43931,7 @@
         <v>44994.41405092592</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43986,7 +43988,7 @@
         <v>45028</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44043,7 +44045,7 @@
         <v>45442.38490740741</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44100,7 +44102,7 @@
         <v>45727.64337962963</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44162,7 +44164,7 @@
         <v>44908</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44219,7 +44221,7 @@
         <v>44943.56112268518</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44281,7 +44283,7 @@
         <v>44943</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44343,7 +44345,7 @@
         <v>45408.49326388889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44400,7 +44402,7 @@
         <v>45106</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44457,7 +44459,7 @@
         <v>45211.52641203703</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44514,7 +44516,7 @@
         <v>45211.52895833334</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44571,7 +44573,7 @@
         <v>45678.57045138889</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44628,7 +44630,7 @@
         <v>45678.58166666667</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44685,7 +44687,7 @@
         <v>45716.40918981482</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44747,7 +44749,7 @@
         <v>44862</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44809,7 +44811,7 @@
         <v>45684.41622685185</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44871,7 +44873,7 @@
         <v>45317</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44933,7 +44935,7 @@
         <v>45215.63818287037</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44990,7 +44992,7 @@
         <v>45043.49425925926</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45047,7 +45049,7 @@
         <v>44236</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45109,7 +45111,7 @@
         <v>44427.49322916667</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45166,7 +45168,7 @@
         <v>45436.41847222222</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45228,7 +45230,7 @@
         <v>44805</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45290,7 +45292,7 @@
         <v>45204</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45352,7 +45354,7 @@
         <v>45201.56556712963</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45409,7 +45411,7 @@
         <v>45132</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45471,7 +45473,7 @@
         <v>45356.64872685185</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45528,7 +45530,7 @@
         <v>44504</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45590,7 +45592,7 @@
         <v>44361</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45647,7 +45649,7 @@
         <v>45836</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45704,7 +45706,7 @@
         <v>45373.48878472222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45761,7 +45763,7 @@
         <v>45527.43385416667</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45818,7 +45820,7 @@
         <v>45215</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45875,7 +45877,7 @@
         <v>44992</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45932,7 +45934,7 @@
         <v>45838.683125</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45989,7 +45991,7 @@
         <v>45334</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46051,7 +46053,7 @@
         <v>44641.78332175926</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46108,7 +46110,7 @@
         <v>45252</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46165,7 +46167,7 @@
         <v>45369.61841435185</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46222,7 +46224,7 @@
         <v>45141</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46284,7 +46286,7 @@
         <v>44945.58030092593</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46341,7 +46343,7 @@
         <v>45673</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46398,7 +46400,7 @@
         <v>45128</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46455,7 +46457,7 @@
         <v>45758.60146990741</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46512,7 +46514,7 @@
         <v>45686.61590277778</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46574,7 +46576,7 @@
         <v>45741.51940972222</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46636,7 +46638,7 @@
         <v>45874</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46693,7 +46695,7 @@
         <v>45883.5738425926</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46750,7 +46752,7 @@
         <v>45883.59934027777</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46807,7 +46809,7 @@
         <v>45881</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46869,7 +46871,7 @@
         <v>45096</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46931,7 +46933,7 @@
         <v>45881</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46988,7 +46990,7 @@
         <v>44218</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47050,7 +47052,7 @@
         <v>44936</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47107,7 +47109,7 @@
         <v>44312</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47169,7 +47171,7 @@
         <v>45883.63648148148</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47226,7 +47228,7 @@
         <v>45883.69113425926</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47283,7 +47285,7 @@
         <v>45736.32394675926</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47340,7 +47342,7 @@
         <v>45840.65592592592</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47397,7 +47399,7 @@
         <v>45883.58756944445</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47454,7 +47456,7 @@
         <v>45840.65777777778</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47511,7 +47513,7 @@
         <v>45840.66978009259</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47568,7 +47570,7 @@
         <v>45840.66780092593</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47625,7 +47627,7 @@
         <v>45638</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47687,7 +47689,7 @@
         <v>45883.58974537037</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47749,7 +47751,7 @@
         <v>45883.74664351852</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47806,7 +47808,7 @@
         <v>45006</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47868,7 +47870,7 @@
         <v>45840.6602199074</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47925,7 +47927,7 @@
         <v>45246.41627314815</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47982,7 +47984,7 @@
         <v>45246</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48039,7 +48041,7 @@
         <v>45673.49019675926</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48101,7 +48103,7 @@
         <v>45582.98494212963</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48163,7 +48165,7 @@
         <v>45174</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48220,7 +48222,7 @@
         <v>45174</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48277,7 +48279,7 @@
         <v>45886</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48334,7 +48336,7 @@
         <v>45886.65516203704</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48391,7 +48393,7 @@
         <v>45457.59425925926</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48448,7 +48450,7 @@
         <v>45884.57759259259</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48510,7 +48512,7 @@
         <v>45884.60458333333</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48572,7 +48574,7 @@
         <v>45845.65797453704</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48634,7 +48636,7 @@
         <v>45680</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48696,7 +48698,7 @@
         <v>45678.44092592593</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48753,7 +48755,7 @@
         <v>45386</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48810,7 +48812,7 @@
         <v>45092.36790509259</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48867,7 +48869,7 @@
         <v>44981</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48929,7 +48931,7 @@
         <v>45414.3944212963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48986,7 +48988,7 @@
         <v>45254</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49048,7 +49050,7 @@
         <v>45027</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49105,7 +49107,7 @@
         <v>45425.89037037037</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49162,7 +49164,7 @@
         <v>45581.62796296296</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49219,7 +49221,7 @@
         <v>45091</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49281,7 +49283,7 @@
         <v>45369.62108796297</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49338,7 +49340,7 @@
         <v>44131</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49395,7 +49397,7 @@
         <v>45071</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49452,7 +49454,7 @@
         <v>45887</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49509,7 +49511,7 @@
         <v>45884.68263888889</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49566,7 +49568,7 @@
         <v>45887</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49623,7 +49625,7 @@
         <v>45845.45563657407</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49685,7 +49687,7 @@
         <v>45043</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49742,7 +49744,7 @@
         <v>45884.45916666667</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49804,7 +49806,7 @@
         <v>45771.76943287037</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49861,7 +49863,7 @@
         <v>44825</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49918,7 +49920,7 @@
         <v>45888.61847222222</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49980,7 +49982,7 @@
         <v>45442.61221064815</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50042,7 +50044,7 @@
         <v>44358</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50104,7 +50106,7 @@
         <v>45008</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50161,7 +50163,7 @@
         <v>45888.46922453704</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50218,7 +50220,7 @@
         <v>45888.4712037037</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50275,7 +50277,7 @@
         <v>45645.27707175926</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50332,7 +50334,7 @@
         <v>45888.4658449074</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50394,7 +50396,7 @@
         <v>45763.64096064815</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50456,7 +50458,7 @@
         <v>45699.65944444444</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50518,7 +50520,7 @@
         <v>45339.5277199074</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50575,7 +50577,7 @@
         <v>45758.60465277778</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50632,7 +50634,7 @@
         <v>45758.61055555556</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50689,7 +50691,7 @@
         <v>44237</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50751,7 +50753,7 @@
         <v>45797</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50813,7 +50815,7 @@
         <v>45891.60103009259</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50870,7 +50872,7 @@
         <v>45889</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50927,7 +50929,7 @@
         <v>45877</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50984,7 +50986,7 @@
         <v>45877</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51041,7 +51043,7 @@
         <v>45891.59726851852</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51098,7 +51100,7 @@
         <v>45891.59938657407</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51155,7 +51157,7 @@
         <v>45796.44922453703</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51217,7 +51219,7 @@
         <v>45030</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51274,7 +51276,7 @@
         <v>44433</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51336,7 +51338,7 @@
         <v>45030.62916666667</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51393,7 +51395,7 @@
         <v>44939</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51450,7 +51452,7 @@
         <v>45093.54811342592</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51507,7 +51509,7 @@
         <v>45891.60346064815</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51564,7 +51566,7 @@
         <v>45798.60880787037</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51626,7 +51628,7 @@
         <v>44177</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51683,7 +51685,7 @@
         <v>44177</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51740,7 +51742,7 @@
         <v>45889</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51797,7 +51799,7 @@
         <v>45093</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51859,7 +51861,7 @@
         <v>44992</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51916,7 +51918,7 @@
         <v>45012</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51973,7 +51975,7 @@
         <v>44980</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52035,7 +52037,7 @@
         <v>45771.66951388889</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52097,7 +52099,7 @@
         <v>45153.36402777778</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52159,7 +52161,7 @@
         <v>45709.4119212963</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52221,7 +52223,7 @@
         <v>45453.52299768518</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52278,7 +52280,7 @@
         <v>45252.91344907408</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52335,7 +52337,7 @@
         <v>45636.45025462963</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52392,7 +52394,7 @@
         <v>45636.4737962963</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52449,7 +52451,7 @@
         <v>44243</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52506,7 +52508,7 @@
         <v>45731.59962962963</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52563,7 +52565,7 @@
         <v>44867</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52625,7 +52627,7 @@
         <v>45373.72511574074</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52682,7 +52684,7 @@
         <v>44980</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52744,7 +52746,7 @@
         <v>45016.64986111111</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52806,7 +52808,7 @@
         <v>44573</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52863,7 +52865,7 @@
         <v>45254</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52925,7 +52927,7 @@
         <v>45742.32277777778</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52982,7 +52984,7 @@
         <v>44333</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53039,7 +53041,7 @@
         <v>44225</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53101,7 +53103,7 @@
         <v>45330</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53158,7 +53160,7 @@
         <v>45497</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53215,7 +53217,7 @@
         <v>44861</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53277,7 +53279,7 @@
         <v>44607</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53334,7 +53336,7 @@
         <v>45629.7202662037</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53391,7 +53393,7 @@
         <v>45716.37259259259</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53453,7 +53455,7 @@
         <v>45106</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53510,7 +53512,7 @@
         <v>45706.54204861111</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -53567,7 +53569,7 @@
         <v>45706.54572916667</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45012</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45798.58304398148</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>44896</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>44299</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>44264</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>45579</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45645.27462962963</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45012</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45139</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>45441</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45568</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>45880.62738425926</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>45886.64045138889</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>45783.4903125</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>45133</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>45604</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>44076</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>45421</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45723.61545138889</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>45742.41269675926</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>45832.36966435185</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44578</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>44412</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45723.59275462963</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45568</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45723.57098379629</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>45881.41636574074</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>45731.65016203704</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>45421</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45042</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44977</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>45604</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>45832.31648148148</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>45833.56057870371</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>44931</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45884.4946875</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>45764.47825231482</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>45013.77040509259</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>45086</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>45583</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45441.33914351852</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45012</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>44789</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>45258.56491898148</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45568.44137731481</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>45832.3365625</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>45733.45780092593</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>45694</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>45772.6571412037</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>45758.54390046297</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>44454</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>45583</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>45086</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44308</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>44480</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>44426</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>44524</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44452</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>44490</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>45723.66964120371</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45583.3479050926</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>45770.63996527778</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>45408</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>45763.60795138889</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>45783.61222222223</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>45376</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>45362</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44886.54420138889</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>45796</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44089</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>45201</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>45421</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>45096</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>45716.5672337963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>45723.55663194445</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45583</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>45201</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>45251</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>45580</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>44777.49493055556</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>45117</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45369</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44354</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>45702.76395833334</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>45742.43848379629</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>45174</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>45056</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>45042</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>45747.58131944444</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>45583</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45744</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45744.41443287037</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>45411.57177083333</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>44132</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>45348.68336805556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44151</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>44219</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>44158</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>44211</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>44211</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>44146</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>44456</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>44456</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>44301</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>44307</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>44582.4696875</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44530</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>44211</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>44217</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>44214</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>44176</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44107</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>44502</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>44622</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44537</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44218</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>44825.47923611111</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>44340.80107638889</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>44728.82296296296</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>44279</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>44739</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>44368</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>44719.43086805556</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>44169</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>44169</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>44216</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>44258</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>44370</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>44440</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>44503</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>44368</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>44448</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>44306</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>44441</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>44301</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>44865</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>44294</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>44286</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>44524.67836805555</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>44385</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>44696.775</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>44390</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>44432</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>44433</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44447</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>44494</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>44368.88704861111</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>44340</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>44333</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>44671</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>44713</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>44813</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44530</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44515</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>44169</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>44571</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>44442.66228009259</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>44208</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>44475</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>44475</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>44393</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>44272</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>44630.3978587963</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>44371</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>44371</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>44124.63679398148</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>44362</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>44211</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>44211</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>44524</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>44271.81282407408</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>44447</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>44530</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>44313</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>44503</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>44300</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>44300</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>44459</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>44446</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>44321</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>44879.39153935185</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>44459</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>44475</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>44475</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>44249</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>44574</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>44686</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>44602</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>44886.47697916667</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>44098</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>44348</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>44889.55255787037</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>44726</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>44328</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>44452</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>44449</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44152</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44825</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44874</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>44219</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>44162</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>44487</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44358</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>44596</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>44756</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44468</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>44208</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44252</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>44441</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>44137</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>44137</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>44432</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>44452</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>44272</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>44582</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>44740</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>44825</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>44630</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>44344.49251157408</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>44741.57063657408</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>44363</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         <v>44313</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>44270</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44302</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44730</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>44354.45140046296</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>44279</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>44445</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44557</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>44362</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>44363</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>44869.4575</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>44865</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>45072</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>44862</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>45043</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44578</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>45771.69168981481</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>45202</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>44326</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>45369.61550925926</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>45532</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>44326</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>44326</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>45678.57045138889</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45709.4119212963</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45405</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45363.58979166667</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45742.32277777778</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>45106</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>45379</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>45758.56056712963</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18620,7 +18620,7 @@
         <v>45268</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>45736.72646990741</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45043.53597222222</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>45215.63818287037</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>45240</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>44805</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>45709.42859953704</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44825</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45118</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>45369.62108796297</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>45336</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45741.63417824074</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45092</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>45037</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>45644</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>45414.3944212963</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>45629.7202662037</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>45763.64096064815</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>45339.5277199074</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45373.73894675926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45408.49326388889</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44862</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>45254</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45726.91224537037</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>44860</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>45777.61991898148</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>45741.53599537037</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45782.66719907407</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>44607</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>45782.659375</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>44414</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>44322</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>45386</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>45783</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>45784</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>44462</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45784.62866898148</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45783.68689814815</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44950</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>45092.35266203704</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>45783.48681712963</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>45006</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>44433</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45030.62740740741</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>45030</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45317</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>45359.68173611111</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>45334</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>45128</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>44861</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>45432.6291550926</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>45425.89037037037</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>44994.41405092592</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>45092.36126157407</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>44880.44351851852</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>45110.56027777777</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>45110</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>45317</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>45786.36358796297</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45671.62931712963</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>44939</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>45278</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22249,7 +22249,7 @@
         <v>44858</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22311,7 +22311,7 @@
         <v>45117</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44236</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44163</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45132</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>45587.58498842592</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>45093</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45453.54733796296</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>45453.55123842593</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>45370</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>44957</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>45670</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>44494</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>44974.564375</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45771.44005787037</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45786</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>45789.42597222222</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>44565</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45310.41982638889</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>45790</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>44084</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>45595</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44361</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>45637</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>44488</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>45593.59819444444</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45673.49019675926</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>45096</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>45126</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>45126</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>45141</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>45792.42109953704</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45792.42542824074</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>45145</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45400</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>45671.59245370371</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45403.86942129629</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>44935.64165509259</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>45114</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>45114</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>45706.47790509259</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45678.57503472222</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>45794.82583333334</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45794.81975694445</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45794.82150462963</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>45266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>45794.81730324074</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>45796.49842592593</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45490.72372685185</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44930</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45527.43385416667</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45796</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>45758.36203703703</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45794.81583333333</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45546</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>45356.64872685185</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45794.82371527778</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44936</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45796</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45796.36326388889</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45106</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>45259</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45092.35369212963</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45336</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45798.59671296296</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45266.69091435185</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>45798.66228009259</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>45797.39876157408</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44890</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>45798.45043981481</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>45191</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>44168</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>45033</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>45565.5381712963</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>44536</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>45414.5519212963</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>44596</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>45408</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>44573</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45554.28857638889</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45722.46946759259</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>45803.43815972222</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45804.59579861111</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44582</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>45723.65960648148</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>45762.76337962963</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>45550.68804398148</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>45202.56994212963</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>45365</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>44176</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45727.6683449074</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>45442.6052199074</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>45442.60829861111</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>45159</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45432.54622685185</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27891,7 +27891,7 @@
         <v>45807</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>45043</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>45369</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>44641.78332175926</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45183.65135416666</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>45183.65233796297</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>44936</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>45673</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>45178.43909722222</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>45053.36554398148</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45217.51479166667</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>45636.4737962963</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>45030</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>44889</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>45313</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45028</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>45716.40918981482</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>45121</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>44910</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>44181</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45860</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>45817</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         <v>44131</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>45106</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>44181</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>45657.94784722223</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>45817</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>45817.64487268519</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>45201.63637731481</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45817.47909722223</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>45817.41037037037</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>45820.37113425926</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>45205.3119212963</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>45205.35753472222</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>45684.41622685185</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>44427.49322916667</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>45820.39863425926</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>44679</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>45369.61841435185</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>45566.46769675926</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>45215</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>45824.32293981482</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>45678.57731481481</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>44936.46326388889</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45824.45221064815</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>44974.65918981482</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>45758.60146990741</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45824.31493055556</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>45761.59716435185</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>44630</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45211.52641203703</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>45867.7115625</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>44943.56112268518</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45579.56570601852</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>45527.40489583334</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>45174</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>45174</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44448</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>44651.42819444444</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>45394</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>45453.52299768518</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>45238.33091435185</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>45446.57724537037</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>45446.5790625</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>44455</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>45832</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45261.50924768519</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>45049</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>44943</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>45832</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>45832</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32043,7 +32043,7 @@
         <v>45764.43002314815</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>45833.4374537037</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>45833.40451388889</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45091</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>45558.54422453704</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>45254.54892361111</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>45112</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45215</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>44677</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>45188</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45680</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45715.5837962963</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45723.66629629629</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>45764.47553240741</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>45699.75583333334</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>44834</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>45833.65659722222</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33037,7 +33037,7 @@
         <v>45317</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44741</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45008.66204861111</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>45838.683125</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>45204</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33337,7 +33337,7 @@
         <v>45468.82832175926</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>45836</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45769.62891203703</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
         <v>45401.46640046296</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33575,7 +33575,7 @@
         <v>44965</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45014</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>44504</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>44956.54967592593</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>45583.55850694444</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45356.64724537037</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45758.35732638889</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>45274</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>45840.65777777778</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>45840.65592592592</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34160,7 +34160,7 @@
         <v>45636.45989583333</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>45840.6602199074</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45252</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>45614.46292824074</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>44279</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>45191.39708333334</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>45758.56946759259</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>44719.43200231482</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34626,7 +34626,7 @@
         <v>45840.66780092593</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34683,7 +34683,7 @@
         <v>45254</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>45840.66978009259</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34802,7 +34802,7 @@
         <v>45883.58974537037</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>45883.63648148148</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>45883.69113425926</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>45883.74664351852</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>45246.41627314815</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>45246</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>44455.68550925926</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>44956</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>45719.4522337963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>44956</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45716.45121527778</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>45252.91344907408</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>45272</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35568,7 +35568,7 @@
         <v>45769.40231481481</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>44974</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
         <v>45581.62796296296</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>45883.5738425926</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>45399.62587962963</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>45874</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35925,7 +35925,7 @@
         <v>44573.38521990741</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35982,7 +35982,7 @@
         <v>45317</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>45884.45916666667</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>45881</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>45883.58756944445</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
         <v>45414.39614583334</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36277,7 +36277,7 @@
         <v>45884.57759259259</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>45884.60458333333</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>45884.68263888889</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36458,7 +36458,7 @@
         <v>44249</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36515,7 +36515,7 @@
         <v>45881</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>45883.59934027777</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>45645.27707175926</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>44998</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>45887</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>44862</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36862,7 +36862,7 @@
         <v>44512</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>44970.65930555556</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>45678.44092592593</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>45716.37259259259</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>45266.66998842593</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44993</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>44980</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45030</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37338,7 +37338,7 @@
         <v>45886</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>45886.65516203704</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>44859</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>44312</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44469</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>45330</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>45386.35986111111</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45266</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>45888.4712037037</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>45888.4658449074</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45887</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         <v>44851</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38042,7 +38042,7 @@
         <v>45845.45563657407</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>44243</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>45888.46922453704</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>45888.61847222222</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>45769.57802083333</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>45845.65797453704</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45797</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44721</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>45114</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>44221</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45106</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45763.41083333334</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45877</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>45043</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38870,7 +38870,7 @@
         <v>45889</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>45178.4275</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45877</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45798.60880787037</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>45889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>45796.44922453703</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>44384</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>44767</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45016.67141203704</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45629.67508101852</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45629.67931712963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45098.37322916667</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>44805</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45096</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>45117</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>45736.31508101852</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>45891.60346064815</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>45582.98494212963</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>45268</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>45894.55337962963</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>45736.32394675926</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40117,7 +40117,7 @@
         <v>44599</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>45894.41133101852</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45894.55216435185</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40298,7 +40298,7 @@
         <v>45873</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>45727.64337962963</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40417,7 +40417,7 @@
         <v>45891.60103009259</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>45817.42607638889</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>44597</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>44225</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>45894.4825</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40712,7 +40712,7 @@
         <v>45597.40140046296</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>45891.59726851852</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
         <v>45891.59938657407</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>45469.43265046296</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40940,7 +40940,7 @@
         <v>45726.90959490741</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40997,7 +40997,7 @@
         <v>45678.59783564815</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>44754.57658564814</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41111,7 +41111,7 @@
         <v>45895.42582175926</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41173,7 +41173,7 @@
         <v>44739.52209490741</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>44713.58678240741</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>45121</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>44970.44197916667</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45813.56320601852</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>45895.373125</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>45896.66505787037</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45896.66944444444</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45896.81087962963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45895.3627662037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>45747.44502314815</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>45201.56556712963</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45215.63990740741</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>45106</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45030.61489583334</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45030.61744212963</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45638</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>44853.64244212963</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45898.86685185185</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>44742</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45898.58202546297</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>44999</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>45053.82055555555</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>44181</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45043.49425925926</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45110</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>44826</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>45442.38490740741</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>45671.5678125</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>44908</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>44897</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>45642</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43057,7 +43057,7 @@
         <v>45442.61221064815</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43119,7 +43119,7 @@
         <v>45733.62203703704</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43181,7 +43181,7 @@
         <v>45686.61590277778</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43243,7 +43243,7 @@
         <v>45008.62458333333</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>44980</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>45702.76590277778</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43424,7 +43424,7 @@
         <v>45013.63658564815</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43481,7 +43481,7 @@
         <v>45229</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         <v>44867</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>44105</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>45764.44263888889</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45442.68033564815</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>44957</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45716.57158564815</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>44364.78170138889</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45043</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>44333</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45715.56964120371</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>44746</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>44880</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>44992</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44304,7 +44304,7 @@
         <v>44861</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44366,7 +44366,7 @@
         <v>44166</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
         <v>44575</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44480,7 +44480,7 @@
         <v>44957</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>44945.58030092593</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>45008</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>45093.54811342592</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>45729</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>45110</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44837,7 +44837,7 @@
         <v>45274.43547453704</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>44936</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>44936</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45030</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>44177</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>44177</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45733.44431712963</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45271,7 +45271,7 @@
         <v>44358</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45333,7 +45333,7 @@
         <v>44096</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>45772.6652662037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45452,7 +45452,7 @@
         <v>45254</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>45077</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>45509.57052083333</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>45174</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>45174.87439814815</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45742,7 +45742,7 @@
         <v>45043</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>44992</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45183</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45913,7 +45913,7 @@
         <v>44155</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45970,7 +45970,7 @@
         <v>45771.76943287037</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45014</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45614.52813657407</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46146,7 +46146,7 @@
         <v>45246.41783564815</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>45049.34974537037</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46260,7 +46260,7 @@
         <v>45049.35048611111</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>45527.41597222222</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>44939</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46431,7 +46431,7 @@
         <v>45012.79270833333</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46488,7 +46488,7 @@
         <v>44218</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46550,7 +46550,7 @@
         <v>45453.55534722222</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46607,7 +46607,7 @@
         <v>45022.34695601852</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46664,7 +46664,7 @@
         <v>44987.5428587963</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46721,7 +46721,7 @@
         <v>45237</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46783,7 +46783,7 @@
         <v>45769.45751157407</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45769</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45769</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>44454</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45733.43347222222</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47083,7 +47083,7 @@
         <v>45770.84420138889</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45090.90752314815</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>44096</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>44860</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>44783</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>44137</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47430,7 +47430,7 @@
         <v>45741.51940972222</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47492,7 +47492,7 @@
         <v>44439.97621527778</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         <v>44147</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>45706.42958333333</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>45090</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47730,7 +47730,7 @@
         <v>44896</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45048</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>44900</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47916,7 +47916,7 @@
         <v>45520.52375</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>44083</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48030,7 +48030,7 @@
         <v>45769</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48087,7 +48087,7 @@
         <v>45356.66037037037</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>44286.88952546296</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>45043</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48258,7 +48258,7 @@
         <v>44897</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>44928.45552083333</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>45071</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>44923.67971064815</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48501,7 +48501,7 @@
         <v>45731.59962962963</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48558,7 +48558,7 @@
         <v>44151.53271990741</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48615,7 +48615,7 @@
         <v>45699</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45279.66864583334</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>44907.66710648148</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>44588</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45435</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45547.64484953704</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48967,7 +48967,7 @@
         <v>44237</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49029,7 +49029,7 @@
         <v>45657.95927083334</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49091,7 +49091,7 @@
         <v>45678.47236111111</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49148,7 +49148,7 @@
         <v>45086.71662037037</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>45436.41847222222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45636.45025462963</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45583.34371527778</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>44783</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49448,7 +49448,7 @@
         <v>45071</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45731.60166666667</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45716.39159722222</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45096</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>45153.36402777778</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>45117</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>45757.66474537037</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         <v>44980</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49924,7 +49924,7 @@
         <v>45093</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49981,7 +49981,7 @@
         <v>44974</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50043,7 +50043,7 @@
         <v>44980.48200231481</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>44981</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50167,7 +50167,7 @@
         <v>44966.57550925926</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50229,7 +50229,7 @@
         <v>45030.62916666667</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50348,7 +50348,7 @@
         <v>44977.57584490741</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         <v>44433</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50467,7 +50467,7 @@
         <v>45721.51255787037</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50524,7 +50524,7 @@
         <v>45721.51346064815</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>44644</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50643,7 +50643,7 @@
         <v>45012</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50700,7 +50700,7 @@
         <v>44652</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50757,7 +50757,7 @@
         <v>45076</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>45706.49520833333</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50876,7 +50876,7 @@
         <v>45706.54385416667</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50933,7 +50933,7 @@
         <v>45048</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>45121</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51052,7 +51052,7 @@
         <v>44803.59099537037</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51109,7 +51109,7 @@
         <v>45678.58166666667</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51166,7 +51166,7 @@
         <v>45771.66951388889</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51228,7 +51228,7 @@
         <v>45769.41631944444</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51290,7 +51290,7 @@
         <v>45628.56513888889</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51352,7 +51352,7 @@
         <v>44159.36447916667</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51409,7 +51409,7 @@
         <v>45436.41305555555</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51471,7 +51471,7 @@
         <v>45758.60465277778</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51528,7 +51528,7 @@
         <v>45758.61055555556</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51585,7 +51585,7 @@
         <v>45699.65944444444</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51647,7 +51647,7 @@
         <v>45092.36790509259</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51704,7 +51704,7 @@
         <v>45535.91413194445</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51761,7 +51761,7 @@
         <v>45373.48878472222</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51818,7 +51818,7 @@
         <v>45219.32268518519</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51875,7 +51875,7 @@
         <v>45330</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51932,7 +51932,7 @@
         <v>45386.32806712963</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51994,7 +51994,7 @@
         <v>45442.67793981481</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52056,7 +52056,7 @@
         <v>45723.67724537037</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52113,7 +52113,7 @@
         <v>45747.59501157407</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52175,7 +52175,7 @@
         <v>45027</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52232,7 +52232,7 @@
         <v>45373.72511574074</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52289,7 +52289,7 @@
         <v>44935</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52346,7 +52346,7 @@
         <v>45558</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52403,7 +52403,7 @@
         <v>44935.60138888889</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>45478.47236111111</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52527,7 +52527,7 @@
         <v>45118</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>44980</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>44977.63902777778</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52708,7 +52708,7 @@
         <v>45678.6377199074</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52765,7 +52765,7 @@
         <v>45153</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>45603.49528935185</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52884,7 +52884,7 @@
         <v>44936</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52941,7 +52941,7 @@
         <v>45742.31784722222</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52998,7 +52998,7 @@
         <v>45153</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53060,7 +53060,7 @@
         <v>44907.65043981482</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53117,7 +53117,7 @@
         <v>45211.52895833334</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53174,7 +53174,7 @@
         <v>44936</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53231,7 +53231,7 @@
         <v>45016.64986111111</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53293,7 +53293,7 @@
         <v>45129</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53350,7 +53350,7 @@
         <v>45457.59425925926</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53407,7 +53407,7 @@
         <v>45250.5799537037</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53464,7 +53464,7 @@
         <v>45764.43782407408</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -53521,7 +53521,7 @@
         <v>45405</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -53578,7 +53578,7 @@
         <v>45497</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>45684.4203125</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -53697,7 +53697,7 @@
         <v>45706.54204861111</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53754,7 +53754,7 @@
         <v>45706.54572916667</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53811,7 +53811,7 @@
         <v>45310</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45012</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45798.58304398148</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>44896</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>44299</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>44264</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>45579</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45645.27462962963</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45012</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45139</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>45441</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45568</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>45880.62738425926</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>45886.64045138889</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>45783.4903125</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>45133</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>45604</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>44076</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>45421</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45723.61545138889</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>45742.41269675926</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>45832.36966435185</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44578</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>44412</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45723.59275462963</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45568</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45723.57098379629</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>45881.41636574074</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>45731.65016203704</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>45421</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45042</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44977</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>45604</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>45832.31648148148</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>45833.56057870371</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>44931</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45884.4946875</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>45764.47825231482</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>45013.77040509259</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>45086</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>45583</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45441.33914351852</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45012</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>44789</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>45258.56491898148</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45568.44137731481</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>45832.3365625</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>45733.45780092593</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>45694</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>45772.6571412037</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>45758.54390046297</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>44454</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>45583</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>45086</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44308</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>44480</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>44426</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>44524</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44452</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>44490</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>45723.66964120371</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45583.3479050926</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>45770.63996527778</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>45408</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>45763.60795138889</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>45783.61222222223</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>45376</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>45362</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44886.54420138889</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>45796</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44089</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>45201</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>45421</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>45096</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>45716.5672337963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>45723.55663194445</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45583</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>45201</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>45251</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>45580</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>44777.49493055556</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>45117</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45369</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44354</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>45702.76395833334</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>45742.43848379629</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>45174</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>45056</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>45042</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>45747.58131944444</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>45583</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45744</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45744.41443287037</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>45411.57177083333</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>44132</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>45348.68336805556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44151</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>44219</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>44158</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>44211</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>44211</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>44146</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>44456</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>44456</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>44301</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>44307</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>44582.4696875</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44530</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>44211</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>44217</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>44214</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>44176</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44107</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>44502</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>44622</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44537</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44218</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>44825.47923611111</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>44340.80107638889</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>44728.82296296296</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>44279</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>44739</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>44368</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>44719.43086805556</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>44169</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>44169</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>44216</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>44258</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>44370</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>44440</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>44503</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>44368</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>44448</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>44306</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>44441</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>44301</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>44865</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>44294</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>44286</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>44524.67836805555</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>44385</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>44696.775</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>44390</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>44432</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>44433</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44447</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>44494</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>44368.88704861111</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>44340</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>44333</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>44671</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>44713</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>44813</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44530</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44515</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>44169</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>44571</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>44442.66228009259</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>44208</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>44475</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>44475</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>44393</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>44272</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>44630.3978587963</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>44371</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>44371</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>44124.63679398148</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>44362</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>44211</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>44211</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>44524</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>44271.81282407408</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>44447</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>44530</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>44313</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>44503</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>44300</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>44300</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>44459</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>44446</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>44321</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>44879.39153935185</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>44459</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>44475</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>44475</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>44249</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>44574</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>44686</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>44602</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>44886.47697916667</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>44098</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>44348</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>44889.55255787037</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>44726</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>44328</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>44452</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>44449</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44152</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44825</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44874</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>44219</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>44162</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>44487</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44358</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>44596</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>44756</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44468</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>44208</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44252</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>44441</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>44137</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>44137</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>44432</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>44452</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>44272</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>44582</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>44740</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>44825</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>44630</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>44344.49251157408</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>44741.57063657408</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>44363</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         <v>44313</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>44270</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44302</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44730</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>44354.45140046296</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>44279</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>44445</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44557</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>44362</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>44363</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>44869.4575</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>44865</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>45072</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>44862</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>45043</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44578</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>45771.69168981481</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>45202</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>44326</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>45369.61550925926</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>45532</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>44326</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>44326</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>45678.57045138889</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45709.4119212963</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45405</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45363.58979166667</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45742.32277777778</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>45106</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>45379</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>45758.56056712963</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18620,7 +18620,7 @@
         <v>45268</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>45736.72646990741</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45043.53597222222</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>45215.63818287037</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>45240</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>44805</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>45709.42859953704</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44825</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45118</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>45369.62108796297</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>45336</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45741.63417824074</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45092</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>45037</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>45644</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>45414.3944212963</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>45629.7202662037</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>45763.64096064815</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>45339.5277199074</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45373.73894675926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45408.49326388889</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44862</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>45254</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45726.91224537037</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>44860</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>45777.61991898148</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>45741.53599537037</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45782.66719907407</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>44607</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>45782.659375</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>44414</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>44322</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>45386</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>45783</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>45784</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>44462</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45784.62866898148</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45783.68689814815</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44950</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>45092.35266203704</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>45783.48681712963</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>45006</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>44433</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45030.62740740741</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>45030</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45317</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>45359.68173611111</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>45334</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>45128</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>44861</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>45432.6291550926</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>45425.89037037037</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>44994.41405092592</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>45092.36126157407</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>44880.44351851852</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>45110.56027777777</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>45110</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>45317</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>45786.36358796297</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45671.62931712963</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>44939</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>45278</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22249,7 +22249,7 @@
         <v>44858</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22311,7 +22311,7 @@
         <v>45117</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44236</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44163</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45132</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>45587.58498842592</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>45093</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45453.54733796296</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>45453.55123842593</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>45370</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>44957</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>45670</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>44494</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>44974.564375</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45771.44005787037</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45786</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>45789.42597222222</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>44565</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45310.41982638889</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>45790</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>44084</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>45595</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44361</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>45637</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>44488</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>45593.59819444444</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45673.49019675926</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>45096</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>45126</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>45126</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>45141</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>45792.42109953704</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45792.42542824074</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>45145</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45400</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>45671.59245370371</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45403.86942129629</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>44935.64165509259</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>45114</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>45114</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>45706.47790509259</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45678.57503472222</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>45794.82583333334</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45794.81975694445</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45794.82150462963</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>45266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>45794.81730324074</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>45796.49842592593</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45490.72372685185</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44930</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45527.43385416667</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45796</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>45758.36203703703</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45794.81583333333</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45546</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>45356.64872685185</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45794.82371527778</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44936</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45796</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45796.36326388889</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45106</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>45259</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45092.35369212963</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45336</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45798.59671296296</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45266.69091435185</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>45798.66228009259</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>45797.39876157408</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44890</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>45798.45043981481</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>45191</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>44168</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>45033</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>45565.5381712963</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>44536</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>45414.5519212963</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>44596</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>45408</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>44573</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45554.28857638889</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45722.46946759259</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>45803.43815972222</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45804.59579861111</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44582</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>45723.65960648148</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>45762.76337962963</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>45550.68804398148</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>45202.56994212963</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>45365</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>44176</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45727.6683449074</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>45442.6052199074</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>45442.60829861111</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>45159</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45432.54622685185</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27891,7 +27891,7 @@
         <v>45807</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>45043</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>45369</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>44641.78332175926</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45183.65135416666</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>45183.65233796297</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>44936</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>45673</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>45178.43909722222</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>45053.36554398148</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45217.51479166667</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>45636.4737962963</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>45030</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>44889</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>45313</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45028</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>45716.40918981482</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>45121</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>44910</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>44181</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45860</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>45817</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         <v>44131</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>45106</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>44181</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>45657.94784722223</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>45817</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>45817.64487268519</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>45201.63637731481</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45817.47909722223</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>45817.41037037037</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>45820.37113425926</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>45205.3119212963</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>45205.35753472222</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>45684.41622685185</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>44427.49322916667</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>45820.39863425926</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>44679</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>45369.61841435185</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>45566.46769675926</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>45215</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>45824.32293981482</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>45678.57731481481</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>44936.46326388889</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45824.45221064815</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>44974.65918981482</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>45758.60146990741</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45824.31493055556</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>45761.59716435185</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>44630</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45211.52641203703</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>45867.7115625</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>44943.56112268518</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45579.56570601852</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>45527.40489583334</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>45174</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>45174</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44448</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>44651.42819444444</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>45394</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>45453.52299768518</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>45238.33091435185</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>45446.57724537037</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>45446.5790625</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>44455</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>45832</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45261.50924768519</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>45049</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>44943</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>45832</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>45832</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32043,7 +32043,7 @@
         <v>45764.43002314815</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>45833.4374537037</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>45833.40451388889</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45091</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>45558.54422453704</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>45254.54892361111</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>45112</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45215</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>44677</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>45188</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45680</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45715.5837962963</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45723.66629629629</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>45764.47553240741</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>45699.75583333334</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>44834</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>45833.65659722222</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33037,7 +33037,7 @@
         <v>45317</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44741</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45008.66204861111</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>45838.683125</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>45204</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33337,7 +33337,7 @@
         <v>45468.82832175926</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>45836</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45769.62891203703</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
         <v>45401.46640046296</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33575,7 +33575,7 @@
         <v>44965</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45014</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>44504</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>44956.54967592593</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>45583.55850694444</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45356.64724537037</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45758.35732638889</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>45274</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>45840.65777777778</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>45840.65592592592</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34160,7 +34160,7 @@
         <v>45636.45989583333</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>45840.6602199074</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45252</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>45614.46292824074</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>44279</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>45191.39708333334</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>45758.56946759259</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>44719.43200231482</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34626,7 +34626,7 @@
         <v>45840.66780092593</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34683,7 +34683,7 @@
         <v>45254</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>45840.66978009259</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34802,7 +34802,7 @@
         <v>45883.58974537037</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>45883.63648148148</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>45883.69113425926</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>45883.74664351852</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>45246.41627314815</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>45246</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>44455.68550925926</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>44956</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>45719.4522337963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>44956</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45716.45121527778</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>45252.91344907408</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>45272</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35568,7 +35568,7 @@
         <v>45769.40231481481</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>44974</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
         <v>45581.62796296296</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>45883.5738425926</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>45399.62587962963</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>45874</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35925,7 +35925,7 @@
         <v>44573.38521990741</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35982,7 +35982,7 @@
         <v>45317</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>45884.45916666667</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>45881</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>45883.58756944445</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
         <v>45414.39614583334</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36277,7 +36277,7 @@
         <v>45884.57759259259</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>45884.60458333333</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>45884.68263888889</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36458,7 +36458,7 @@
         <v>44249</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36515,7 +36515,7 @@
         <v>45881</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>45883.59934027777</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>45645.27707175926</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>44998</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>45887</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>44862</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36862,7 +36862,7 @@
         <v>44512</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>44970.65930555556</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>45678.44092592593</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>45716.37259259259</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>45266.66998842593</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44993</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>44980</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45030</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37338,7 +37338,7 @@
         <v>45886</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>45886.65516203704</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>44859</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>44312</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44469</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>45330</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>45386.35986111111</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45266</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>45888.4712037037</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>45888.4658449074</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45887</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         <v>44851</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38042,7 +38042,7 @@
         <v>45845.45563657407</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>44243</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>45888.46922453704</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>45888.61847222222</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>45769.57802083333</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>45845.65797453704</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45797</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44721</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>45114</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>44221</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45106</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45763.41083333334</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45877</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>45043</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38870,7 +38870,7 @@
         <v>45889</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>45178.4275</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45877</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45798.60880787037</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>45889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>45796.44922453703</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>44384</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>44767</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45016.67141203704</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45629.67508101852</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45629.67931712963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45098.37322916667</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>44805</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45096</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>45117</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>45736.31508101852</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>45891.60346064815</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>45582.98494212963</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>45268</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>45894.55337962963</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>45736.32394675926</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40117,7 +40117,7 @@
         <v>44599</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>45894.41133101852</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45894.55216435185</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40298,7 +40298,7 @@
         <v>45873</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>45727.64337962963</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40417,7 +40417,7 @@
         <v>45891.60103009259</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>45817.42607638889</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>44597</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>44225</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>45894.4825</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40712,7 +40712,7 @@
         <v>45597.40140046296</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>45891.59726851852</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
         <v>45891.59938657407</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>45469.43265046296</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40940,7 +40940,7 @@
         <v>45726.90959490741</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40997,7 +40997,7 @@
         <v>45678.59783564815</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>44754.57658564814</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41111,7 +41111,7 @@
         <v>45895.42582175926</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41173,7 +41173,7 @@
         <v>44739.52209490741</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>44713.58678240741</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>45121</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>44970.44197916667</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45813.56320601852</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>45895.373125</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>45896.66505787037</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45896.66944444444</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45896.81087962963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45895.3627662037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>45747.44502314815</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>45201.56556712963</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45215.63990740741</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>45106</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45030.61489583334</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45030.61744212963</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45638</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>44853.64244212963</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45898.86685185185</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>44742</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45898.58202546297</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>44999</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>45053.82055555555</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>44181</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45043.49425925926</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45110</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>44826</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>45442.38490740741</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>45671.5678125</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>44908</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>44897</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>45642</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43057,7 +43057,7 @@
         <v>45442.61221064815</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43119,7 +43119,7 @@
         <v>45733.62203703704</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43181,7 +43181,7 @@
         <v>45686.61590277778</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43243,7 +43243,7 @@
         <v>45008.62458333333</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>44980</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>45702.76590277778</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43424,7 +43424,7 @@
         <v>45013.63658564815</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43481,7 +43481,7 @@
         <v>45229</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         <v>44867</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>44105</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>45764.44263888889</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45442.68033564815</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>44957</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45716.57158564815</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>44364.78170138889</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45043</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>44333</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45715.56964120371</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>44746</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>44880</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>44992</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44304,7 +44304,7 @@
         <v>44861</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44366,7 +44366,7 @@
         <v>44166</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
         <v>44575</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44480,7 +44480,7 @@
         <v>44957</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>44945.58030092593</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>45008</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>45093.54811342592</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>45729</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>45110</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44837,7 +44837,7 @@
         <v>45274.43547453704</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>44936</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>44936</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45030</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>44177</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>44177</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45733.44431712963</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45271,7 +45271,7 @@
         <v>44358</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45333,7 +45333,7 @@
         <v>44096</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>45772.6652662037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45452,7 +45452,7 @@
         <v>45254</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>45077</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>45509.57052083333</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>45174</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>45174.87439814815</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45742,7 +45742,7 @@
         <v>45043</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>44992</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45183</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45913,7 +45913,7 @@
         <v>44155</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45970,7 +45970,7 @@
         <v>45771.76943287037</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45014</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45614.52813657407</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46146,7 +46146,7 @@
         <v>45246.41783564815</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>45049.34974537037</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46260,7 +46260,7 @@
         <v>45049.35048611111</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>45527.41597222222</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>44939</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46431,7 +46431,7 @@
         <v>45012.79270833333</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46488,7 +46488,7 @@
         <v>44218</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46550,7 +46550,7 @@
         <v>45453.55534722222</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46607,7 +46607,7 @@
         <v>45022.34695601852</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46664,7 +46664,7 @@
         <v>44987.5428587963</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46721,7 +46721,7 @@
         <v>45237</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46783,7 +46783,7 @@
         <v>45769.45751157407</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45769</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45769</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>44454</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45733.43347222222</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47083,7 +47083,7 @@
         <v>45770.84420138889</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45090.90752314815</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>44096</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>44860</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>44783</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>44137</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47430,7 +47430,7 @@
         <v>45741.51940972222</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47492,7 +47492,7 @@
         <v>44439.97621527778</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         <v>44147</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>45706.42958333333</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>45090</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47730,7 +47730,7 @@
         <v>44896</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45048</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>44900</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47916,7 +47916,7 @@
         <v>45520.52375</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>44083</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48030,7 +48030,7 @@
         <v>45769</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48087,7 +48087,7 @@
         <v>45356.66037037037</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>44286.88952546296</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>45043</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48258,7 +48258,7 @@
         <v>44897</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>44928.45552083333</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>45071</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>44923.67971064815</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48501,7 +48501,7 @@
         <v>45731.59962962963</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48558,7 +48558,7 @@
         <v>44151.53271990741</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48615,7 +48615,7 @@
         <v>45699</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45279.66864583334</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>44907.66710648148</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>44588</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45435</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45547.64484953704</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48967,7 +48967,7 @@
         <v>44237</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49029,7 +49029,7 @@
         <v>45657.95927083334</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49091,7 +49091,7 @@
         <v>45678.47236111111</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49148,7 +49148,7 @@
         <v>45086.71662037037</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>45436.41847222222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45636.45025462963</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45583.34371527778</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>44783</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49448,7 +49448,7 @@
         <v>45071</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45731.60166666667</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45716.39159722222</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45096</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>45153.36402777778</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>45117</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>45757.66474537037</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         <v>44980</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49924,7 +49924,7 @@
         <v>45093</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49981,7 +49981,7 @@
         <v>44974</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50043,7 +50043,7 @@
         <v>44980.48200231481</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>44981</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50167,7 +50167,7 @@
         <v>44966.57550925926</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50229,7 +50229,7 @@
         <v>45030.62916666667</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50348,7 +50348,7 @@
         <v>44977.57584490741</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         <v>44433</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50467,7 +50467,7 @@
         <v>45721.51255787037</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50524,7 +50524,7 @@
         <v>45721.51346064815</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>44644</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50643,7 +50643,7 @@
         <v>45012</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50700,7 +50700,7 @@
         <v>44652</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50757,7 +50757,7 @@
         <v>45076</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>45706.49520833333</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50876,7 +50876,7 @@
         <v>45706.54385416667</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50933,7 +50933,7 @@
         <v>45048</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>45121</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51052,7 +51052,7 @@
         <v>44803.59099537037</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51109,7 +51109,7 @@
         <v>45678.58166666667</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51166,7 +51166,7 @@
         <v>45771.66951388889</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51228,7 +51228,7 @@
         <v>45769.41631944444</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51290,7 +51290,7 @@
         <v>45628.56513888889</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51352,7 +51352,7 @@
         <v>44159.36447916667</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51409,7 +51409,7 @@
         <v>45436.41305555555</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51471,7 +51471,7 @@
         <v>45758.60465277778</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51528,7 +51528,7 @@
         <v>45758.61055555556</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51585,7 +51585,7 @@
         <v>45699.65944444444</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51647,7 +51647,7 @@
         <v>45092.36790509259</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51704,7 +51704,7 @@
         <v>45535.91413194445</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51761,7 +51761,7 @@
         <v>45373.48878472222</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51818,7 +51818,7 @@
         <v>45219.32268518519</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51875,7 +51875,7 @@
         <v>45330</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51932,7 +51932,7 @@
         <v>45386.32806712963</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51994,7 +51994,7 @@
         <v>45442.67793981481</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52056,7 +52056,7 @@
         <v>45723.67724537037</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52113,7 +52113,7 @@
         <v>45747.59501157407</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52175,7 +52175,7 @@
         <v>45027</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52232,7 +52232,7 @@
         <v>45373.72511574074</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52289,7 +52289,7 @@
         <v>44935</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52346,7 +52346,7 @@
         <v>45558</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52403,7 +52403,7 @@
         <v>44935.60138888889</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>45478.47236111111</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52527,7 +52527,7 @@
         <v>45118</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>44980</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>44977.63902777778</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52708,7 +52708,7 @@
         <v>45678.6377199074</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52765,7 +52765,7 @@
         <v>45153</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>45603.49528935185</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52884,7 +52884,7 @@
         <v>44936</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52941,7 +52941,7 @@
         <v>45742.31784722222</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52998,7 +52998,7 @@
         <v>45153</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53060,7 +53060,7 @@
         <v>44907.65043981482</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53117,7 +53117,7 @@
         <v>45211.52895833334</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53174,7 +53174,7 @@
         <v>44936</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53231,7 +53231,7 @@
         <v>45016.64986111111</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53293,7 +53293,7 @@
         <v>45129</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53350,7 +53350,7 @@
         <v>45457.59425925926</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53407,7 +53407,7 @@
         <v>45250.5799537037</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53464,7 +53464,7 @@
         <v>45764.43782407408</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -53521,7 +53521,7 @@
         <v>45405</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -53578,7 +53578,7 @@
         <v>45497</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>45684.4203125</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -53697,7 +53697,7 @@
         <v>45706.54204861111</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53754,7 +53754,7 @@
         <v>45706.54572916667</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53811,7 +53811,7 @@
         <v>45310</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45012</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45798.58304398148</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>44896</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>44299</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>44264</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>45579</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45645.27462962963</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45139</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45012</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>45880.62738425926</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45886.64045138889</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>45568</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>45441</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>45783.4903125</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>45133</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>45604</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>45723.61545138889</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>45742.41269675926</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>45832.36966435185</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>45421</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>44578</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>44412</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>45723.59275462963</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45042</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>45421</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>45731.65016203704</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>45723.57098379629</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>45881.41636574074</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45568</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>45583</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>45086</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>45012</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>45441.33914351852</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>45764.47825231482</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45013.77040509259</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>44977</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>45832.31648148148</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>45833.56057870371</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>45884.4946875</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>45905.42704861111</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44931</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>45604</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>45733.45780092593</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>45782.659375</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>45694</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>45772.6571412037</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44454</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45568.44137731481</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>45832.3365625</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>45258.56491898148</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>45905.3244675926</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>45583</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>44789</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>45086</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>45758.54390046297</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>44308</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>44480</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>44426</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>44452</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>44524</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>44490</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>45580</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>45348.68336805556</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>45763.60795138889</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>45723.66964120371</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>45783.61222222223</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>45042</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>45117</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>45362</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>45747.58131944444</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>44777.49493055556</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>45702.76395833334</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>45770.63996527778</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>45796</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>45201</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>45583</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>45583.3479050926</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44886.54420138889</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>45174</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45742.43848379629</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>45096</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45723.55663194445</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>45583</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>45744</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>45056</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>45744.41443287037</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>45369</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>45905.58907407407</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>45201</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>45408</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>44132</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>45716.5672337963</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>45376</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>45411.57177083333</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>45421</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>45251</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>44354</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>44089</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>44151</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>44219</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>44211</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>44211</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>44158</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>44146</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>44456</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>44456</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44301</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>44307</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>44530</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>44582.4696875</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44211</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>44217</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>44214</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>44176</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>44502</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>44107</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>44622</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>44537</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>44218</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>44825.47923611111</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>44728.82296296296</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>44340.80107638889</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>44279</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>44739</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>44368</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>44719.43086805556</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>44216</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>44169</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>44169</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44370</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>44258</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>44440</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>44503</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>44448</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>44306</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>44368</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>44441</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>44301</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>44865</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>44294</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>44286</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>44524.67836805555</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>44385</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>44696.775</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>44390</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>44432</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>44433</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>44447</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>44494</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>44368.88704861111</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>44333</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
         <v>44340</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>44671</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>44713</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>44813</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>44530</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>44515</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>44571</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>44169</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>44442.66228009259</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>44208</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>44272</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>44475</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>44475</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>44393</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44630.3978587963</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>44371</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>44371</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>44124.63679398148</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>44362</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>44211</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>44211</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>44524</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>44271.81282407408</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>44447</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>44530</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>44503</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>44313</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>44300</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44300</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>44459</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>44446</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>44321</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>44879.39153935185</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44459</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>44475</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>44475</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>44249</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>44574</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>44686</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>44602</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>44889.55255787037</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>44328</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>44452</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>44874</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44219</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>44825</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44162</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44487</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>44358</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>44756</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>44596</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44468</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>44137</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>44137</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>44432</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>44208</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>44252</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44441</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>44582</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44825</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>44740</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
         <v>44452</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44272</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44630</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44344.49251157408</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>44363</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>44270</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>44279</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>44313</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44445</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>44557</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>44741.57063657408</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44302</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>44730</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>44354.45140046296</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>44869.4575</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>44098</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>44348</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>44363</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>44152</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>45118</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
         <v>44362</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>44578</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>45086.71662037037</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>44726</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44512</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44326</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>44326</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
         <v>44326</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>44783</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         <v>45090.90752314815</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>45706.42958333333</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>45758.56056712963</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44936.46326388889</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>44322</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45191</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>44886.47697916667</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>45076</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45386.32806712963</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>44449</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18663,7 +18663,7 @@
         <v>45579.56570601852</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>44462</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45566.46769675926</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>45033</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>45593.59819444444</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>45037</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45678.47236111111</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>45030</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45048</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>45205.35753472222</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>45614.52813657407</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45401.46640046296</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44651.42819444444</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>45777.61991898148</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45726.91224537037</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45706.49520833333</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>45706.54385416667</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45446.57724537037</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>45446.5790625</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>45716.39159722222</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>45077</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>45092</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>45278</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>45783</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45520.52375</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>44935.64165509259</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45783.68689814815</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>45093</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45783.48681712963</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20351,7 +20351,7 @@
         <v>45030</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45399.62587962963</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>45053.36554398148</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>45782.66719907407</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20584,7 +20584,7 @@
         <v>44105</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45547.64484953704</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45159</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>45106</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>45671.62931712963</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>45784</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45121</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>45699</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>45699.75583333334</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44861</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>45110</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>45356.66037037037</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>44957</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>44910</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>45442.67793981481</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45008.66204861111</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44928.45552083333</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>44249</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45784.62866898148</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>44826</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21774,7 +21774,7 @@
         <v>45637</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>44998</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>45266</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>45758.36203703703</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45117</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45373.73894675926</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>44880</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>45786</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>45786.36358796297</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45527.40489583334</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45789.42597222222</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>45678.57731481481</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>45014</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>45587.58498842592</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>44565</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>45092.36126157407</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44096</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45092.35266203704</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44974.65918981482</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>45636.45989583333</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>45313</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>45644</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>45266</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>45049.34974537037</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45049.35048611111</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>45238.33091435185</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45453.54733796296</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45453.55123842593</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45469.43265046296</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>44900</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45266.66998842593</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44181</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>45432.6291550926</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>45310.41982638889</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>44741</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>44159.36447916667</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45237</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>45742.31784722222</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>44974.564375</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44137</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>44965</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>45790</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>45747.59501157407</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45583.55850694444</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>44834</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>45792.42109953704</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>45583.34371527778</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44652</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45386.35986111111</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>44596</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>45022.34695601852</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>45772.6652662037</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
         <v>45043.53597222222</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45792.42542824074</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>45771.44005787037</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45259</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45527.41597222222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>45794.82150462963</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>45546</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25237,7 +25237,7 @@
         <v>45796</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>45796.36326388889</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>45678.57503472222</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>45796</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25470,7 +25470,7 @@
         <v>45794.81583333333</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>45229</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>44970.44197916667</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>44181</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>45030.62740740741</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45030</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>44862</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>45188</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>45797.39876157408</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>45796.49842592593</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>45794.81730324074</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>45794.82583333334</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>45254.54892361111</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>45794.82371527778</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>45535.91413194445</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>45268</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>45550.68804398148</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>45794.81975694445</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>45798.45043981481</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>45702.76590277778</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>45356.64724537037</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44439.97621527778</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44980</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         <v>44956</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>45764.43002314815</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>45053.82055555555</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>44966.57550925926</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>44860</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27091,7 +27091,7 @@
         <v>44597</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         <v>45014</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>45798.59671296296</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>44936</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>45408</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>45246.41783564815</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>45565.5381712963</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>45798.66228009259</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>44936</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>44575</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>45554.28857638889</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>45414.5519212963</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>45723.65960648148</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>44455.68550925926</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>44588</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>45722.46946759259</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>45272</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>45803.43815972222</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45769.62891203703</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>45762.76337962963</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>45603.49528935185</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45400</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45274</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44494</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44754.57658564814</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45771.69168981481</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>45174</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45174.87439814815</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>45804.59579861111</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>45274.43547453704</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>45558.54422453704</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>45558</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45731.60166666667</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44859</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>45807</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45363.58979166667</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>45628.56513888889</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29250,7 +29250,7 @@
         <v>45336</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>44582</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45442.6052199074</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>45442.60829861111</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45442.68033564815</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>44897</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>45183.65135416666</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>45183.65233796297</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44935</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>44935.60138888889</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>44950</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>45043</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>45736.72646990741</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>45509.57052083333</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>45369.61550925926</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>45145</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44896</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>44858</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>45436.41305555555</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30373,7 +30373,7 @@
         <v>45758.56946759259</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30435,7 +30435,7 @@
         <v>45369</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45215.63990740741</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44644</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>44084</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>44454</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>44936</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45110.56027777777</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>45110</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>44890</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>44176</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>45769</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>45013.63658564815</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>44956.54967592593</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>44721</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45117</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45817.64487268519</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45817.41037037037</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31444,7 +31444,7 @@
         <v>45817.47909722223</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>44980</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>45817</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>45817</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>45763.41083333334</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>45671.59245370371</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>45217.51479166667</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45096</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>45657.94784722223</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45532</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45202</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32106,7 +32106,7 @@
         <v>45191.39708333334</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>45121</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>45820.39863425926</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>45597.40140046296</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>45820.37113425926</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>45279.66864583334</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>45071</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>45733.62203703704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>45824.31493055556</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>44448</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>44803.59099537037</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>45867.7115625</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>45824.45221064815</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>45824.32293981482</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>45684.4203125</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>45678.6377199074</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>44889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>44166</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>45178.43909722222</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>45678.59783564815</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45317</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>44860</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>45832</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>45202.56994212963</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>45833.65659722222</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>45833.40451388889</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45833.4374537037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>45832</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>45832</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>45043</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>44504</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>45836</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>45453.55534722222</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34037,7 +34037,7 @@
         <v>45838.683125</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34094,7 +34094,7 @@
         <v>44939</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34156,7 +34156,7 @@
         <v>44987.5428587963</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>45883.5738425926</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34270,7 +34270,7 @@
         <v>45883.59934027777</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45881</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>45883.63648148148</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>45883.69113425926</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>45840.65592592592</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45883.58756944445</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45840.65777777778</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45840.66978009259</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45840.66780092593</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>45883.58974537037</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>45883.74664351852</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>45840.6602199074</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>45098.37322916667</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>44956</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45886</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35197,7 +35197,7 @@
         <v>45886.65516203704</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>45379</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>45884.57759259259</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35373,7 +35373,7 @@
         <v>45845.65797453704</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>45678.44092592593</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35492,7 +35492,7 @@
         <v>44677</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35549,7 +35549,7 @@
         <v>45887</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>45884.68263888889</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>45887</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>45845.45563657407</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>45884.45916666667</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45888.61847222222</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>45414.39614583334</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45126</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45126</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>45888.46922453704</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>45888.4712037037</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>44384</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45888.4658449074</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45797</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>45891.60103009259</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>45889</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>45877</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>45877</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>45891.59726851852</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>45891.59938657407</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>45796.44922453703</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>45891.60346064815</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36838,7 +36838,7 @@
         <v>45798.60880787037</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>45889</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>45183</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45894.55337962963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>45873</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37133,7 +37133,7 @@
         <v>45894.4825</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45741.63417824074</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>45894.55216435185</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45817.42607638889</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45736.31508101852</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>45894.41133101852</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>45764.43782407408</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45895.3627662037</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45764.44263888889</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45895.373125</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>45895.42582175926</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>45896.66944444444</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37852,7 +37852,7 @@
         <v>45896.66505787037</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37909,7 +37909,7 @@
         <v>45896.81087962963</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>45813.56320601852</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>45884.60458333333</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>45043</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>44096</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45268</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>45898.86685185185</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>45757.66474537037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38380,7 +38380,7 @@
         <v>45898.58202546297</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>44907.66710648148</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45114</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>45114</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>45758.35732638889</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38670,7 +38670,7 @@
         <v>45903.45952546296</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38732,7 +38732,7 @@
         <v>45860</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45903.43489583334</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44742</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>44163</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>44469</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>45240</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>45723.66629629629</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         <v>45118</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39198,7 +39198,7 @@
         <v>45874</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>45614.46292824074</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39317,7 +39317,7 @@
         <v>44679</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
         <v>45715.56964120371</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39441,7 +39441,7 @@
         <v>44536</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39498,7 +39498,7 @@
         <v>45359.68173611111</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>45904.55924768518</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39617,7 +39617,7 @@
         <v>44993</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39679,7 +39679,7 @@
         <v>45153</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>45215</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45881</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>45096</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>44880.44351851852</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39984,7 +39984,7 @@
         <v>44599</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>44999</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40103,7 +40103,7 @@
         <v>45049</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>44221</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45330</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40274,7 +40274,7 @@
         <v>45219.32268518519</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>44414</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>45468.82832175926</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>45048</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>44936</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>44936</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>45201.63637731481</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>45106</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40745,7 +40745,7 @@
         <v>44980.48200231481</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>45747.44502314815</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>45769.57802083333</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>45769</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>45178.4275</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>44488</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>44994.41405092592</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>45028</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45442.38490740741</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41268,7 +41268,7 @@
         <v>45727.64337962963</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>45408.49326388889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>45106</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41444,7 +41444,7 @@
         <v>45729</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>45716.40918981482</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>44862</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>45684.41622685185</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         <v>45043.49425925926</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>45317</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41811,7 +41811,7 @@
         <v>44236</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41873,7 +41873,7 @@
         <v>45365</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41935,7 +41935,7 @@
         <v>45405</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41992,7 +41992,7 @@
         <v>45769.45751157407</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>44923.67971064815</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42116,7 +42116,7 @@
         <v>44930</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>44974</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>44805</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45043</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42354,7 +42354,7 @@
         <v>45716.57158564815</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>45092.35369212963</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42468,7 +42468,7 @@
         <v>44970.65930555556</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42525,7 +42525,7 @@
         <v>44865</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42582,7 +42582,7 @@
         <v>45770.84420138889</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45201.56556712963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>45132</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42758,7 +42758,7 @@
         <v>44908</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42815,7 +42815,7 @@
         <v>45373.48878472222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42872,7 +42872,7 @@
         <v>44943.56112268518</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>44943</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45527.43385416667</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>44992</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45211.52641203703</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>45211.52895833334</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>44641.78332175926</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43281,7 +43281,7 @@
         <v>45252</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>45678.57045138889</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>45678.58166666667</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>45369.61841435185</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43509,7 +43509,7 @@
         <v>45673</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>45128</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>45758.60146990741</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43680,7 +43680,7 @@
         <v>45686.61590277778</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45741.51940972222</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>45317</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43866,7 +43866,7 @@
         <v>45215.63818287037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>45096</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43985,7 +43985,7 @@
         <v>44218</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44047,7 +44047,7 @@
         <v>44427.49322916667</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44104,7 +44104,7 @@
         <v>45436.41847222222</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45736.32394675926</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>45638</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45204</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45356.64872685185</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45246.41627314815</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45246</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>44361</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45215</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44632,7 +44632,7 @@
         <v>45174</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44689,7 +44689,7 @@
         <v>45174</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>45334</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45457.59425925926</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45680</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44927,7 +44927,7 @@
         <v>45092.36790509259</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>44981</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45046,7 +45046,7 @@
         <v>45141</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45414.3944212963</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45254</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>44945.58030092593</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>45027</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>45425.89037037037</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45398,7 +45398,7 @@
         <v>45581.62796296296</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45091</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45369.62108796297</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>44131</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>45071</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45688,7 +45688,7 @@
         <v>45043</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45745,7 +45745,7 @@
         <v>45771.76943287037</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45802,7 +45802,7 @@
         <v>45442.61221064815</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>44358</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>45008</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>44936</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>44312</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>45763.64096064815</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>45699.65944444444</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
         <v>45006</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>45339.5277199074</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>45673.49019675926</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46407,7 +46407,7 @@
         <v>45582.98494212963</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>45758.60465277778</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>45758.61055555556</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>45386</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>45093.54811342592</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>44992</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>44980</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46816,7 +46816,7 @@
         <v>44825</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>45645.27707175926</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46930,7 +46930,7 @@
         <v>45453.52299768518</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46987,7 +46987,7 @@
         <v>45252.91344907408</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>44237</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47106,7 +47106,7 @@
         <v>45636.45025462963</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45636.4737962963</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>44243</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47277,7 +47277,7 @@
         <v>45030</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>44433</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45030.62916666667</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>44939</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45731.59962962963</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>44177</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>44177</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
         <v>45093</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47743,7 +47743,7 @@
         <v>44573</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>45012</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45771.66951388889</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>45153.36402777778</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47981,7 +47981,7 @@
         <v>44333</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48038,7 +48038,7 @@
         <v>45709.4119212963</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48100,7 +48100,7 @@
         <v>44225</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>45330</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>44279</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48276,7 +48276,7 @@
         <v>44862</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>45719.4522337963</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>44573.38521990741</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48452,7 +48452,7 @@
         <v>44867</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48514,7 +48514,7 @@
         <v>45373.72511574074</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48571,7 +48571,7 @@
         <v>45405</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48628,7 +48628,7 @@
         <v>44980</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48690,7 +48690,7 @@
         <v>45016.64986111111</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48752,7 +48752,7 @@
         <v>45110</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>44713.58678240741</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>45254</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>45742.32277777778</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48990,7 +48990,7 @@
         <v>45497</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49047,7 +49047,7 @@
         <v>44861</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49109,7 +49109,7 @@
         <v>44607</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>45336</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49223,7 +49223,7 @@
         <v>45629.7202662037</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49280,7 +49280,7 @@
         <v>45716.37259259259</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49342,7 +49342,7 @@
         <v>45106</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49399,7 +49399,7 @@
         <v>45016.67141203704</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49461,7 +49461,7 @@
         <v>45706.54204861111</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49518,7 +49518,7 @@
         <v>45706.54572916667</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49575,7 +49575,7 @@
         <v>45112</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49632,7 +49632,7 @@
         <v>45043</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>45769</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49751,7 +49751,7 @@
         <v>45266.69091435185</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>45435</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>44977.57584490741</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49927,7 +49927,7 @@
         <v>45595</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>45090</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50046,7 +50046,7 @@
         <v>45709.42859953704</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50108,7 +50108,7 @@
         <v>45671.5678125</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50170,7 +50170,7 @@
         <v>44739.52209490741</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>44147</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         <v>45114</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50341,7 +50341,7 @@
         <v>44630</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45008.62458333333</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>44364.78170138889</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50517,7 +50517,7 @@
         <v>45250.5799537037</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50574,7 +50574,7 @@
         <v>44286.88952546296</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50631,7 +50631,7 @@
         <v>44783</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>45261.50924768519</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45721.51255787037</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45721.51346064815</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50859,7 +50859,7 @@
         <v>44083</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50916,7 +50916,7 @@
         <v>45317</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>44977.63902777778</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>44168</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45432.54622685185</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>45715.5837962963</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51216,7 +51216,7 @@
         <v>44719.43200231482</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
         <v>45012.79270833333</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>45726.90959490741</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51387,7 +51387,7 @@
         <v>45723.67724537037</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         <v>45030.61489583334</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>45030.61744212963</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>45254</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45670</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>44455</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
         <v>45310</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51796,7 +51796,7 @@
         <v>45706.47790509259</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51853,7 +51853,7 @@
         <v>45761.59716435185</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51915,7 +51915,7 @@
         <v>45153</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51977,7 +51977,7 @@
         <v>45490.72372685185</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52034,7 +52034,7 @@
         <v>45769.40231481481</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52096,7 +52096,7 @@
         <v>44151.53271990741</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52153,7 +52153,7 @@
         <v>44433</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>44181</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52267,7 +52267,7 @@
         <v>45205.3119212963</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52324,7 +52324,7 @@
         <v>44851</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52381,7 +52381,7 @@
         <v>45716.45121527778</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52443,7 +52443,7 @@
         <v>45370</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52505,7 +52505,7 @@
         <v>44805</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>44746</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52624,7 +52624,7 @@
         <v>45129</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52681,7 +52681,7 @@
         <v>44907.65043981482</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52738,7 +52738,7 @@
         <v>45657.95927083334</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52800,7 +52800,7 @@
         <v>45117</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52862,7 +52862,7 @@
         <v>45741.53599537037</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52924,7 +52924,7 @@
         <v>45121</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52986,7 +52986,7 @@
         <v>45478.47236111111</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>45733.43347222222</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53110,7 +53110,7 @@
         <v>45733.44431712963</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45764.47553240741</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>44957</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>45403.86942129629</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53368,7 +53368,7 @@
         <v>44155</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
         <v>44957</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53487,7 +53487,7 @@
         <v>45394</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53549,7 +53549,7 @@
         <v>44767</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -53606,7 +53606,7 @@
         <v>45769.41631944444</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -53668,7 +53668,7 @@
         <v>45072</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -53730,7 +53730,7 @@
         <v>44974</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -53792,7 +53792,7 @@
         <v>45642</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53854,7 +53854,7 @@
         <v>45106</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53911,7 +53911,7 @@
         <v>44853.64244212963</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53968,7 +53968,7 @@
         <v>44897</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54030,7 +54030,7 @@
         <v>45629.67508101852</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54087,7 +54087,7 @@
         <v>45629.67931712963</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54144,7 +54144,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54206,7 +54206,7 @@
         <v>45727.6683449074</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45012</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45798.58304398148</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>44896</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>44299</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>44264</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>45579</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>45139</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>45645.27462962963</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45012</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45441</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>45568</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45880.62738425926</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>45886.64045138889</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>45783.4903125</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45133</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>45604</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>45421</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45723.61545138889</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45742.41269675926</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>45832.36966435185</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>44578</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>44412</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45723.59275462963</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45568</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>45723.57098379629</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>45731.65016203704</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>45881.41636574074</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45421</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45042</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45771.69168981481</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44977</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>45604</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>45832.31648148148</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>45833.56057870371</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>44931</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45884.4946875</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>45764.47825231482</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>45013.77040509259</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>45086</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>45905.42704861111</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45583</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>45441.33914351852</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>45012</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44789</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45782.659375</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45783.68689814815</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>45258.56491898148</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>45568.44137731481</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>45832.3365625</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>45733.45780092593</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>45694</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>45772.6571412037</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45758.54390046297</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>45583</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>44454</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>45086</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45905.3244675926</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44308</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44480</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>44426</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44524</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>44452</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>44490</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>45723.66964120371</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         <v>45583.3479050926</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>45770.63996527778</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>45408</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>45763.60795138889</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>45783.61222222223</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>45376</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45362</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44886.54420138889</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>45796</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>44089</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>45201</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>45421</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>45096</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>45716.5672337963</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>45723.55663194445</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>45583</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>45201</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45251</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>44777.49493055556</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>45580</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>45117</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>44354</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>45702.76395833334</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>45742.43848379629</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>45771.76943287037</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>45747.58131944444</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>45174</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>45369</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>45056</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>45042</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>45905.58907407407</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>45583</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>45744</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45744.41443287037</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>45411.57177083333</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>44132</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>45348.68336805556</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>44151</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>44219</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>44211</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>44211</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>44158</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>44146</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>44301</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>44307</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>44530</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>44582.4696875</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>44456</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>44456</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>44211</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>44217</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>44214</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>44176</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>44107</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>44502</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>44622</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>44537</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>44218</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>44825.47923611111</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44728.82296296296</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>44340.80107638889</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44279</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>44739</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>44368</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>44719.43086805556</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44216</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>44169</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44169</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>44370</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>44258</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>44503</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>44448</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         <v>44440</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>44306</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>44368</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12121,7 +12121,7 @@
         <v>44441</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>44301</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>44865</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44294</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>44286</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44524.67836805555</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44385</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>44696.775</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>44390</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>44432</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44433</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44447</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>44494</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>44340</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>44333</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>44671</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44713</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>44368.88704861111</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44813</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>44530</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>44515</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44571</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44169</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44442.66228009259</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44208</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44475</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44475</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44272</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>44393</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>44630.3978587963</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44371</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>44371</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>44124.63679398148</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44362</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44211</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>44211</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>44524</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>44271.81282407408</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>44447</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>44530</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44313</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>44300</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44300</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>44446</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>44459</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>44503</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>44321</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>44879.39153935185</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>44459</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>44475</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>44475</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44249</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44574</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44886.47697916667</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>44686</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>44602</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44726</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44449</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44889.55255787037</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>44328</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         <v>44452</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>44098</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>44348</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>44825</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44487</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44358</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>44596</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>44468</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>44152</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>44756</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>44874</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>44219</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>44162</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>44137</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>44137</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>44432</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>44630</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>44582</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>44740</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>44825</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>44208</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>44252</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>44279</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>44741.57063657408</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>44445</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>44557</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>44441</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>44270</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>44302</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>44730</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
         <v>44869.4575</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>44354.45140046296</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45043.53597222222</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45215.63818287037</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>44825</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>44865</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>45072</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>44862</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>44362</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45043</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45709.4119212963</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45202</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45532</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>45678.57045138889</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>44578</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>45363.58979166667</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45405</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>44326</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>44326</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>44326</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>44452</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>44272</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>45736.72646990741</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>44805</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>45118</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>45369.62108796297</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>45336</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45741.63417824074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>45092</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>45037</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45369.61550925926</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>45414.3944212963</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45268</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>45742.32277777778</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>45758.56056712963</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45106</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>45379</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19595,7 +19595,7 @@
         <v>45709.42859953704</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45240</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>45373.73894675926</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>44862</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>45644</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45629.7202662037</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>44860</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45763.64096064815</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>45339.5277199074</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>44414</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45408.49326388889</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45254</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45386</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         <v>45726.91224537037</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>45741.53599537037</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>44462</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>45777.61991898148</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44607</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44322</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44344.49251157408</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>44363</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45782.66719907407</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>44950</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>45092.35266203704</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45783</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45006</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44433</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45784</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45784.62866898148</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45317</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45783.48681712963</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>45030.62740740741</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45030</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45359.68173611111</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>44994.41405092592</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45334</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45128</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>45110.56027777777</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45110</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>44861</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45432.6291550926</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>45425.89037037037</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44880.44351851852</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45132</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45317</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>45092.36126157407</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>44939</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>45278</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>44858</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>45370</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45786.36358796297</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>45671.62931712963</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>44957</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>45117</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>45670</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>44236</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44494</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44974.564375</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>44313</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>44163</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>45771.44005787037</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45587.58498842592</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>45595</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>45637</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>45593.59819444444</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>45673.49019675926</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45453.54733796296</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45453.55123842593</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23688,7 +23688,7 @@
         <v>45126</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>45126</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>45093</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>45141</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45786</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>45789.42597222222</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44565</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45310.41982638889</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>45145</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45400</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>45790</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>45671.59245370371</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>44361</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>44488</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>45096</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>45403.86942129629</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44935.64165509259</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>45114</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45114</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45706.47790509259</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45792.42109953704</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>45792.42542824074</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>45527.43385416667</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>45758.36203703703</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>45546</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>45356.64872685185</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>45106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>45678.57503472222</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>45794.82583333334</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25386,7 +25386,7 @@
         <v>45266</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>45794.81975694445</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>45794.82150462963</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45490.72372685185</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44930</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>45794.81730324074</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>45796.49842592593</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>45092.35369212963</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>44936</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45336</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>45266.69091435185</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>45796</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45794.81583333333</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>45794.82371527778</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45796</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45796.36326388889</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26303,7 +26303,7 @@
         <v>45191</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>44168</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45259</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45033</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>44536</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>44596</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44363</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>44573</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45798.66228009259</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>44890</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45797.39876157408</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>45723.65960648148</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45550.68804398148</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>45798.45043981481</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>45414.5519212963</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45565.5381712963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45408</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>45554.28857638889</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45727.6683449074</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>45159</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>45432.54622685185</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>45722.46946759259</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>45043</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>45803.43815972222</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>45804.59579861111</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>45762.76337962963</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44582</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44641.78332175926</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>45183.65135416666</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>45183.65233796297</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>45673</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>45053.36554398148</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>45217.51479166667</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>45636.4737962963</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>45313</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>45716.40918981482</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         <v>45121</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45202.56994212963</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>45365</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28591,7 +28591,7 @@
         <v>44176</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>45442.6052199074</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>45442.60829861111</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>44936</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28834,7 +28834,7 @@
         <v>45178.43909722222</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>45205.3119212963</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>45205.35753472222</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>45369</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>45684.41622685185</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>45030</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>44889</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>44679</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29310,7 +29310,7 @@
         <v>45028</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>44910</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29429,7 +29429,7 @@
         <v>45758.60146990741</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>44181</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45761.59716435185</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44630</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>45211.52641203703</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44131</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>45106</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44181</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>44651.42819444444</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>45201.63637731481</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>45817</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>45657.94784722223</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>45817</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>44427.49322916667</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>45817.64487268519</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45446.57724537037</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45446.5790625</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>45817.47909722223</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45817.41037037037</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>45369.61841435185</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>45820.37113425926</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>45261.50924768519</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>45215</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45678.57731481481</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>44936.46326388889</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>45820.39863425926</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>44974.65918981482</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>45254.54892361111</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>45215</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>45824.32293981482</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>45188</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>45824.45221064815</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>45715.5837962963</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>45723.66629629629</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>45764.47553240741</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>45824.31493055556</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         <v>45699.75583333334</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31578,7 +31578,7 @@
         <v>44943.56112268518</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>45579.56570601852</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45527.40489583334</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45204</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45468.82832175926</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>45174</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31935,7 +31935,7 @@
         <v>45174</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>44448</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32049,7 +32049,7 @@
         <v>45769.62891203703</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45401.46640046296</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>45274</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>45394</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>45453.52299768518</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>45832</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
         <v>45252</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45238.33091435185</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45191.39708333334</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>45758.56946759259</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>45254</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>45832</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>45832</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>44455</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>45833.4374537037</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>45833.40451388889</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>45246.41627314815</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>45246</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>45049</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>44455.68550925926</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>44956</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45719.4522337963</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>44956</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>45833.65659722222</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>45716.45121527778</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>44943</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33581,7 +33581,7 @@
         <v>45252.91344907408</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33638,7 +33638,7 @@
         <v>45272</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45769.40231481481</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>44974</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45764.43002314815</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>45091</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
         <v>45838.683125</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>45558.54422453704</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34057,7 +34057,7 @@
         <v>45112</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>44677</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34171,7 +34171,7 @@
         <v>44834</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34233,7 +34233,7 @@
         <v>45317</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>44741</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>45008.66204861111</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>45399.62587962963</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45836</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>45317</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>44249</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>44504</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34714,7 +34714,7 @@
         <v>44965</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>45014</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>44862</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>44956.54967592593</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34947,7 +34947,7 @@
         <v>45583.55850694444</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45356.64724537037</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35066,7 +35066,7 @@
         <v>45758.35732638889</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35123,7 +35123,7 @@
         <v>45636.45989583333</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35180,7 +35180,7 @@
         <v>45614.46292824074</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>44279</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>45716.37259259259</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>45266.66998842593</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45840.65777777778</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>44859</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>44719.43200231482</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35594,7 +35594,7 @@
         <v>44469</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>45581.62796296296</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45330</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>44573.38521990741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>45414.39614583334</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>45266</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>45840.65592592592</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>44851</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>44243</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>45840.6602199074</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36164,7 +36164,7 @@
         <v>45645.27707175926</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36221,7 +36221,7 @@
         <v>45106</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36278,7 +36278,7 @@
         <v>45763.41083333334</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>44998</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>44512</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>44970.65930555556</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36516,7 +36516,7 @@
         <v>44993</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>44980</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         <v>45030</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36697,7 +36697,7 @@
         <v>45043</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>44312</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>45840.66780092593</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>45386.35986111111</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>45769.57802083333</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>44721</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>45114</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>44221</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45178.4275</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>45629.67508101852</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>45629.67931712963</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>45098.37322916667</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>44805</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45096</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>45117</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>45582.98494212963</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>45727.64337962963</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>44384</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>44767</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37830,7 +37830,7 @@
         <v>45016.67141203704</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>45597.40140046296</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>45469.43265046296</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>45268</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>44599</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38120,7 +38120,7 @@
         <v>45726.90959490741</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>44713.58678240741</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38234,7 +38234,7 @@
         <v>45121</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>45840.66978009259</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>44597</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>44225</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>45747.44502314815</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38529,7 +38529,7 @@
         <v>45883.58974537037</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38591,7 +38591,7 @@
         <v>45883.63648148148</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>45883.69113425926</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38705,7 +38705,7 @@
         <v>45883.74664351852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38762,7 +38762,7 @@
         <v>45201.56556712963</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         <v>45030.61489583334</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>45030.61744212963</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>44853.64244212963</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38990,7 +38990,7 @@
         <v>45678.59783564815</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39047,7 +39047,7 @@
         <v>44754.57658564814</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>44742</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39161,7 +39161,7 @@
         <v>44999</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>44739.52209490741</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39280,7 +39280,7 @@
         <v>45883.5738425926</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39337,7 +39337,7 @@
         <v>44970.44197916667</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>45110</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39461,7 +39461,7 @@
         <v>44826</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39518,7 +39518,7 @@
         <v>45442.38490740741</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39575,7 +39575,7 @@
         <v>45884.45916666667</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45881</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>45883.58756944445</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>45442.61221064815</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>45008.62458333333</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>44980</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>45702.76590277778</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39994,7 +39994,7 @@
         <v>45013.63658564815</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>45215.63990740741</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>45106</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>45229</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>45884.57759259259</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45884.68263888889</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45764.44263888889</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>45716.57158564815</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>44364.78170138889</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45715.56964120371</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40574,7 +40574,7 @@
         <v>44746</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>44880</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>44992</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40745,7 +40745,7 @@
         <v>44575</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40802,7 +40802,7 @@
         <v>44957</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44945.58030092593</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>45093.54811342592</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>45729</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>45110</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>45274.43547453704</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>45733.44431712963</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>44096</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>45772.6652662037</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>45254</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>45638</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>45883.59934027777</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41541,7 +41541,7 @@
         <v>45077</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41598,7 +41598,7 @@
         <v>45509.57052083333</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41655,7 +41655,7 @@
         <v>45043</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>45183</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>45053.82055555555</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>45614.52813657407</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>45049.34974537037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>45049.35048611111</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>45527.41597222222</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>44939</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42116,7 +42116,7 @@
         <v>45012.79270833333</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45237</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45769.45751157407</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>44181</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45043.49425925926</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>45769</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>45769</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42530,7 +42530,7 @@
         <v>44454</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>45733.43347222222</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42654,7 +42654,7 @@
         <v>44096</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42711,7 +42711,7 @@
         <v>45671.5678125</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>44860</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>44137</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45741.51940972222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>44439.97621527778</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43011,7 +43011,7 @@
         <v>44147</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43068,7 +43068,7 @@
         <v>45706.42958333333</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43125,7 +43125,7 @@
         <v>44908</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>45090</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43244,7 +43244,7 @@
         <v>44896</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43306,7 +43306,7 @@
         <v>44897</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45642</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>44900</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>45520.52375</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43549,7 +43549,7 @@
         <v>45887</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>45733.62203703704</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>45678.44092592593</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43725,7 +43725,7 @@
         <v>45769</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43782,7 +43782,7 @@
         <v>45686.61590277778</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>44897</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43906,7 +43906,7 @@
         <v>44928.45552083333</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>44923.67971064815</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>45731.59962962963</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44151.53271990741</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>45886</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>45886.65516203704</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44867</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>45279.66864583334</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>44907.66710648148</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>44588</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>44105</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>45888.4712037037</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45888.4658449074</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45887</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>44237</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>45845.45563657407</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>45442.68033564815</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>45888.46922453704</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>44957</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45039,7 +45039,7 @@
         <v>45436.41847222222</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45101,7 +45101,7 @@
         <v>45888.61847222222</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>45845.65797453704</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45225,7 +45225,7 @@
         <v>45797</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>45043</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>44333</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>44783</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>44861</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45520,7 +45520,7 @@
         <v>44166</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>45008</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>45877</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45691,7 +45691,7 @@
         <v>44936</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45753,7 +45753,7 @@
         <v>44936</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45815,7 +45815,7 @@
         <v>45030</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>44177</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45929,7 +45929,7 @@
         <v>44177</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45986,7 +45986,7 @@
         <v>45889</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>45877</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46100,7 +46100,7 @@
         <v>45798.60880787037</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46162,7 +46162,7 @@
         <v>45889</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46219,7 +46219,7 @@
         <v>45731.60166666667</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46276,7 +46276,7 @@
         <v>45716.39159722222</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46333,7 +46333,7 @@
         <v>44358</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>45796.44922453703</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
         <v>45736.31508101852</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46514,7 +46514,7 @@
         <v>45891.60346064815</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46571,7 +46571,7 @@
         <v>45174</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46628,7 +46628,7 @@
         <v>45174.87439814815</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>45894.55337962963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46747,7 +46747,7 @@
         <v>44992</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>45894.41133101852</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>45894.55216435185</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>44155</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>45873</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>45891.60103009259</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>45817.42607638889</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47156,7 +47156,7 @@
         <v>45894.4825</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>45891.59726851852</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>45891.59938657407</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>45014</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>45895.42582175926</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>45246.41783564815</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>45813.56320601852</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45895.373125</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>44218</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>45896.66505787037</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>45896.66944444444</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>45896.81087962963</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>45895.3627662037</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>45453.55534722222</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47984,7 +47984,7 @@
         <v>45022.34695601852</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>44987.5428587963</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48098,7 +48098,7 @@
         <v>45898.86685185185</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48155,7 +48155,7 @@
         <v>45898.58202546297</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>45770.84420138889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>45090.90752314815</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>44783</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45048</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>45884.60458333333</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48512,7 +48512,7 @@
         <v>45860</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>45356.66037037037</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>45043</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>45904.55924768518</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45071</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45903.45952546296</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45699</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45903.43489583334</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45798.59671296296</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45435</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>45547.64484953704</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49169,7 +49169,7 @@
         <v>45657.95927083334</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45678.47236111111</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49288,7 +49288,7 @@
         <v>45086.71662037037</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49350,7 +49350,7 @@
         <v>45908.46045138889</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>45636.45025462963</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>45583.34371527778</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45706.54385416667</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45908.47244212963</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>44286.88952546296</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49707,7 +49707,7 @@
         <v>45071</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>45096</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>45867.7115625</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>45153.36402777778</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49945,7 +49945,7 @@
         <v>45117</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50007,7 +50007,7 @@
         <v>45757.66474537037</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50064,7 +50064,7 @@
         <v>44980</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>45093</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>44974</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45807</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45881</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>44980.48200231481</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>44981</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>44966.57550925926</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45030.62916666667</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50669,7 +50669,7 @@
         <v>44977.57584490741</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>44433</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50788,7 +50788,7 @@
         <v>45721.51255787037</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>45721.51346064815</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50902,7 +50902,7 @@
         <v>44644</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45012</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>44652</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45076</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         <v>45706.49520833333</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>45048</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51254,7 +51254,7 @@
         <v>45121</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51316,7 +51316,7 @@
         <v>44803.59099537037</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51373,7 +51373,7 @@
         <v>45678.58166666667</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51430,7 +51430,7 @@
         <v>45771.66951388889</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>45769.41631944444</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51554,7 +51554,7 @@
         <v>45628.56513888889</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51616,7 +51616,7 @@
         <v>44159.36447916667</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51673,7 +51673,7 @@
         <v>45436.41305555555</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>45758.60465277778</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51792,7 +51792,7 @@
         <v>45758.61055555556</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>45699.65944444444</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51911,7 +51911,7 @@
         <v>45092.36790509259</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45535.91413194445</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45373.48878472222</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
         <v>45219.32268518519</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>45330</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>45386.32806712963</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52258,7 +52258,7 @@
         <v>45442.67793981481</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>45723.67724537037</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52377,7 +52377,7 @@
         <v>45747.59501157407</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>45027</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>45373.72511574074</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>44935</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>45558</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>44935.60138888889</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52729,7 +52729,7 @@
         <v>45478.47236111111</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         <v>45118</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52848,7 +52848,7 @@
         <v>44980</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52910,7 +52910,7 @@
         <v>44977.63902777778</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45678.6377199074</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45153</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45603.49528935185</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>44936</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45742.31784722222</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         <v>45153</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53324,7 +53324,7 @@
         <v>44907.65043981482</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53381,7 +53381,7 @@
         <v>45211.52895833334</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53438,7 +53438,7 @@
         <v>44936</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53495,7 +53495,7 @@
         <v>45016.64986111111</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53557,7 +53557,7 @@
         <v>45129</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53614,7 +53614,7 @@
         <v>45457.59425925926</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53671,7 +53671,7 @@
         <v>45250.5799537037</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -53728,7 +53728,7 @@
         <v>45764.43782407408</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -53785,7 +53785,7 @@
         <v>45405</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -53842,7 +53842,7 @@
         <v>45497</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -53899,7 +53899,7 @@
         <v>45684.4203125</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53961,7 +53961,7 @@
         <v>45706.54204861111</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54018,7 +54018,7 @@
         <v>45706.54572916667</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54075,7 +54075,7 @@
         <v>45310</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45012</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45798.58304398148</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>44896</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>44299</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>44264</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>45579</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>45139</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>45645.27462962963</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45012</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45441</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>45568</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45880.62738425926</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>45886.64045138889</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>45783.4903125</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45133</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>45604</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>45421</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45723.61545138889</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45742.41269675926</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>45832.36966435185</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>44578</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>44412</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45723.59275462963</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45568</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>45723.57098379629</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>45731.65016203704</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>45881.41636574074</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45421</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45042</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45771.69168981481</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44977</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>45604</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>45832.31648148148</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>45833.56057870371</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>44931</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45884.4946875</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>45764.47825231482</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>45013.77040509259</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>45086</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>45905.42704861111</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45583</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>45441.33914351852</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>45012</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44789</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45782.659375</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45783.68689814815</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>45258.56491898148</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>45568.44137731481</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>45832.3365625</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>45733.45780092593</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>45694</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>45772.6571412037</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45758.54390046297</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>45583</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>44454</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>45086</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45905.3244675926</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44308</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44480</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>44426</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44524</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>44452</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>44490</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>45723.66964120371</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         <v>45583.3479050926</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>45770.63996527778</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>45408</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>45763.60795138889</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>45783.61222222223</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>45376</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45362</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44886.54420138889</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>45796</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>44089</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>45201</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>45421</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>45096</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>45716.5672337963</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>45723.55663194445</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>45583</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>45201</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45251</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>44777.49493055556</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>45580</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>45117</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>44354</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>45702.76395833334</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>45742.43848379629</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>45771.76943287037</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>45747.58131944444</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>45174</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>45369</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>45056</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>45042</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>45905.58907407407</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>45583</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>45744</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45744.41443287037</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>45411.57177083333</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>44132</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>45348.68336805556</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>44151</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>44219</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>44211</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>44211</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>44158</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>44146</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>44301</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>44307</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>44530</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>44582.4696875</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>44456</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>44456</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>44211</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>44217</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>44214</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>44176</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>44107</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>44502</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>44622</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>44537</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>44218</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>44825.47923611111</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44728.82296296296</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>44340.80107638889</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44279</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>44739</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>44368</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>44719.43086805556</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44216</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>44169</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44169</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>44370</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>44258</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>44503</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>44448</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         <v>44440</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>44306</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>44368</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12121,7 +12121,7 @@
         <v>44441</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>44301</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>44865</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44294</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>44286</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44524.67836805555</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44385</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>44696.775</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>44390</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>44432</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44433</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44447</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>44494</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>44340</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>44333</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>44671</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44713</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>44368.88704861111</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44813</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>44530</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>44515</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44571</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44169</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44442.66228009259</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44208</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44475</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44475</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44272</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>44393</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>44630.3978587963</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44371</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>44371</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>44124.63679398148</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44362</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44211</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>44211</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>44524</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>44271.81282407408</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>44447</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>44530</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44313</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>44300</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44300</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>44446</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>44459</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>44503</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>44321</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>44879.39153935185</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>44459</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>44475</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>44475</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44249</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44574</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44886.47697916667</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>44686</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>44602</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44726</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44449</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44889.55255787037</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>44328</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         <v>44452</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>44098</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>44348</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>44825</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44487</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44358</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>44596</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>44468</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>44152</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>44756</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>44874</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>44219</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>44162</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>44137</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>44137</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>44432</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>44630</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>44582</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>44740</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>44825</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>44208</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>44252</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>44279</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>44741.57063657408</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>44445</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>44557</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>44441</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>44270</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>44302</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>44730</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
         <v>44869.4575</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>44354.45140046296</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45043.53597222222</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45215.63818287037</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>44825</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>44865</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>45072</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>44862</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>44362</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45043</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45709.4119212963</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45202</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45532</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>45678.57045138889</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>44578</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>45363.58979166667</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45405</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>44326</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>44326</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>44326</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>44452</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>44272</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>45736.72646990741</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>44805</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>45118</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>45369.62108796297</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>45336</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45741.63417824074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>45092</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>45037</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45369.61550925926</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>45414.3944212963</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45268</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>45742.32277777778</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>45758.56056712963</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45106</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>45379</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19595,7 +19595,7 @@
         <v>45709.42859953704</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45240</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>45373.73894675926</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>44862</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>45644</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45629.7202662037</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>44860</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45763.64096064815</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>45339.5277199074</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>44414</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45408.49326388889</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45254</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45386</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         <v>45726.91224537037</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>45741.53599537037</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>44462</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>45777.61991898148</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44607</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44322</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44344.49251157408</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>44363</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45782.66719907407</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>44950</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>45092.35266203704</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45783</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45006</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44433</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45784</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45784.62866898148</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45317</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45783.48681712963</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>45030.62740740741</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45030</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45359.68173611111</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>44994.41405092592</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45334</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45128</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>45110.56027777777</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45110</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>44861</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45432.6291550926</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>45425.89037037037</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44880.44351851852</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45132</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45317</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>45092.36126157407</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>44939</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>45278</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>44858</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>45370</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45786.36358796297</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>45671.62931712963</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>44957</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>45117</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>45670</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>44236</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44494</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44974.564375</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>44313</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>44163</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>45771.44005787037</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45587.58498842592</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>45595</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>45637</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>45593.59819444444</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>45673.49019675926</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45453.54733796296</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45453.55123842593</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23688,7 +23688,7 @@
         <v>45126</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>45126</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>45093</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>45141</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45786</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>45789.42597222222</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44565</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45310.41982638889</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>45145</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45400</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>45790</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>45671.59245370371</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>44361</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>44488</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>45096</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>45403.86942129629</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44935.64165509259</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>45114</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45114</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45706.47790509259</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45792.42109953704</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>45792.42542824074</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>45527.43385416667</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>45758.36203703703</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>45546</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>45356.64872685185</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>45106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>45678.57503472222</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>45794.82583333334</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25386,7 +25386,7 @@
         <v>45266</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>45794.81975694445</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>45794.82150462963</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45490.72372685185</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44930</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>45794.81730324074</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>45796.49842592593</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>45092.35369212963</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>44936</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45336</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>45266.69091435185</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>45796</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45794.81583333333</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>45794.82371527778</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45796</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45796.36326388889</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26303,7 +26303,7 @@
         <v>45191</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>44168</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45259</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45033</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>44536</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>44596</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44363</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>44573</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45798.66228009259</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>44890</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45797.39876157408</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>45723.65960648148</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45550.68804398148</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>45798.45043981481</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>45414.5519212963</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45565.5381712963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45408</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>45554.28857638889</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45727.6683449074</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>45159</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>45432.54622685185</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>45722.46946759259</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>45043</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>45803.43815972222</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>45804.59579861111</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>45762.76337962963</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44582</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44641.78332175926</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>45183.65135416666</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>45183.65233796297</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>45673</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>45053.36554398148</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>45217.51479166667</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>45636.4737962963</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>45313</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>45716.40918981482</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         <v>45121</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45202.56994212963</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>45365</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28591,7 +28591,7 @@
         <v>44176</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>45442.6052199074</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>45442.60829861111</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>44936</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28834,7 +28834,7 @@
         <v>45178.43909722222</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>45205.3119212963</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>45205.35753472222</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>45369</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>45684.41622685185</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>45030</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>44889</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>44679</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29310,7 +29310,7 @@
         <v>45028</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>44910</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29429,7 +29429,7 @@
         <v>45758.60146990741</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>44181</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45761.59716435185</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44630</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>45211.52641203703</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44131</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>45106</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44181</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>44651.42819444444</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>45201.63637731481</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>45817</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>45657.94784722223</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>45817</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>44427.49322916667</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>45817.64487268519</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45446.57724537037</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45446.5790625</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>45817.47909722223</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45817.41037037037</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>45369.61841435185</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>45820.37113425926</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>45261.50924768519</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>45215</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45678.57731481481</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>44936.46326388889</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>45820.39863425926</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>44974.65918981482</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>45254.54892361111</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>45215</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>45824.32293981482</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>45188</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>45824.45221064815</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>45715.5837962963</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>45723.66629629629</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>45764.47553240741</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>45824.31493055556</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         <v>45699.75583333334</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31578,7 +31578,7 @@
         <v>44943.56112268518</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>45579.56570601852</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45527.40489583334</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45204</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45468.82832175926</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>45174</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31935,7 +31935,7 @@
         <v>45174</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>44448</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32049,7 +32049,7 @@
         <v>45769.62891203703</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45401.46640046296</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>45274</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>45394</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>45453.52299768518</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>45832</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
         <v>45252</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45238.33091435185</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45191.39708333334</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>45758.56946759259</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>45254</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>45832</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>45832</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>44455</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>45833.4374537037</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>45833.40451388889</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>45246.41627314815</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>45246</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>45049</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>44455.68550925926</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>44956</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45719.4522337963</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>44956</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>45833.65659722222</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>45716.45121527778</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>44943</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33581,7 +33581,7 @@
         <v>45252.91344907408</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33638,7 +33638,7 @@
         <v>45272</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45769.40231481481</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>44974</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45764.43002314815</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>45091</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
         <v>45838.683125</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>45558.54422453704</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34057,7 +34057,7 @@
         <v>45112</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>44677</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34171,7 +34171,7 @@
         <v>44834</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34233,7 +34233,7 @@
         <v>45317</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>44741</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>45008.66204861111</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>45399.62587962963</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45836</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>45317</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>44249</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>44504</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34714,7 +34714,7 @@
         <v>44965</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>45014</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>44862</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>44956.54967592593</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34947,7 +34947,7 @@
         <v>45583.55850694444</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45356.64724537037</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35066,7 +35066,7 @@
         <v>45758.35732638889</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35123,7 +35123,7 @@
         <v>45636.45989583333</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35180,7 +35180,7 @@
         <v>45614.46292824074</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>44279</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>45716.37259259259</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>45266.66998842593</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45840.65777777778</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>44859</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>44719.43200231482</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35594,7 +35594,7 @@
         <v>44469</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>45581.62796296296</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45330</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>44573.38521990741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>45414.39614583334</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>45266</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>45840.65592592592</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>44851</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>44243</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>45840.6602199074</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36164,7 +36164,7 @@
         <v>45645.27707175926</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36221,7 +36221,7 @@
         <v>45106</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36278,7 +36278,7 @@
         <v>45763.41083333334</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>44998</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>44512</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>44970.65930555556</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36516,7 +36516,7 @@
         <v>44993</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>44980</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         <v>45030</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36697,7 +36697,7 @@
         <v>45043</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>44312</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>45840.66780092593</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>45386.35986111111</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>45769.57802083333</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>44721</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>45114</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>44221</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45178.4275</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>45629.67508101852</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>45629.67931712963</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>45098.37322916667</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>44805</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45096</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>45117</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>45582.98494212963</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>45727.64337962963</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>44384</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>44767</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37830,7 +37830,7 @@
         <v>45016.67141203704</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>45597.40140046296</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>45469.43265046296</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>45268</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>44599</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38120,7 +38120,7 @@
         <v>45726.90959490741</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>44713.58678240741</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38234,7 +38234,7 @@
         <v>45121</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>45840.66978009259</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>44597</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>44225</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>45747.44502314815</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38529,7 +38529,7 @@
         <v>45883.58974537037</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38591,7 +38591,7 @@
         <v>45883.63648148148</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>45883.69113425926</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38705,7 +38705,7 @@
         <v>45883.74664351852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38762,7 +38762,7 @@
         <v>45201.56556712963</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         <v>45030.61489583334</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>45030.61744212963</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>44853.64244212963</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38990,7 +38990,7 @@
         <v>45678.59783564815</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39047,7 +39047,7 @@
         <v>44754.57658564814</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>44742</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39161,7 +39161,7 @@
         <v>44999</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>44739.52209490741</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39280,7 +39280,7 @@
         <v>45883.5738425926</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39337,7 +39337,7 @@
         <v>44970.44197916667</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>45110</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39461,7 +39461,7 @@
         <v>44826</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39518,7 +39518,7 @@
         <v>45442.38490740741</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39575,7 +39575,7 @@
         <v>45884.45916666667</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45881</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>45883.58756944445</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>45442.61221064815</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>45008.62458333333</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>44980</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>45702.76590277778</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39994,7 +39994,7 @@
         <v>45013.63658564815</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>45215.63990740741</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>45106</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>45229</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>45884.57759259259</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45884.68263888889</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45764.44263888889</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>45716.57158564815</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>44364.78170138889</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45715.56964120371</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40574,7 +40574,7 @@
         <v>44746</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>44880</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>44992</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40745,7 +40745,7 @@
         <v>44575</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40802,7 +40802,7 @@
         <v>44957</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44945.58030092593</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>45093.54811342592</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>45729</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>45110</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>45274.43547453704</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>45733.44431712963</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>44096</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>45772.6652662037</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>45254</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>45638</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>45883.59934027777</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41541,7 +41541,7 @@
         <v>45077</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41598,7 +41598,7 @@
         <v>45509.57052083333</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41655,7 +41655,7 @@
         <v>45043</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>45183</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>45053.82055555555</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>45614.52813657407</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>45049.34974537037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>45049.35048611111</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>45527.41597222222</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>44939</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42116,7 +42116,7 @@
         <v>45012.79270833333</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45237</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45769.45751157407</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>44181</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45043.49425925926</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>45769</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>45769</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42530,7 +42530,7 @@
         <v>44454</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>45733.43347222222</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42654,7 +42654,7 @@
         <v>44096</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42711,7 +42711,7 @@
         <v>45671.5678125</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>44860</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>44137</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45741.51940972222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>44439.97621527778</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43011,7 +43011,7 @@
         <v>44147</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43068,7 +43068,7 @@
         <v>45706.42958333333</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43125,7 +43125,7 @@
         <v>44908</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>45090</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43244,7 +43244,7 @@
         <v>44896</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43306,7 +43306,7 @@
         <v>44897</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45642</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>44900</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>45520.52375</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43549,7 +43549,7 @@
         <v>45887</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>45733.62203703704</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>45678.44092592593</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43725,7 +43725,7 @@
         <v>45769</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43782,7 +43782,7 @@
         <v>45686.61590277778</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>44897</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43906,7 +43906,7 @@
         <v>44928.45552083333</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>44923.67971064815</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>45731.59962962963</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44151.53271990741</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>45886</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>45886.65516203704</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44867</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>45279.66864583334</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>44907.66710648148</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>44588</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>44105</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>45888.4712037037</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45888.4658449074</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45887</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>44237</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>45845.45563657407</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>45442.68033564815</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>45888.46922453704</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>44957</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45039,7 +45039,7 @@
         <v>45436.41847222222</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45101,7 +45101,7 @@
         <v>45888.61847222222</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>45845.65797453704</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45225,7 +45225,7 @@
         <v>45797</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>45043</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>44333</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>44783</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>44861</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45520,7 +45520,7 @@
         <v>44166</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>45008</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>45877</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45691,7 +45691,7 @@
         <v>44936</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45753,7 +45753,7 @@
         <v>44936</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45815,7 +45815,7 @@
         <v>45030</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>44177</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45929,7 +45929,7 @@
         <v>44177</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45986,7 +45986,7 @@
         <v>45889</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>45877</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46100,7 +46100,7 @@
         <v>45798.60880787037</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46162,7 +46162,7 @@
         <v>45889</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46219,7 +46219,7 @@
         <v>45731.60166666667</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46276,7 +46276,7 @@
         <v>45716.39159722222</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46333,7 +46333,7 @@
         <v>44358</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>45796.44922453703</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
         <v>45736.31508101852</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46514,7 +46514,7 @@
         <v>45891.60346064815</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46571,7 +46571,7 @@
         <v>45174</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46628,7 +46628,7 @@
         <v>45174.87439814815</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>45894.55337962963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46747,7 +46747,7 @@
         <v>44992</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>45894.41133101852</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>45894.55216435185</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>44155</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>45873</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>45891.60103009259</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>45817.42607638889</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47156,7 +47156,7 @@
         <v>45894.4825</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>45891.59726851852</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>45891.59938657407</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>45014</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>45895.42582175926</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>45246.41783564815</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>45813.56320601852</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45895.373125</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>44218</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>45896.66505787037</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>45896.66944444444</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>45896.81087962963</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>45895.3627662037</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>45453.55534722222</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47984,7 +47984,7 @@
         <v>45022.34695601852</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>44987.5428587963</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48098,7 +48098,7 @@
         <v>45898.86685185185</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48155,7 +48155,7 @@
         <v>45898.58202546297</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>45770.84420138889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>45090.90752314815</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>44783</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45048</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>45884.60458333333</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48512,7 +48512,7 @@
         <v>45860</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>45356.66037037037</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>45043</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>45904.55924768518</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45071</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45903.45952546296</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45699</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45903.43489583334</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45798.59671296296</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45435</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>45547.64484953704</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49169,7 +49169,7 @@
         <v>45657.95927083334</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45678.47236111111</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49288,7 +49288,7 @@
         <v>45086.71662037037</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49350,7 +49350,7 @@
         <v>45908.46045138889</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>45636.45025462963</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>45583.34371527778</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45706.54385416667</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45908.47244212963</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>44286.88952546296</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49707,7 +49707,7 @@
         <v>45071</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>45096</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>45867.7115625</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>45153.36402777778</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49945,7 +49945,7 @@
         <v>45117</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50007,7 +50007,7 @@
         <v>45757.66474537037</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50064,7 +50064,7 @@
         <v>44980</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>45093</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>44974</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45807</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45881</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>44980.48200231481</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>44981</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>44966.57550925926</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45030.62916666667</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50669,7 +50669,7 @@
         <v>44977.57584490741</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>44433</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50788,7 +50788,7 @@
         <v>45721.51255787037</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>45721.51346064815</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50902,7 +50902,7 @@
         <v>44644</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45012</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>44652</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45076</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         <v>45706.49520833333</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>45048</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51254,7 +51254,7 @@
         <v>45121</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51316,7 +51316,7 @@
         <v>44803.59099537037</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51373,7 +51373,7 @@
         <v>45678.58166666667</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51430,7 +51430,7 @@
         <v>45771.66951388889</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>45769.41631944444</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51554,7 +51554,7 @@
         <v>45628.56513888889</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51616,7 +51616,7 @@
         <v>44159.36447916667</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51673,7 +51673,7 @@
         <v>45436.41305555555</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>45758.60465277778</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51792,7 +51792,7 @@
         <v>45758.61055555556</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>45699.65944444444</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51911,7 +51911,7 @@
         <v>45092.36790509259</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45535.91413194445</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45373.48878472222</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
         <v>45219.32268518519</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>45330</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>45386.32806712963</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52258,7 +52258,7 @@
         <v>45442.67793981481</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>45723.67724537037</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52377,7 +52377,7 @@
         <v>45747.59501157407</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>45027</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>45373.72511574074</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>44935</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>45558</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>44935.60138888889</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52729,7 +52729,7 @@
         <v>45478.47236111111</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         <v>45118</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52848,7 +52848,7 @@
         <v>44980</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52910,7 +52910,7 @@
         <v>44977.63902777778</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45678.6377199074</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45153</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45603.49528935185</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>44936</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45742.31784722222</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         <v>45153</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53324,7 +53324,7 @@
         <v>44907.65043981482</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53381,7 +53381,7 @@
         <v>45211.52895833334</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53438,7 +53438,7 @@
         <v>44936</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53495,7 +53495,7 @@
         <v>45016.64986111111</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53557,7 +53557,7 @@
         <v>45129</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53614,7 +53614,7 @@
         <v>45457.59425925926</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53671,7 +53671,7 @@
         <v>45250.5799537037</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -53728,7 +53728,7 @@
         <v>45764.43782407408</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -53785,7 +53785,7 @@
         <v>45405</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -53842,7 +53842,7 @@
         <v>45497</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -53899,7 +53899,7 @@
         <v>45684.4203125</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53961,7 +53961,7 @@
         <v>45706.54204861111</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54018,7 +54018,7 @@
         <v>45706.54572916667</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54075,7 +54075,7 @@
         <v>45310</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45012</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45798</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>44896</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>44299</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>44264</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>45579</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>45139</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>45645.27462962963</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45012</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45783</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>45441</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>45880.62738425926</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45568</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>45886.64045138889</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>45133</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>45604</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44578</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>45723.61545138889</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>45742.41269675926</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45832.36966435185</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>44412</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45881.41636574074</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45568</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45042</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>45723.59275462963</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45723.57098379629</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>45731.65016203704</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45421</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>45771.69168981481</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45905.42704861111</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>44931</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>45583</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>45922.60398148148</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45884.4946875</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>45441.33914351852</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45012</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>45764.47825231482</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45013.77040509259</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>45086</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>44977</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45832.31648148148</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>45833.56057870371</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>45604</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>44789</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>45568.44137731481</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>45258.56491898148</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45905.3244675926</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44886.54420138889</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>44454</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>45086</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>45922.57796296296</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>45733.45780092593</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>45694</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>45772.6571412037</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>45758.54390046297</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>45583</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45782.659375</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>45783.68689814815</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>45723.55663194445</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>45832.3365625</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>44308</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>44480</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>44426</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>44524</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>44452</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>44490</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>45723.66964120371</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>45583.3479050926</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         <v>45905.58907407407</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>45251</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>45174</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>45056</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>45042</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>45580</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>45583</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45924.69556712963</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>45117</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>45744</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>45744.41443287037</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>45201</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>44354</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>45411.57177083333</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>44132</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>45702.76395833334</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45742.43848379629</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>45348.68336805556</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>45770.63996527778</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>45747.58131944444</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>45763.60795138889</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>45783.61222222223</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>45408</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>45796</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>45376</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>45362</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>45583</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>45201</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>45421</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>45096</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45716.5672337963</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>45369</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>44777.49493055556</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>44151</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>44219</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>44211</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>44211</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>44146</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>44456</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>44456</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>44301</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>44307</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>44530</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>44582.4696875</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         <v>44211</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44217</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44214</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44176</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>44107</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44502</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44622</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>44537</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>44218</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44825.47923611111</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>44340.80107638889</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44728.82296296296</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>44279</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>44739</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>44368</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>44719.43086805556</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>44169</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>44169</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>44216</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>44370</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>44258</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44440</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44503</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         <v>44448</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>44368</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>44306</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>44441</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>44301</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>44865</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>44294</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>44286</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44524.67836805555</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>44385</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>44696.775</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44390</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>44432</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>44433</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>44494</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44447</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44368.88704861111</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>44340</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>44333</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44671</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>44713</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>44813</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         <v>44530</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>44515</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>44571</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>44169</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>44442.66228009259</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>44208</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>44475</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>44475</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>44272</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>44393</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>44630.3978587963</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>44371</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>44371</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>44124.63679398148</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>44362</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>44211</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>44211</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>44524</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>44271.81282407408</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>44447</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>44530</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>44503</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>44313</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>44300</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>44300</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>44459</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>44446</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>44321</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44879.39153935185</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>44459</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>44475</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>44475</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>44249</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>44574</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>44686</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>44602</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44889.55255787037</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>44328</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>44452</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>44825</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>44756</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>44452</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>44272</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>44137</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>44137</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44630</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44432</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>44344.49251157408</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>44363</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>44582</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>44313</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>44740</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>44825</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>44279</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>44445</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>44557</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>44741.57063657408</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>44869.4575</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>44302</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>44730</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>44363</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>45709.4119212963</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>44270</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45405</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>44354.45140046296</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>45268</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45043.53597222222</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45215.63818287037</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>44726</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>44825</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>44362</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>44865</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>45072</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44862</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>45043</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>45202</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>45532</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45678.57045138889</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>44487</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44578</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44326</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44326</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44326</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>45363.58979166667</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>44348</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44596</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>45736.72646990741</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44468</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44805</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>45118</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>45369.62108796297</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>45336</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45741.63417824074</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>45092</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>45037</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>44886.47697916667</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45414.3944212963</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44874</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>44219</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44162</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>44449</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>44974.65918981482</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>44358</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45373.73894675926</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>44862</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>44860</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>44208</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44252</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>44970.44197916667</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>44441</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45891.60103009259</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>45817.42607638889</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>45894.4825</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>44414</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>45386</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45891.59726851852</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>45891.59938657407</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>45895.42582175926</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>45215.63990740741</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45106</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>44462</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>45813.56320601852</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         <v>45895.373125</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>45638</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45896.66505787037</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>44943.56112268518</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>45896.66944444444</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>45896.81087962963</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45895.3627662037</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>45053.82055555555</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>45579.56570601852</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>44181</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>45527.40489583334</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21039,7 +21039,7 @@
         <v>45043.49425925926</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>44433</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>45671.5678125</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>45317</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21282,7 +21282,7 @@
         <v>45174</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>45174</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>44908</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>45898.86685185185</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45359.68173611111</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>44897</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45898.58202546297</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>44448</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45334</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>45128</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>44861</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>45432.6291550926</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45425.89037037037</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>45642</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>44880.44351851852</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>45733.62203703704</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>45317</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>45686.61590277778</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>45394</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>45453.52299768518</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44939</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>45860</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>44867</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45278</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>44858</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22767,7 +22767,7 @@
         <v>45238.33091435185</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>45117</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45904.55924768518</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44105</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>45442.68033564815</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>44236</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>44957</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>44163</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45043</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>44455</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>44333</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>45903.45952546296</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>44861</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>44166</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>45008</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>44936</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>44936</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45030</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>45049</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45903.43489583334</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>44177</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>44177</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>45798.59671296296</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>44943</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>45093</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         <v>45764.43002314815</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24319,7 +24319,7 @@
         <v>44358</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         <v>45091</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>45908.46045138889</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>45558.54422453704</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>44361</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45112</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>44488</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>45706.54385416667</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45096</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>44677</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45174</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>45174.87439814815</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45908.47244212963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>44286.88952546296</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>44992</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>44155</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45014</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>45867.7115625</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>44834</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45246.41783564815</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>44218</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>45453.55534722222</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45266</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>45022.34695601852</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>44987.5428587963</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>45490.72372685185</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>44930</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>45317</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>44741</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>45008.66204861111</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>45770.84420138889</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>45090.90752314815</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>44936</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>44890</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>44783</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>44965</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         <v>45014</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>45048</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         <v>45414.5519212963</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>44956.54967592593</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>45583.55850694444</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>45356.64724537037</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>45758.35732638889</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>44152</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>45636.45989583333</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>45356.66037037037</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>45043</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45071</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>45699</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>45614.46292824074</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>44279</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>45435</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27363,7 +27363,7 @@
         <v>44719.43200231482</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>44582</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>45581.62796296296</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45547.64484953704</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>45657.95927083334</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>45678.47236111111</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44573.38521990741</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>45917.5712037037</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45917.58798611111</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>45086.71662037037</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>45636.45025462963</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45917.46651620371</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>45917.34472222222</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>45583.34371527778</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>45414.39614583334</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>45807</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>45917.34253472222</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>45071</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>45645.27707175926</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>45917.60378472223</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44998</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>44512</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>44970.65930555556</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>45096</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28781,7 +28781,7 @@
         <v>44993</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44980</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>45030</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>45922.60783564814</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45922.55509259259</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>45202.56994212963</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44312</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29200,7 +29200,7 @@
         <v>45796</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>44158</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>45365</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>45796</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>45386.35986111111</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29495,7 +29495,7 @@
         <v>44176</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>45922.61070601852</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>45153.36402777778</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>45117</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>45757.66474537037</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>45769.57802083333</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>44980</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45922.59829861111</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>44721</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>45093</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>44974</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>45114</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>44221</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>44980.48200231481</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>44981</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>44966.57550925926</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>45030.62916666667</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>45442.6052199074</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30566,7 +30566,7 @@
         <v>45442.60829861111</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>45478.42675925926</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>45924.61788194445</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>45924.61070601852</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>45924.70513888889</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>44936</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>45178.4275</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>45923.67458333333</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>45706.54204861111</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>45881</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44977.57584490741</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31223,7 +31223,7 @@
         <v>45178.43909722222</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>45764.47553240741</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>45924.65238425926</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>44433</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>45881</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>45030</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>45721.51255787037</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>45721.51346064815</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44644</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>44889</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45012</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>45028</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31927,7 +31927,7 @@
         <v>44652</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>45798</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>45629.67508101852</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>45629.67931712963</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>45098.37322916667</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>44805</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>45096</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>45117</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44910</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>45582.98494212963</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>45797</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>45076</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>45727.64337962963</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>45926.61226851852</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>44181</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>45597.40140046296</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32884,7 +32884,7 @@
         <v>45706.49520833333</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45469.43265046296</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>45726.90959490741</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33055,7 +33055,7 @@
         <v>44713.58678240741</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>44131</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>45121</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>45106</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45048</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>45121</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44181</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>45747.44502314815</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>45201.56556712963</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>45030.61489583334</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>45030.61744212963</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44853.64244212963</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45201.63637731481</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>44803.59099537037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>44742</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>44427.49322916667</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>44999</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>45110</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>45678.58166666667</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>45771.66951388889</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>45369.61841435185</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45769.41631944444</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>44826</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>45442.38490740741</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>45215</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34510,7 +34510,7 @@
         <v>45628.56513888889</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>44159.36447916667</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>45678.57731481481</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>44936.46326388889</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>45436.41305555555</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>45758.60465277778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45758.61055555556</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>45699.65944444444</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45883.58974537037</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>45883.69113425926</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45884.57759259259</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>45884.60458333333</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>45442.61221064815</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>45883.74664351852</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>45884.45916666667</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>45092.36790509259</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>45008.62458333333</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>44980</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>45535.91413194445</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>45702.76590277778</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>45373.48878472222</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45884.68263888889</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35814,7 +35814,7 @@
         <v>45013.63658564815</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35871,7 +35871,7 @@
         <v>44439.97621527778</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>45883.63648148148</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>45883.5738425926</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>45883.59934027777</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45796</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36166,7 +36166,7 @@
         <v>45926.58292824074</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36223,7 +36223,7 @@
         <v>45883.58756944445</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>45229</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45764.44263888889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36394,7 +36394,7 @@
         <v>45219.32268518519</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36451,7 +36451,7 @@
         <v>45716.57158564815</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36508,7 +36508,7 @@
         <v>45330</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>44364.78170138889</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>45715.56964120371</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>44746</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>45386.32806712963</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36803,7 +36803,7 @@
         <v>45442.67793981481</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>44880</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>44992</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>44575</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>44957</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37098,7 +37098,7 @@
         <v>44945.58030092593</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37155,7 +37155,7 @@
         <v>45723.67724537037</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>45093.54811342592</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45729</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
         <v>45110</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37393,7 +37393,7 @@
         <v>45274.43547453704</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>45747.59501157407</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>45027</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>45373.72511574074</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37626,7 +37626,7 @@
         <v>45733.44431712963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44935</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>45558</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>44935.60138888889</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>45478.47236111111</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45772.6652662037</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>45118</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>45254</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>44980</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>45077</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>45509.57052083333</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>45043</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38360,7 +38360,7 @@
         <v>44977.63902777778</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>45183</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>45678.6377199074</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38536,7 +38536,7 @@
         <v>45771.76943287037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>45153</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>45603.49528935185</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>45614.52813657407</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45049.34974537037</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>45049.35048611111</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>45527.41597222222</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>44936</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45742.31784722222</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>44939</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45012.79270833333</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45153</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39235,7 +39235,7 @@
         <v>45237</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39297,7 +39297,7 @@
         <v>45769.45751157407</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39359,7 +39359,7 @@
         <v>45769</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39416,7 +39416,7 @@
         <v>45769</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39473,7 +39473,7 @@
         <v>44454</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>44907.65043981482</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39592,7 +39592,7 @@
         <v>45211.52895833334</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>44936</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>45733.43347222222</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39768,7 +39768,7 @@
         <v>45016.64986111111</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>45129</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>44860</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>44137</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>45457.59425925926</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>45741.51940972222</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40120,7 +40120,7 @@
         <v>45250.5799537037</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40177,7 +40177,7 @@
         <v>44439.97621527778</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40239,7 +40239,7 @@
         <v>45764.43782407408</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>44147</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40353,7 +40353,7 @@
         <v>45706.42958333333</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>45405</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>45090</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         <v>45497</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40586,7 +40586,7 @@
         <v>44896</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40648,7 +40648,7 @@
         <v>45684.4203125</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40710,7 +40710,7 @@
         <v>45706.54572916667</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>45310</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>44900</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>45520.52375</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>45742.32277777778</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45769</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>44897</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41124,7 +41124,7 @@
         <v>45758.56056712963</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>44928.45552083333</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>44923.67971064815</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45731.59962962963</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>45709.42859953704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>44151.53271990741</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41486,7 +41486,7 @@
         <v>45629.7202662037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41543,7 +41543,7 @@
         <v>45763.64096064815</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>45726.91224537037</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>45777.61991898148</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>45782.66719907407</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>45783</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>45784</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>45784.62866898148</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         <v>45279.66864583334</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44907.66710648148</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>45783.48681712963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44588</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44237</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42257,7 +42257,7 @@
         <v>45436.41847222222</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>44783</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>45092.36126157407</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>45786.36358796297</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42495,7 +42495,7 @@
         <v>45671.62931712963</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>45731.60166666667</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42609,7 +42609,7 @@
         <v>45716.39159722222</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>45369.61550925926</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>45587.58498842592</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>45453.54733796296</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42842,7 +42842,7 @@
         <v>45453.55123842593</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>45106</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>45786</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45379</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43075,7 +43075,7 @@
         <v>45789.42597222222</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>44565</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45310.41982638889</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>45240</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43308,7 +43308,7 @@
         <v>45790</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>45644</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43427,7 +43427,7 @@
         <v>45792.42109953704</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43484,7 +43484,7 @@
         <v>45792.42542824074</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>45339.5277199074</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>45408.49326388889</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43655,7 +43655,7 @@
         <v>45254</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>45678.57503472222</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45794.82583333334</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43831,7 +43831,7 @@
         <v>45794.81975694445</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>45794.82150462963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>45741.53599537037</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
         <v>45794.81730324074</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44064,7 +44064,7 @@
         <v>45796.49842592593</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44121,7 +44121,7 @@
         <v>44607</v>
       </c>
       <c r=